--- a/parser/downloader/files/schedule.xlsx
+++ b/parser/downloader/files/schedule.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,6 +87,13 @@
       <sz val="20"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
+      <charset val="204"/>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="14"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="204"/>
       <b val="1"/>
@@ -97,6 +104,19 @@
       <name val="Times New Roman"/>
       <charset val="204"/>
       <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <charset val="204"/>
+      <color rgb="00FF0000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <charset val="204"/>
+      <b val="1"/>
+      <color rgb="00008000"/>
       <sz val="14"/>
     </font>
     <font>
@@ -114,6 +134,14 @@
       <sz val="14"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <charset val="204"/>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="14"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -128,7 +156,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="56">
+  <borders count="55">
     <border>
       <left/>
       <right/>
@@ -715,40 +743,6 @@
       </diagonal>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="00000000"/>
-      </left>
-      <right>
-        <color rgb="00000000"/>
-      </right>
-      <top>
-        <color rgb="00000000"/>
-      </top>
-      <bottom>
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal>
-        <color rgb="00000000"/>
-      </diagonal>
-    </border>
-    <border>
-      <left>
-        <color rgb="00000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="00000000"/>
-      </right>
-      <top>
-        <color rgb="00000000"/>
-      </top>
-      <bottom>
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal>
-        <color rgb="00000000"/>
-      </diagonal>
-    </border>
-    <border>
       <left>
         <color rgb="00000000"/>
       </left>
@@ -829,47 +823,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal>
-        <color rgb="00000000"/>
-      </diagonal>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color rgb="00000000"/>
@@ -932,6 +885,47 @@
       <left style="medium">
         <color rgb="00000000"/>
       </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal>
+        <color rgb="00000000"/>
+      </diagonal>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
       <right/>
       <top/>
       <bottom style="medium">
@@ -972,6 +966,23 @@
       <right>
         <color rgb="00000000"/>
       </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal>
+        <color rgb="00000000"/>
+      </diagonal>
+    </border>
+    <border>
+      <left>
+        <color rgb="00000000"/>
+      </left>
+      <right>
+        <color rgb="00000000"/>
+      </right>
       <top style="thin">
         <color rgb="00000000"/>
       </top>
@@ -995,28 +1006,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="bottom"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1072,42 +1087,46 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="43" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="46" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="19" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1123,11 +1142,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="52" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="50" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="29" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1142,7 +1165,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="48" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="43" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="29" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1150,19 +1177,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1178,52 +1205,66 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="29" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="29" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="34" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="54" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="52" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="53" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom" textRotation="90" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1672,40 +1713,40 @@
           <t>УТВЕРЖДАЮ:</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr"/>
+      <c r="AH1" s="3" t="inlineStr"/>
     </row>
     <row r="2" ht="57.75" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>ЗНАМЕНАТЕЛЬ</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РАСПИСАНИЕ  ЗАНЯТИЙ 07 - 11 октября 2024 - 2025 учебного года
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ЧИСЛИТЕЛЬ</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">РАСПИСАНИЕ  ЗАНЯТИЙ 14 - 18 октября  2024 - 2025 учебного года
 </t>
         </is>
       </c>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
-      <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
-      <c r="O2" s="4" t="n"/>
-      <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="4" t="n"/>
-      <c r="R2" s="4" t="n"/>
-      <c r="S2" s="4" t="n"/>
-      <c r="T2" s="4" t="n"/>
-      <c r="U2" s="4" t="n"/>
-      <c r="V2" s="4" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+      <c r="P2" s="5" t="n"/>
+      <c r="Q2" s="5" t="n"/>
+      <c r="R2" s="5" t="n"/>
+      <c r="S2" s="5" t="n"/>
+      <c r="T2" s="5" t="n"/>
+      <c r="U2" s="1" t="inlineStr"/>
+      <c r="V2" s="1" t="inlineStr"/>
       <c r="W2" s="1" t="inlineStr"/>
       <c r="X2" s="1" t="inlineStr"/>
       <c r="Y2" s="1" t="inlineStr"/>
@@ -1713,11 +1754,11 @@
       <c r="AA2" s="1" t="inlineStr"/>
       <c r="AB2" s="1" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr"/>
-      <c r="AD2" s="4" t="n"/>
-      <c r="AE2" s="4" t="n"/>
-      <c r="AF2" s="4" t="n"/>
-      <c r="AG2" s="4" t="n"/>
-      <c r="AH2" s="1" t="inlineStr"/>
+      <c r="AD2" s="5" t="n"/>
+      <c r="AE2" s="5" t="n"/>
+      <c r="AF2" s="5" t="n"/>
+      <c r="AG2" s="5" t="n"/>
+      <c r="AH2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="inlineStr"/>
@@ -1748,12 +1789,12 @@
       <c r="Z3" s="1" t="inlineStr"/>
       <c r="AA3" s="1" t="inlineStr"/>
       <c r="AB3" s="1" t="inlineStr"/>
-      <c r="AC3" s="6" t="inlineStr"/>
-      <c r="AD3" s="4" t="n"/>
-      <c r="AE3" s="4" t="n"/>
-      <c r="AF3" s="4" t="n"/>
-      <c r="AG3" s="4" t="n"/>
-      <c r="AH3" s="1" t="inlineStr"/>
+      <c r="AC3" s="7" t="inlineStr"/>
+      <c r="AD3" s="5" t="n"/>
+      <c r="AE3" s="5" t="n"/>
+      <c r="AF3" s="5" t="n"/>
+      <c r="AG3" s="5" t="n"/>
+      <c r="AH3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="inlineStr"/>
@@ -1785,11 +1826,11 @@
       <c r="AA4" s="1" t="inlineStr"/>
       <c r="AB4" s="1" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
-      <c r="AD4" s="4" t="n"/>
-      <c r="AE4" s="4" t="n"/>
-      <c r="AF4" s="4" t="n"/>
-      <c r="AG4" s="4" t="n"/>
-      <c r="AH4" s="1" t="inlineStr"/>
+      <c r="AD4" s="5" t="n"/>
+      <c r="AE4" s="5" t="n"/>
+      <c r="AF4" s="5" t="n"/>
+      <c r="AG4" s="5" t="n"/>
+      <c r="AH4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="1.5" customHeight="1" thickBot="1">
       <c r="A5" s="1" t="inlineStr"/>
@@ -1825,1617 +1866,1573 @@
       <c r="AE5" s="1" t="inlineStr"/>
       <c r="AF5" s="1" t="inlineStr"/>
       <c r="AG5" s="1" t="inlineStr"/>
-      <c r="AH5" s="1" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="58.5" customHeight="1" thickBot="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>День</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Урок</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>СТ - 11</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>СТ - 12</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>СД - 11</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">ОД - 11, ТД - 11, Ю - 11  </t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>ТИК - 11</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>ТИК - 12</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>Ю - 21</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>ПР - 31</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>ОД - 21</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>ОД - 31</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="12" t="inlineStr">
         <is>
           <t>ТД- 21</t>
         </is>
       </c>
-      <c r="N6" s="12" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t>К- 31</t>
         </is>
       </c>
-      <c r="O6" s="13" t="inlineStr"/>
-      <c r="P6" s="14" t="inlineStr">
+      <c r="O6" s="14" t="inlineStr"/>
+      <c r="P6" s="15" t="inlineStr">
         <is>
           <t>День</t>
         </is>
       </c>
-      <c r="Q6" s="14" t="inlineStr">
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>Урок</t>
         </is>
       </c>
-      <c r="R6" s="9" t="inlineStr">
+      <c r="R6" s="10" t="inlineStr">
         <is>
           <t>СТ - 11У</t>
         </is>
       </c>
-      <c r="S6" s="9" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>СТ - 21</t>
         </is>
       </c>
-      <c r="T6" s="9" t="inlineStr">
+      <c r="T6" s="10" t="inlineStr">
         <is>
           <t>СТ - 21У</t>
         </is>
       </c>
-      <c r="U6" s="9" t="inlineStr">
+      <c r="U6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">СТУ - 11 </t>
         </is>
       </c>
-      <c r="V6" s="9" t="inlineStr">
+      <c r="V6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">СТУ - 12 </t>
         </is>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">СТУ - 21 </t>
         </is>
       </c>
-      <c r="X6" s="8" t="inlineStr">
+      <c r="X6" s="9" t="inlineStr">
         <is>
           <t>СО - 11У</t>
         </is>
       </c>
-      <c r="Y6" s="9" t="inlineStr">
+      <c r="Y6" s="10" t="inlineStr">
         <is>
           <t>СО - 21У</t>
         </is>
       </c>
-      <c r="Z6" s="9" t="inlineStr">
+      <c r="Z6" s="10" t="inlineStr">
         <is>
           <t>СД - 21                  СД - 11У</t>
         </is>
       </c>
-      <c r="AA6" s="9" t="inlineStr">
+      <c r="AA6" s="10" t="inlineStr">
         <is>
           <t>СД - 21У</t>
         </is>
       </c>
-      <c r="AB6" s="9" t="inlineStr">
+      <c r="AB6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">ТИК - 21     </t>
         </is>
       </c>
-      <c r="AC6" s="15" t="inlineStr">
+      <c r="AC6" s="16" t="inlineStr">
         <is>
           <t>ТИК - 22        ТИК - 11У</t>
         </is>
       </c>
-      <c r="AD6" s="9" t="inlineStr">
+      <c r="AD6" s="10" t="inlineStr">
         <is>
           <t>ТИК - 21У</t>
         </is>
       </c>
-      <c r="AE6" s="15" t="inlineStr">
+      <c r="AE6" s="16" t="inlineStr">
         <is>
           <t>ТЭУ - 31</t>
         </is>
       </c>
-      <c r="AF6" s="9" t="inlineStr">
+      <c r="AF6" s="10" t="inlineStr">
         <is>
           <t>ТЭУ - 41</t>
         </is>
       </c>
-      <c r="AG6" s="9" t="inlineStr">
+      <c r="AG6" s="10" t="inlineStr">
         <is>
           <t>ТЭУ - 42</t>
         </is>
       </c>
-      <c r="AH6" s="1" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
     </row>
     <row r="7" ht="99.95" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">понедельник </t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Русский язык       Исаева Г.А.</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve"> Информатика    Олимова Е.Н.          1 подгруппа</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>География      Зайцева Л.В.</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>Обществознание   Кожевников В.Е.</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Иностранный язык            Шарипов И.Н. </t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve"> Математика       Ширнин А.Г.</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">БЖД         Ходаковский В.В. </t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>Иностранный язык            Шарипов И.Н.</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> История России   Козлов Д.В. </t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Трудовое право   Баринов С.В. </t>
         </is>
       </c>
-      <c r="K7" s="18" t="inlineStr"/>
-      <c r="L7" s="18" t="inlineStr"/>
-      <c r="M7" s="18" t="inlineStr"/>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="21" t="inlineStr"/>
-      <c r="P7" s="22" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr"/>
+      <c r="L7" s="19" t="inlineStr"/>
+      <c r="M7" s="21" t="inlineStr"/>
+      <c r="N7" s="22" t="inlineStr"/>
+      <c r="O7" s="1" t="inlineStr"/>
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">понедельник </t>
         </is>
       </c>
-      <c r="Q7" s="23" t="n">
+      <c r="Q7" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="18" t="inlineStr">
-        <is>
-          <t>Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.</t>
-        </is>
-      </c>
-      <c r="S7" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">История России   Козлов Д.В. </t>
-        </is>
-      </c>
-      <c r="T7" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Средства гигиены и профилактика стоматологических заболеваний полости рта  Станишевская Д.Н. </t>
-        </is>
-      </c>
-      <c r="U7" s="18" t="inlineStr"/>
-      <c r="V7" s="18" t="inlineStr"/>
-      <c r="W7" s="18" t="inlineStr"/>
-      <c r="X7" s="18" t="inlineStr"/>
-      <c r="Y7" s="20" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr"/>
+      <c r="S7" s="21" t="inlineStr"/>
+      <c r="T7" s="25" t="inlineStr">
+        <is>
+          <t>Стоматологические заболевания и их профилактика Станишевская Д.Н.</t>
+        </is>
+      </c>
+      <c r="U7" s="19" t="inlineStr"/>
+      <c r="V7" s="19" t="inlineStr"/>
+      <c r="W7" s="19" t="inlineStr"/>
+      <c r="X7" s="19" t="inlineStr"/>
+      <c r="Y7" s="25" t="inlineStr">
         <is>
           <t>Технология изготовления съемных пластиночных  протезов        Горин А.А.</t>
         </is>
       </c>
-      <c r="Z7" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Анатомия и физиология человека            Маклаков И.А. </t>
-        </is>
-      </c>
-      <c r="AA7" s="18" t="inlineStr">
+      <c r="Z7" s="21" t="inlineStr"/>
+      <c r="AA7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Сестринский уход за пациентами хирургического профиля        Байбакова А.Х. </t>
         </is>
       </c>
-      <c r="AB7" s="18" t="inlineStr"/>
-      <c r="AC7" s="18" t="inlineStr"/>
-      <c r="AD7" s="18" t="inlineStr">
+      <c r="AB7" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Анатомия и физиология человека          Маклаков И.А. </t>
+        </is>
+      </c>
+      <c r="AC7" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Анатомия и физиология человека          Маклаков И.А. </t>
+        </is>
+      </c>
+      <c r="AD7" s="19" t="inlineStr">
         <is>
           <t>Технология коррекции тела     Березовикова А.В.</t>
         </is>
       </c>
-      <c r="AE7" s="18" t="inlineStr">
-        <is>
-          <t>Технология косметических услуг                       Джокич Э.А.</t>
-        </is>
-      </c>
-      <c r="AF7" s="18" t="inlineStr"/>
-      <c r="AG7" s="18" t="inlineStr">
+      <c r="AE7" s="19" t="inlineStr"/>
+      <c r="AF7" s="21" t="inlineStr"/>
+      <c r="AG7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Выполнение работ по профессии "Маникюрша"  Алексеенко Е.М.  </t>
         </is>
       </c>
-      <c r="AH7" s="1" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="99.95" customHeight="1">
-      <c r="A8" s="24" t="n"/>
-      <c r="B8" s="25" t="n">
+      <c r="A8" s="26" t="n"/>
+      <c r="B8" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="26" t="n"/>
-      <c r="D8" s="26" t="n"/>
-      <c r="E8" s="26" t="n"/>
-      <c r="F8" s="26" t="n"/>
-      <c r="G8" s="26" t="n"/>
-      <c r="H8" s="26" t="n"/>
-      <c r="I8" s="27" t="n"/>
-      <c r="J8" s="26" t="n"/>
-      <c r="K8" s="26" t="n"/>
-      <c r="L8" s="26" t="n"/>
-      <c r="M8" s="26" t="n"/>
-      <c r="N8" s="28" t="n"/>
-      <c r="O8" s="21" t="inlineStr"/>
-      <c r="P8" s="29" t="n"/>
-      <c r="Q8" s="30" t="n">
+      <c r="C8" s="28" t="n"/>
+      <c r="D8" s="28" t="n"/>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
+      <c r="H8" s="28" t="n"/>
+      <c r="I8" s="29" t="n"/>
+      <c r="J8" s="28" t="n"/>
+      <c r="K8" s="28" t="n"/>
+      <c r="L8" s="28" t="n"/>
+      <c r="M8" s="28" t="n"/>
+      <c r="N8" s="30" t="n"/>
+      <c r="O8" s="1" t="inlineStr"/>
+      <c r="P8" s="31" t="n"/>
+      <c r="Q8" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="R8" s="26" t="n"/>
-      <c r="S8" s="26" t="n"/>
-      <c r="T8" s="28" t="n"/>
-      <c r="U8" s="26" t="n"/>
-      <c r="V8" s="26" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
-      <c r="Y8" s="28" t="n"/>
-      <c r="Z8" s="26" t="n"/>
-      <c r="AA8" s="26" t="n"/>
-      <c r="AB8" s="26" t="n"/>
-      <c r="AC8" s="26" t="n"/>
-      <c r="AD8" s="26" t="n"/>
-      <c r="AE8" s="26" t="n"/>
-      <c r="AF8" s="26" t="n"/>
-      <c r="AG8" s="26" t="n"/>
-      <c r="AH8" s="1" t="inlineStr"/>
+      <c r="R8" s="28" t="n"/>
+      <c r="S8" s="28" t="n"/>
+      <c r="T8" s="30" t="n"/>
+      <c r="U8" s="28" t="n"/>
+      <c r="V8" s="28" t="n"/>
+      <c r="W8" s="28" t="n"/>
+      <c r="X8" s="28" t="n"/>
+      <c r="Y8" s="30" t="n"/>
+      <c r="Z8" s="28" t="n"/>
+      <c r="AA8" s="28" t="n"/>
+      <c r="AB8" s="28" t="n"/>
+      <c r="AC8" s="28" t="n"/>
+      <c r="AD8" s="28" t="n"/>
+      <c r="AE8" s="28" t="n"/>
+      <c r="AF8" s="28" t="n"/>
+      <c r="AG8" s="28" t="n"/>
+      <c r="AH8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="99.95" customHeight="1">
-      <c r="A9" s="24" t="n"/>
-      <c r="B9" s="25" t="n">
+      <c r="A9" s="26" t="n"/>
+      <c r="B9" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>География      Зайцева Л.В.</t>
         </is>
       </c>
-      <c r="D9" s="31" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>География      Зайцева Л.В.</t>
         </is>
       </c>
-      <c r="E9" s="31" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>Обществознание   Кожевников В.Е.</t>
         </is>
       </c>
-      <c r="F9" s="31" t="inlineStr">
+      <c r="F9" s="33" t="inlineStr">
         <is>
           <t>Математика       Ширнин А.Г.</t>
         </is>
       </c>
-      <c r="G9" s="31" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve"> Информатика    Олимова Е.Н. </t>
         </is>
       </c>
-      <c r="H9" s="31" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>Русский язык       Исаева Г.А.</t>
         </is>
       </c>
-      <c r="I9" s="32" t="inlineStr">
+      <c r="I9" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">Конституционное право России     Баринов С.В. </t>
         </is>
       </c>
-      <c r="J9" s="31" t="inlineStr">
+      <c r="J9" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Иностранный язык            Шарипов И.Н. </t>
         </is>
       </c>
-      <c r="K9" s="33" t="inlineStr">
+      <c r="K9" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История России   Козлов Д.В. </t>
+        </is>
+      </c>
+      <c r="L9" s="33" t="inlineStr">
+        <is>
+          <t>Моделирование логистических систем     Коломиец А.И.                        УРОК НА ПРОИЗВОДСТВЕ</t>
+        </is>
+      </c>
+      <c r="M9" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История России   Козлов Д.В. </t>
+        </is>
+      </c>
+      <c r="N9" s="35" t="inlineStr">
+        <is>
+          <t>Маркетинг  Систейкина Е.Е.</t>
+        </is>
+      </c>
+      <c r="O9" s="1" t="inlineStr"/>
+      <c r="P9" s="31" t="n"/>
+      <c r="Q9" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" s="36" t="inlineStr"/>
+      <c r="S9" s="36" t="inlineStr"/>
+      <c r="T9" s="35" t="inlineStr">
+        <is>
+          <t>Стоматологические заболевания и их профилактика Станишевская Д.Н.</t>
+        </is>
+      </c>
+      <c r="U9" s="33" t="inlineStr"/>
+      <c r="V9" s="33" t="inlineStr"/>
+      <c r="W9" s="33" t="inlineStr"/>
+      <c r="X9" s="33" t="inlineStr">
+        <is>
+          <t>Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.</t>
+        </is>
+      </c>
+      <c r="Y9" s="35" t="inlineStr">
+        <is>
+          <t>Технология изготовления съемных пластиночных  протезов        Горин А.А.</t>
+        </is>
+      </c>
+      <c r="Z9" s="33" t="inlineStr">
         <is>
           <t>Физическая культура                    Ритор Л.М.</t>
         </is>
       </c>
-      <c r="L9" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Менеджмент       Систейкина Е.Е. </t>
-        </is>
-      </c>
-      <c r="M9" s="31" t="inlineStr">
+      <c r="AA9" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сестринский уход за пациентами хирургического профиля        Байбакова А.Х. </t>
+        </is>
+      </c>
+      <c r="AB9" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Анатомия и физиология человека          Маклаков И.А. </t>
+        </is>
+      </c>
+      <c r="AC9" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Анатомия и физиология человека          Маклаков И.А. </t>
+        </is>
+      </c>
+      <c r="AD9" s="33" t="inlineStr">
+        <is>
+          <t>Технология коррекции тела     Березовикова А.В.</t>
+        </is>
+      </c>
+      <c r="AE9" s="33" t="inlineStr"/>
+      <c r="AF9" s="33" t="inlineStr">
         <is>
           <t>Физическая культура                    Ритор Л.М.</t>
         </is>
       </c>
-      <c r="N9" s="33" t="inlineStr">
-        <is>
-          <t>Физическая культура                    Ритор Л.М.</t>
-        </is>
-      </c>
-      <c r="O9" s="21" t="inlineStr"/>
-      <c r="P9" s="29" t="n"/>
-      <c r="Q9" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">История России   Козлов Д.В. </t>
-        </is>
-      </c>
-      <c r="S9" s="31" t="inlineStr">
-        <is>
-          <t>Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.</t>
-        </is>
-      </c>
-      <c r="T9" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Средства гигиены и профилактика стоматологических заболеваний полости рта  Станишевская Д.Н. </t>
-        </is>
-      </c>
-      <c r="U9" s="31" t="inlineStr"/>
-      <c r="V9" s="31" t="inlineStr"/>
-      <c r="W9" s="31" t="inlineStr"/>
-      <c r="X9" s="31" t="inlineStr"/>
-      <c r="Y9" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Технология изготовления съемных пластиночных  протезов        Горин А.А.                       </t>
-        </is>
-      </c>
-      <c r="Z9" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Генетика с основами медицинской генетики  Маклаков И.А. </t>
-        </is>
-      </c>
-      <c r="AA9" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сестринский уход за пациентами хирургического профиля        Байбакова А.Х. </t>
-        </is>
-      </c>
-      <c r="AB9" s="31" t="inlineStr"/>
-      <c r="AC9" s="31" t="inlineStr"/>
-      <c r="AD9" s="31" t="inlineStr">
-        <is>
-          <t>Технология коррекции тела     Березовикова А.В.</t>
-        </is>
-      </c>
-      <c r="AE9" s="31" t="inlineStr">
-        <is>
-          <t>Технология косметических услуг                       Джокич Э.А.</t>
-        </is>
-      </c>
-      <c r="AF9" s="31" t="inlineStr">
-        <is>
-          <t>Физическая культура                    Ритор Л.М.</t>
-        </is>
-      </c>
-      <c r="AG9" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Выполнение работ по профессии "Маникюрша"  Алексеенко Е.М.  </t>
-        </is>
-      </c>
-      <c r="AH9" s="1" t="inlineStr"/>
+      <c r="AG9" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Выполнение работ по профессии "Педикюрша"  Алексеенко Е.М.  </t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="99.95" customHeight="1">
-      <c r="A10" s="24" t="n"/>
-      <c r="B10" s="25" t="n">
+      <c r="A10" s="26" t="n"/>
+      <c r="B10" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="26" t="n"/>
-      <c r="D10" s="26" t="n"/>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="26" t="n"/>
-      <c r="G10" s="26" t="n"/>
-      <c r="H10" s="26" t="n"/>
-      <c r="I10" s="27" t="n"/>
-      <c r="J10" s="26" t="n"/>
-      <c r="K10" s="28" t="n"/>
-      <c r="L10" s="26" t="n"/>
-      <c r="M10" s="26" t="n"/>
-      <c r="N10" s="28" t="n"/>
-      <c r="O10" s="21" t="inlineStr"/>
-      <c r="P10" s="29" t="n"/>
-      <c r="Q10" s="30" t="n">
+      <c r="C10" s="28" t="n"/>
+      <c r="D10" s="28" t="n"/>
+      <c r="E10" s="28" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
+      <c r="H10" s="28" t="n"/>
+      <c r="I10" s="29" t="n"/>
+      <c r="J10" s="28" t="n"/>
+      <c r="K10" s="30" t="n"/>
+      <c r="L10" s="28" t="n"/>
+      <c r="M10" s="28" t="n"/>
+      <c r="N10" s="30" t="n"/>
+      <c r="O10" s="1" t="inlineStr"/>
+      <c r="P10" s="31" t="n"/>
+      <c r="Q10" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="R10" s="26" t="n"/>
-      <c r="S10" s="26" t="n"/>
-      <c r="T10" s="28" t="n"/>
-      <c r="U10" s="26" t="n"/>
-      <c r="V10" s="26" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
-      <c r="Y10" s="28" t="n"/>
-      <c r="Z10" s="26" t="n"/>
-      <c r="AA10" s="26" t="n"/>
-      <c r="AB10" s="26" t="n"/>
-      <c r="AC10" s="26" t="n"/>
-      <c r="AD10" s="26" t="n"/>
-      <c r="AE10" s="26" t="n"/>
-      <c r="AF10" s="26" t="n"/>
-      <c r="AG10" s="26" t="n"/>
-      <c r="AH10" s="1" t="inlineStr"/>
+      <c r="R10" s="28" t="n"/>
+      <c r="S10" s="28" t="n"/>
+      <c r="T10" s="30" t="n"/>
+      <c r="U10" s="28" t="n"/>
+      <c r="V10" s="28" t="n"/>
+      <c r="W10" s="28" t="n"/>
+      <c r="X10" s="28" t="n"/>
+      <c r="Y10" s="30" t="n"/>
+      <c r="Z10" s="28" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="28" t="n"/>
+      <c r="AD10" s="28" t="n"/>
+      <c r="AE10" s="28" t="n"/>
+      <c r="AF10" s="28" t="n"/>
+      <c r="AG10" s="28" t="n"/>
+      <c r="AH10" s="3" t="inlineStr"/>
     </row>
     <row r="11" ht="99.95" customHeight="1">
-      <c r="A11" s="24" t="n"/>
-      <c r="B11" s="25" t="n">
+      <c r="A11" s="26" t="n"/>
+      <c r="B11" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="31" t="inlineStr"/>
-      <c r="D11" s="31" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>Математика       Ширнин А.Г.</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Обществознание   Кожевников В.Е.</t>
         </is>
       </c>
-      <c r="E11" s="31" t="inlineStr">
-        <is>
-          <t>Математика       Ширнин А.Г.</t>
-        </is>
-      </c>
-      <c r="F11" s="31" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> История                 Козлов Д.В. </t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
         <is>
           <t>География      Зайцева Л.В.</t>
         </is>
       </c>
-      <c r="G11" s="31" t="inlineStr">
+      <c r="G11" s="33" t="inlineStr">
         <is>
           <t>Русский язык       Исаева Г.А.</t>
         </is>
       </c>
-      <c r="H11" s="31" t="inlineStr">
+      <c r="H11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve"> Информатика    Олимова Е.Н. </t>
         </is>
       </c>
-      <c r="I11" s="32" t="inlineStr">
+      <c r="I11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">Административное право         Баринов С.В. </t>
         </is>
       </c>
-      <c r="J11" s="31" t="inlineStr"/>
-      <c r="K11" s="34" t="inlineStr">
+      <c r="J11" s="33" t="inlineStr"/>
+      <c r="K11" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">Иностранный язык в профессиональной деятельности        Шарипов И.Н. </t>
         </is>
       </c>
-      <c r="L11" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Менеджмент       Систейкина Е.Е. </t>
-        </is>
-      </c>
-      <c r="M11" s="31" t="inlineStr">
+      <c r="L11" s="33" t="inlineStr">
+        <is>
+          <t>Моделирование логистических систем     Коломиец А.И.</t>
+        </is>
+      </c>
+      <c r="M11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Иностранный язык в профессиональной деятельности        Шарипов И.Н. </t>
         </is>
       </c>
-      <c r="N11" s="33" t="inlineStr"/>
-      <c r="O11" s="21" t="inlineStr"/>
-      <c r="P11" s="29" t="n"/>
-      <c r="Q11" s="30" t="n">
+      <c r="N11" s="35" t="inlineStr">
+        <is>
+          <t>Маркетинг  Систейкина Е.Е.</t>
+        </is>
+      </c>
+      <c r="O11" s="1" t="inlineStr"/>
+      <c r="P11" s="31" t="n"/>
+      <c r="Q11" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="R11" s="31" t="inlineStr"/>
-      <c r="S11" s="31" t="inlineStr"/>
-      <c r="T11" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Средства гигиены и профилактика стоматологических заболеваний полости рта  Станишевская Д.Н. </t>
-        </is>
-      </c>
-      <c r="U11" s="31" t="inlineStr"/>
-      <c r="V11" s="31" t="inlineStr"/>
-      <c r="W11" s="31" t="inlineStr"/>
-      <c r="X11" s="31" t="inlineStr">
+      <c r="R11" s="36" t="inlineStr"/>
+      <c r="S11" s="36" t="inlineStr"/>
+      <c r="T11" s="35" t="inlineStr">
+        <is>
+          <t>Средства гигиены и профилактика стоматологических заболеваний полости рта  Станишевская Д.Н.</t>
+        </is>
+      </c>
+      <c r="U11" s="33" t="inlineStr"/>
+      <c r="V11" s="33" t="inlineStr"/>
+      <c r="W11" s="33" t="inlineStr"/>
+      <c r="X11" s="33" t="inlineStr">
         <is>
           <t>Зуботехническое материаловедение с курсом охраны труда и техники безопасности   Горин А.А.</t>
         </is>
       </c>
-      <c r="Y11" s="33" t="inlineStr"/>
-      <c r="Z11" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> История России   Козлов Д.В. </t>
-        </is>
-      </c>
-      <c r="AA11" s="31" t="inlineStr">
+      <c r="Y11" s="35" t="inlineStr"/>
+      <c r="Z11" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Обеспечение безопасной окружающей среды в медицинской организации    Маклаков И.А. </t>
+        </is>
+      </c>
+      <c r="AA11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Сестринский уход и реабилитация пациентов терапевтического профиля разных возрастных групп Байбакова А.Х. </t>
         </is>
       </c>
-      <c r="AB11" s="31" t="inlineStr">
+      <c r="AB11" s="33" t="inlineStr">
         <is>
           <t>Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.</t>
         </is>
       </c>
-      <c r="AC11" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Анатомия и физиология человека          Маклаков И.А. </t>
-        </is>
-      </c>
-      <c r="AD11" s="32" t="inlineStr">
-        <is>
-          <t>Технология косметических услуг                       Джокич Э.А.</t>
-        </is>
-      </c>
-      <c r="AE11" s="31" t="inlineStr">
-        <is>
-          <t>Технология коррекции тела  Березовикова А.В.</t>
-        </is>
-      </c>
-      <c r="AF11" s="31" t="inlineStr">
+      <c r="AC11" s="33" t="inlineStr">
+        <is>
+          <t>Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.</t>
+        </is>
+      </c>
+      <c r="AD11" s="34" t="inlineStr"/>
+      <c r="AE11" s="33" t="inlineStr">
+        <is>
+          <t>Технология коррекции тела     Березовикова А.В.</t>
+        </is>
+      </c>
+      <c r="AF11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Выполнение работ по профессии "Маникюрша"  Алексеенко Е.М.  </t>
         </is>
       </c>
-      <c r="AG11" s="31" t="inlineStr"/>
-      <c r="AH11" s="1" t="inlineStr"/>
+      <c r="AG11" s="36" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="99.95" customHeight="1">
-      <c r="A12" s="24" t="n"/>
-      <c r="B12" s="25" t="n">
+      <c r="A12" s="26" t="n"/>
+      <c r="B12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="27" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="35" t="n"/>
-      <c r="L12" s="26" t="n"/>
-      <c r="M12" s="26" t="n"/>
-      <c r="N12" s="28" t="n"/>
-      <c r="O12" s="21" t="inlineStr"/>
-      <c r="P12" s="29" t="n"/>
-      <c r="Q12" s="30" t="n">
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+      <c r="H12" s="28" t="n"/>
+      <c r="I12" s="29" t="n"/>
+      <c r="J12" s="28" t="n"/>
+      <c r="K12" s="38" t="n"/>
+      <c r="L12" s="28" t="n"/>
+      <c r="M12" s="28" t="n"/>
+      <c r="N12" s="30" t="n"/>
+      <c r="O12" s="1" t="inlineStr"/>
+      <c r="P12" s="31" t="n"/>
+      <c r="Q12" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="R12" s="26" t="n"/>
-      <c r="S12" s="26" t="n"/>
-      <c r="T12" s="28" t="n"/>
-      <c r="U12" s="26" t="n"/>
-      <c r="V12" s="26" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
-      <c r="Y12" s="28" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="26" t="n"/>
-      <c r="AB12" s="26" t="n"/>
-      <c r="AC12" s="26" t="n"/>
-      <c r="AD12" s="27" t="n"/>
-      <c r="AE12" s="26" t="n"/>
-      <c r="AF12" s="26" t="n"/>
-      <c r="AG12" s="26" t="n"/>
-      <c r="AH12" s="1" t="inlineStr"/>
+      <c r="R12" s="28" t="n"/>
+      <c r="S12" s="28" t="n"/>
+      <c r="T12" s="30" t="n"/>
+      <c r="U12" s="28" t="n"/>
+      <c r="V12" s="28" t="n"/>
+      <c r="W12" s="28" t="n"/>
+      <c r="X12" s="28" t="n"/>
+      <c r="Y12" s="30" t="n"/>
+      <c r="Z12" s="28" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="28" t="n"/>
+      <c r="AD12" s="29" t="n"/>
+      <c r="AE12" s="28" t="n"/>
+      <c r="AF12" s="28" t="n"/>
+      <c r="AG12" s="28" t="n"/>
+      <c r="AH12" s="3" t="inlineStr"/>
     </row>
     <row r="13" ht="99.95" customHeight="1">
-      <c r="A13" s="24" t="n"/>
-      <c r="B13" s="25" t="n">
+      <c r="A13" s="26" t="n"/>
+      <c r="B13" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="C13" s="36" t="inlineStr"/>
-      <c r="D13" s="36" t="inlineStr">
+      <c r="C13" s="39" t="inlineStr">
+        <is>
+          <t>Обществознание   Кожевников В.Е.</t>
+        </is>
+      </c>
+      <c r="D13" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> Информатика    Олимова Е.Н.          2 подгруппа</t>
         </is>
       </c>
-      <c r="E13" s="36" t="inlineStr">
-        <is>
-          <t>Право     Кожевников В.Е.</t>
-        </is>
-      </c>
-      <c r="F13" s="36" t="inlineStr">
+      <c r="E13" s="39" t="inlineStr">
+        <is>
+          <t>Математика       Ширнин А.Г.</t>
+        </is>
+      </c>
+      <c r="F13" s="39" t="inlineStr">
         <is>
           <t>Русский язык       Исаева Г.А.</t>
         </is>
       </c>
-      <c r="G13" s="37" t="inlineStr">
+      <c r="G13" s="40" t="inlineStr">
         <is>
           <t>География      Зайцева Л.В.</t>
         </is>
       </c>
-      <c r="H13" s="31" t="inlineStr">
+      <c r="H13" s="33" t="inlineStr">
         <is>
           <t>География      Зайцева Л.В.</t>
         </is>
       </c>
-      <c r="I13" s="38" t="inlineStr">
+      <c r="I13" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Теория государства и права                   Баринов С.В. </t>
         </is>
       </c>
-      <c r="J13" s="36" t="inlineStr"/>
-      <c r="K13" s="39" t="inlineStr">
+      <c r="J13" s="39" t="inlineStr"/>
+      <c r="K13" s="42" t="inlineStr"/>
+      <c r="L13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Иностранный язык        Шарипов И.Н. </t>
+        </is>
+      </c>
+      <c r="M13" s="33" t="inlineStr"/>
+      <c r="N13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Иностранный язык        Шарипов И.Н. </t>
+        </is>
+      </c>
+      <c r="O13" s="1" t="inlineStr"/>
+      <c r="P13" s="31" t="n"/>
+      <c r="Q13" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" s="40" t="inlineStr"/>
+      <c r="S13" s="39" t="inlineStr"/>
+      <c r="T13" s="42" t="inlineStr">
+        <is>
+          <t>Организация трудовой деятельности и ведение медицинской документации  Станишевская Д.Н.</t>
+        </is>
+      </c>
+      <c r="U13" s="39" t="inlineStr"/>
+      <c r="V13" s="39" t="inlineStr"/>
+      <c r="W13" s="39" t="inlineStr"/>
+      <c r="X13" s="33" t="inlineStr">
+        <is>
+          <t>Технология изготовления съемных пластиночных  протезов        Горин А.А.</t>
+        </is>
+      </c>
+      <c r="Y13" s="42" t="inlineStr"/>
+      <c r="Z13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Санитария и гигиена в деятельности медицинской сестры                Маклаков И.А. </t>
+        </is>
+      </c>
+      <c r="AA13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сестринский уход и реабилитация пациентов терапевтического профиля разных возрастных групп Байбакова А.Х. </t>
+        </is>
+      </c>
+      <c r="AB13" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> История России   Козлов Д.В. </t>
         </is>
       </c>
-      <c r="L13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Иностранный язык            Шарипов И.Н. </t>
-        </is>
-      </c>
-      <c r="M13" s="31" t="inlineStr">
+      <c r="AC13" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> История России   Козлов Д.В. </t>
         </is>
       </c>
-      <c r="N13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Иностранный язык            Шарипов И.Н. </t>
-        </is>
-      </c>
-      <c r="O13" s="21" t="inlineStr"/>
-      <c r="P13" s="29" t="n"/>
-      <c r="Q13" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="R13" s="37" t="inlineStr"/>
-      <c r="S13" s="36" t="inlineStr"/>
-      <c r="T13" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Средства гигиены и профилактика стоматологических заболеваний полости рта  Станишевская Д.Н. </t>
-        </is>
-      </c>
-      <c r="U13" s="36" t="inlineStr"/>
-      <c r="V13" s="36" t="inlineStr"/>
-      <c r="W13" s="36" t="inlineStr"/>
-      <c r="X13" s="31" t="inlineStr">
-        <is>
-          <t>Технология изготовления съемных пластиночных  протезов        Горин А.А.</t>
-        </is>
-      </c>
-      <c r="Y13" s="39" t="inlineStr"/>
-      <c r="Z13" s="36" t="inlineStr"/>
-      <c r="AA13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сестринский уход и реабилитация пациентов терапевтического профиля разных возрастных групп Байбакова А.Х. </t>
-        </is>
-      </c>
-      <c r="AB13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Анатомия и физиология человека          Маклаков И.А. </t>
-        </is>
-      </c>
-      <c r="AC13" s="38" t="inlineStr">
-        <is>
-          <t>Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.</t>
-        </is>
-      </c>
-      <c r="AD13" s="32" t="inlineStr">
-        <is>
-          <t>Технология косметических услуг                       Джокич Э.А.</t>
-        </is>
-      </c>
-      <c r="AE13" s="36" t="inlineStr">
-        <is>
-          <t>Технология коррекции тела Березовикова А.В.</t>
-        </is>
-      </c>
-      <c r="AF13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Выполнение работ по профессии "Маникюрша"  Алексеенко Е.М.  </t>
-        </is>
-      </c>
-      <c r="AG13" s="36" t="inlineStr"/>
-      <c r="AH13" s="1" t="inlineStr"/>
+      <c r="AD13" s="34" t="inlineStr"/>
+      <c r="AE13" s="39" t="inlineStr">
+        <is>
+          <t>Технология коррекции тела     Березовикова А.В.</t>
+        </is>
+      </c>
+      <c r="AF13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Выполнение работ по профессии "Педикюрша"  Алексеенко Е.М.  </t>
+        </is>
+      </c>
+      <c r="AG13" s="43" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
     </row>
     <row r="14" ht="99.95" customHeight="1" thickBot="1">
-      <c r="A14" s="26" t="n"/>
-      <c r="B14" s="40" t="n">
+      <c r="A14" s="28" t="n"/>
+      <c r="B14" s="44" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="41" t="n"/>
-      <c r="D14" s="41" t="n"/>
-      <c r="E14" s="41" t="n"/>
-      <c r="F14" s="41" t="n"/>
-      <c r="G14" s="24" t="n"/>
-      <c r="H14" s="26" t="n"/>
-      <c r="I14" s="42" t="n"/>
-      <c r="J14" s="41" t="n"/>
-      <c r="K14" s="43" t="n"/>
-      <c r="L14" s="41" t="n"/>
-      <c r="M14" s="26" t="n"/>
-      <c r="N14" s="41" t="n"/>
-      <c r="O14" s="21" t="inlineStr"/>
-      <c r="P14" s="44" t="n"/>
-      <c r="Q14" s="45" t="n">
+      <c r="C14" s="45" t="n"/>
+      <c r="D14" s="45" t="n"/>
+      <c r="E14" s="45" t="n"/>
+      <c r="F14" s="45" t="n"/>
+      <c r="G14" s="26" t="n"/>
+      <c r="H14" s="28" t="n"/>
+      <c r="I14" s="46" t="n"/>
+      <c r="J14" s="45" t="n"/>
+      <c r="K14" s="47" t="n"/>
+      <c r="L14" s="45" t="n"/>
+      <c r="M14" s="28" t="n"/>
+      <c r="N14" s="45" t="n"/>
+      <c r="O14" s="1" t="inlineStr"/>
+      <c r="P14" s="48" t="n"/>
+      <c r="Q14" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="R14" s="24" t="n"/>
-      <c r="S14" s="41" t="n"/>
-      <c r="T14" s="43" t="n"/>
-      <c r="U14" s="41" t="n"/>
-      <c r="V14" s="41" t="n"/>
-      <c r="W14" s="41" t="n"/>
-      <c r="X14" s="26" t="n"/>
-      <c r="Y14" s="43" t="n"/>
-      <c r="Z14" s="41" t="n"/>
-      <c r="AA14" s="41" t="n"/>
-      <c r="AB14" s="41" t="n"/>
-      <c r="AC14" s="42" t="n"/>
-      <c r="AD14" s="27" t="n"/>
-      <c r="AE14" s="41" t="n"/>
-      <c r="AF14" s="41" t="n"/>
-      <c r="AG14" s="41" t="n"/>
-      <c r="AH14" s="1" t="inlineStr"/>
+      <c r="R14" s="26" t="n"/>
+      <c r="S14" s="45" t="n"/>
+      <c r="T14" s="47" t="n"/>
+      <c r="U14" s="45" t="n"/>
+      <c r="V14" s="45" t="n"/>
+      <c r="W14" s="45" t="n"/>
+      <c r="X14" s="28" t="n"/>
+      <c r="Y14" s="47" t="n"/>
+      <c r="Z14" s="45" t="n"/>
+      <c r="AA14" s="45" t="n"/>
+      <c r="AB14" s="45" t="n"/>
+      <c r="AC14" s="45" t="n"/>
+      <c r="AD14" s="29" t="n"/>
+      <c r="AE14" s="45" t="n"/>
+      <c r="AF14" s="45" t="n"/>
+      <c r="AG14" s="45" t="n"/>
+      <c r="AH14" s="3" t="inlineStr"/>
     </row>
     <row r="15" ht="99.95" customHeight="1">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">вторник </t>
         </is>
       </c>
-      <c r="B15" s="47" t="n">
+      <c r="B15" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>Обществознание   Кожевников В.Е.</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr"/>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Биология              Морозова Е.Н. </t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>Математика       Ширнин А.Г.</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr"/>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Биология              Морозова Е.Н. </t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr"/>
-      <c r="H15" s="20" t="inlineStr"/>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>ВПО           Писарева Н.А.</t>
-        </is>
-      </c>
-      <c r="J15" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">БЖД         Ходаковский В.В. </t>
-        </is>
-      </c>
-      <c r="K15" s="18" t="inlineStr">
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>Право     Кожевников В.Е.</t>
+        </is>
+      </c>
+      <c r="H15" s="25" t="inlineStr"/>
+      <c r="I15" s="19" t="inlineStr">
+        <is>
+          <t>Гражданское  право                          Лебедева М.Л.</t>
+        </is>
+      </c>
+      <c r="J15" s="52" t="inlineStr">
+        <is>
+          <t>БЖД                                    Ходаковский В.В.</t>
+        </is>
+      </c>
+      <c r="K15" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Основы логистической деятельности      Коломиец А.И. </t>
         </is>
       </c>
-      <c r="L15" s="48" t="inlineStr"/>
-      <c r="M15" s="48" t="inlineStr">
+      <c r="L15" s="53" t="inlineStr"/>
+      <c r="M15" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">Эксплуатация торгово - технологического оборудования и охрана труда </t>
         </is>
       </c>
-      <c r="N15" s="48" t="inlineStr">
+      <c r="N15" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">Финансы, налоги и налогообложение Иванов В.В. </t>
         </is>
       </c>
-      <c r="O15" s="21" t="inlineStr"/>
-      <c r="P15" s="22" t="inlineStr">
+      <c r="O15" s="1" t="inlineStr"/>
+      <c r="P15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">вторник </t>
         </is>
       </c>
-      <c r="Q15" s="23" t="n">
+      <c r="Q15" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="R15" s="18" t="inlineStr"/>
-      <c r="S15" s="48" t="inlineStr"/>
-      <c r="T15" s="18" t="inlineStr">
+      <c r="R15" s="19" t="inlineStr"/>
+      <c r="S15" s="54" t="inlineStr"/>
+      <c r="T15" s="21" t="inlineStr"/>
+      <c r="U15" s="19" t="inlineStr">
+        <is>
+          <t>Гигиена полости рта                Мхитарян Л.С.</t>
+        </is>
+      </c>
+      <c r="V15" s="19" t="inlineStr">
+        <is>
+          <t>Гигиена полости рта                Мхитарян Л.С.</t>
+        </is>
+      </c>
+      <c r="W15" s="19" t="inlineStr"/>
+      <c r="X15" s="52" t="inlineStr">
+        <is>
+          <t>Анатомия и физиология человека с курсом биомеханики зубочелюстной системы                    Горин А.А.</t>
+        </is>
+      </c>
+      <c r="Y15" s="21" t="inlineStr"/>
+      <c r="Z15" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> История России   Козлов Д.В. </t>
+        </is>
+      </c>
+      <c r="AA15" s="19" t="inlineStr">
         <is>
           <t>Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.</t>
         </is>
       </c>
-      <c r="U15" s="48" t="inlineStr">
-        <is>
-          <t>Гигиена полости рта                Мхитарян Л.С.</t>
-        </is>
-      </c>
-      <c r="V15" s="48" t="inlineStr">
-        <is>
-          <t>Гигиена полости рта                Мхитарян Л.С.</t>
-        </is>
-      </c>
-      <c r="W15" s="20" t="inlineStr"/>
-      <c r="X15" s="48" t="inlineStr"/>
-      <c r="Y15" s="18" t="inlineStr">
-        <is>
-          <t>Технология изготовления съемных пластиночных  протезов        Горин А.А.</t>
-        </is>
-      </c>
-      <c r="Z15" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> История России   Козлов Д.В. </t>
-        </is>
-      </c>
-      <c r="AA15" s="18" t="inlineStr">
+      <c r="AB15" s="19" t="inlineStr"/>
+      <c r="AC15" s="19" t="inlineStr"/>
+      <c r="AD15" s="52" t="inlineStr">
         <is>
           <t>Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.</t>
         </is>
       </c>
-      <c r="AB15" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Технология маникюра Алексеенко Е.М.  </t>
-        </is>
-      </c>
-      <c r="AC15" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Анатомия и физиология человека          Маклаков И.А. </t>
-        </is>
-      </c>
-      <c r="AD15" s="48" t="inlineStr">
-        <is>
-          <t>Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.</t>
-        </is>
-      </c>
-      <c r="AE15" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Технология визажа Ермолаева И.В.                                               </t>
-        </is>
-      </c>
-      <c r="AF15" s="48" t="inlineStr">
-        <is>
-          <t>Технология косметических услуг                       Джокич Э.А.</t>
-        </is>
-      </c>
-      <c r="AG15" s="48" t="inlineStr"/>
-      <c r="AH15" s="1" t="inlineStr"/>
+      <c r="AE15" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Технология визажа  Ермолаева И.В.                        </t>
+        </is>
+      </c>
+      <c r="AF15" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Выполнение работ по профессии "Маникюрша"  Алексеенко Е.М.  </t>
+        </is>
+      </c>
+      <c r="AG15" s="52" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
     </row>
     <row r="16" ht="99.95" customHeight="1">
-      <c r="A16" s="24" t="n"/>
-      <c r="B16" s="25" t="n">
+      <c r="A16" s="26" t="n"/>
+      <c r="B16" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="26" t="n"/>
-      <c r="D16" s="26" t="n"/>
-      <c r="E16" s="26" t="n"/>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="26" t="n"/>
-      <c r="H16" s="28" t="n"/>
-      <c r="I16" s="26" t="n"/>
-      <c r="J16" s="26" t="n"/>
-      <c r="K16" s="26" t="n"/>
-      <c r="L16" s="26" t="n"/>
-      <c r="M16" s="26" t="n"/>
-      <c r="N16" s="26" t="n"/>
-      <c r="O16" s="21" t="inlineStr"/>
-      <c r="P16" s="29" t="n"/>
-      <c r="Q16" s="30" t="n">
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="29" t="n"/>
+      <c r="G16" s="28" t="n"/>
+      <c r="H16" s="30" t="n"/>
+      <c r="I16" s="28" t="n"/>
+      <c r="J16" s="28" t="n"/>
+      <c r="K16" s="28" t="n"/>
+      <c r="L16" s="28" t="n"/>
+      <c r="M16" s="28" t="n"/>
+      <c r="N16" s="28" t="n"/>
+      <c r="O16" s="1" t="inlineStr"/>
+      <c r="P16" s="31" t="n"/>
+      <c r="Q16" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="R16" s="26" t="n"/>
-      <c r="S16" s="26" t="n"/>
-      <c r="T16" s="26" t="n"/>
-      <c r="U16" s="26" t="n"/>
-      <c r="V16" s="26" t="n"/>
+      <c r="R16" s="28" t="n"/>
+      <c r="S16" s="28" t="n"/>
+      <c r="T16" s="28" t="n"/>
+      <c r="U16" s="28" t="n"/>
+      <c r="V16" s="28" t="n"/>
       <c r="W16" s="28" t="n"/>
-      <c r="X16" s="26" t="n"/>
-      <c r="Y16" s="26" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="26" t="n"/>
-      <c r="AB16" s="26" t="n"/>
-      <c r="AC16" s="26" t="n"/>
-      <c r="AD16" s="26" t="n"/>
-      <c r="AE16" s="26" t="n"/>
-      <c r="AF16" s="26" t="n"/>
-      <c r="AG16" s="26" t="n"/>
-      <c r="AH16" s="1" t="inlineStr"/>
+      <c r="X16" s="28" t="n"/>
+      <c r="Y16" s="28" t="n"/>
+      <c r="Z16" s="28" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="28" t="n"/>
+      <c r="AD16" s="28" t="n"/>
+      <c r="AE16" s="28" t="n"/>
+      <c r="AF16" s="28" t="n"/>
+      <c r="AG16" s="28" t="n"/>
+      <c r="AH16" s="3" t="inlineStr"/>
     </row>
     <row r="17" ht="99.95" customHeight="1">
-      <c r="A17" s="24" t="n"/>
-      <c r="B17" s="25" t="n">
+      <c r="A17" s="26" t="n"/>
+      <c r="B17" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="31" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Биология              Морозова Е.Н. </t>
         </is>
       </c>
-      <c r="D17" s="31" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Иностранный язык            Шарипов И.Н. </t>
+        </is>
+      </c>
+      <c r="E17" s="36" t="inlineStr"/>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>Математика       Ширнин А.Г.</t>
+        </is>
+      </c>
+      <c r="G17" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Основы безопасности и защиты Родины   Иванов В.В.  </t>
         </is>
       </c>
-      <c r="E17" s="31" t="inlineStr"/>
-      <c r="F17" s="32" t="inlineStr">
-        <is>
-          <t>Математика       Ширнин А.Г.</t>
-        </is>
-      </c>
-      <c r="G17" s="31" t="inlineStr"/>
-      <c r="H17" s="33" t="inlineStr"/>
-      <c r="I17" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Документационное  обеспечение управления       Иванова Ж.В. </t>
-        </is>
-      </c>
-      <c r="J17" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Иностранный язык            Шарипов И.Н. </t>
-        </is>
-      </c>
-      <c r="K17" s="31" t="inlineStr">
+      <c r="H17" s="35" t="inlineStr"/>
+      <c r="I17" s="33" t="inlineStr">
+        <is>
+          <t>БЖД                                    Ходаковский В.В.</t>
+        </is>
+      </c>
+      <c r="J17" s="55" t="inlineStr">
+        <is>
+          <t>Право социального обеспечения                             Лебедева М.Л.</t>
+        </is>
+      </c>
+      <c r="K17" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Основы логистической деятельности      Коломиец А.И. </t>
         </is>
       </c>
-      <c r="L17" s="31" t="inlineStr"/>
-      <c r="M17" s="31" t="inlineStr">
+      <c r="L17" s="36" t="inlineStr"/>
+      <c r="M17" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Эксплуатация торгово - технологического оборудования и охрана труда </t>
         </is>
       </c>
-      <c r="N17" s="31" t="inlineStr">
+      <c r="N17" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Информационные технологии в профессиональной деятельности     Олимова Е.Н. </t>
         </is>
       </c>
-      <c r="O17" s="21" t="inlineStr"/>
-      <c r="P17" s="29" t="n"/>
-      <c r="Q17" s="30" t="n">
+      <c r="O17" s="1" t="inlineStr"/>
+      <c r="P17" s="31" t="n"/>
+      <c r="Q17" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="R17" s="31" t="inlineStr"/>
-      <c r="S17" s="31" t="inlineStr"/>
-      <c r="T17" s="31" t="inlineStr">
+      <c r="R17" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> История России   Козлов Д.В. </t>
+        </is>
+      </c>
+      <c r="S17" s="56" t="inlineStr"/>
+      <c r="T17" s="36" t="inlineStr"/>
+      <c r="U17" s="33" t="inlineStr">
+        <is>
+          <t>Гигиена полости рта                Мхитарян Л.С.</t>
+        </is>
+      </c>
+      <c r="V17" s="33" t="inlineStr">
+        <is>
+          <t>Гигиена полости рта                Мхитарян Л.С.</t>
+        </is>
+      </c>
+      <c r="W17" s="33" t="inlineStr"/>
+      <c r="X17" s="33" t="inlineStr">
+        <is>
+          <t>Технология изготовления съемных пластиночных  протезов        Горин А.А.</t>
+        </is>
+      </c>
+      <c r="Y17" s="36" t="inlineStr"/>
+      <c r="Z17" s="33" t="inlineStr">
+        <is>
+          <t>Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.</t>
+        </is>
+      </c>
+      <c r="AA17" s="33" t="inlineStr">
         <is>
           <t>Правовое обеспечение профессиональной деятельности     Кожевников В.Е.</t>
         </is>
       </c>
-      <c r="U17" s="31" t="inlineStr">
-        <is>
-          <t>Гигиена полости рта                Мхитарян Л.С.</t>
-        </is>
-      </c>
-      <c r="V17" s="31" t="inlineStr">
-        <is>
-          <t>Гигиена полости рта                Мхитарян Л.С.</t>
-        </is>
-      </c>
-      <c r="W17" s="33" t="inlineStr"/>
-      <c r="X17" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> История России   Козлов Д.В. </t>
-        </is>
-      </c>
-      <c r="Y17" s="31" t="inlineStr">
-        <is>
-          <t>Технология изготовления съемных пластиночных  протезов        Горин А.А.</t>
-        </is>
-      </c>
-      <c r="Z17" s="31" t="inlineStr">
-        <is>
-          <t>Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.</t>
-        </is>
-      </c>
-      <c r="AA17" s="31" t="inlineStr">
-        <is>
-          <t>Правовое обеспечение профессиональной деятельности     Кожевников В.Е.</t>
-        </is>
-      </c>
-      <c r="AB17" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Анатомия и физиология человека          Маклаков И.А. </t>
-        </is>
-      </c>
-      <c r="AC17" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Технология маникюра Алексеенко Е.М.  </t>
-        </is>
-      </c>
-      <c r="AD17" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Выполнение работ по профессии "Педикюрша"  Алексеенко Е.М.  </t>
-        </is>
-      </c>
-      <c r="AE17" s="31" t="inlineStr">
+      <c r="AB17" s="33" t="inlineStr"/>
+      <c r="AC17" s="33" t="inlineStr"/>
+      <c r="AD17" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Технология визажа Ермолаева И.В.                                               </t>
         </is>
       </c>
-      <c r="AF17" s="31" t="inlineStr">
-        <is>
-          <t>Технология косметических услуг                       Джокич Э.А.</t>
-        </is>
-      </c>
-      <c r="AG17" s="31" t="inlineStr"/>
-      <c r="AH17" s="1" t="inlineStr"/>
+      <c r="AE17" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Экологические основы природопользования                                      Иванова Ж.В.   </t>
+        </is>
+      </c>
+      <c r="AF17" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Выполнение работ по профессии "Маникюрша"  Алексеенко Е.М.  </t>
+        </is>
+      </c>
+      <c r="AG17" s="33" t="inlineStr"/>
+      <c r="AH17" s="3" t="inlineStr"/>
     </row>
     <row r="18" ht="99.95" customHeight="1">
-      <c r="A18" s="24" t="n"/>
-      <c r="B18" s="25" t="n">
+      <c r="A18" s="26" t="n"/>
+      <c r="B18" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="26" t="n"/>
-      <c r="D18" s="26" t="n"/>
-      <c r="E18" s="26" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="26" t="n"/>
-      <c r="H18" s="28" t="n"/>
-      <c r="I18" s="26" t="n"/>
-      <c r="J18" s="26" t="n"/>
-      <c r="K18" s="26" t="n"/>
-      <c r="L18" s="26" t="n"/>
-      <c r="M18" s="26" t="n"/>
-      <c r="N18" s="26" t="n"/>
-      <c r="O18" s="21" t="inlineStr"/>
-      <c r="P18" s="29" t="n"/>
-      <c r="Q18" s="30" t="n">
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="28" t="n"/>
+      <c r="E18" s="28" t="n"/>
+      <c r="F18" s="29" t="n"/>
+      <c r="G18" s="28" t="n"/>
+      <c r="H18" s="30" t="n"/>
+      <c r="I18" s="28" t="n"/>
+      <c r="J18" s="28" t="n"/>
+      <c r="K18" s="28" t="n"/>
+      <c r="L18" s="28" t="n"/>
+      <c r="M18" s="28" t="n"/>
+      <c r="N18" s="28" t="n"/>
+      <c r="O18" s="1" t="inlineStr"/>
+      <c r="P18" s="31" t="n"/>
+      <c r="Q18" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="R18" s="26" t="n"/>
-      <c r="S18" s="26" t="n"/>
-      <c r="T18" s="26" t="n"/>
-      <c r="U18" s="26" t="n"/>
-      <c r="V18" s="26" t="n"/>
+      <c r="R18" s="28" t="n"/>
+      <c r="S18" s="28" t="n"/>
+      <c r="T18" s="28" t="n"/>
+      <c r="U18" s="28" t="n"/>
+      <c r="V18" s="28" t="n"/>
       <c r="W18" s="28" t="n"/>
-      <c r="X18" s="26" t="n"/>
-      <c r="Y18" s="26" t="n"/>
-      <c r="Z18" s="26" t="n"/>
-      <c r="AA18" s="26" t="n"/>
-      <c r="AB18" s="26" t="n"/>
-      <c r="AC18" s="26" t="n"/>
-      <c r="AD18" s="26" t="n"/>
-      <c r="AE18" s="26" t="n"/>
-      <c r="AF18" s="26" t="n"/>
-      <c r="AG18" s="26" t="n"/>
-      <c r="AH18" s="1" t="inlineStr"/>
+      <c r="X18" s="28" t="n"/>
+      <c r="Y18" s="28" t="n"/>
+      <c r="Z18" s="28" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="28" t="n"/>
+      <c r="AD18" s="28" t="n"/>
+      <c r="AE18" s="28" t="n"/>
+      <c r="AF18" s="28" t="n"/>
+      <c r="AG18" s="28" t="n"/>
+      <c r="AH18" s="3" t="inlineStr"/>
     </row>
     <row r="19" ht="99.95" customHeight="1">
-      <c r="A19" s="24" t="n"/>
-      <c r="B19" s="25" t="n">
+      <c r="A19" s="26" t="n"/>
+      <c r="B19" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="C19" s="31" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>Математика       Ширнин А.Г.</t>
         </is>
       </c>
-      <c r="D19" s="31" t="inlineStr"/>
-      <c r="E19" s="31" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Основы безопасности и защиты Родины   Иванов В.В.  </t>
+        </is>
+      </c>
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Иностранный язык            Шарипов И.Н. </t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Основы безопасности и защиты Родины   Иванов В.В.  </t>
-        </is>
-      </c>
-      <c r="G19" s="31" t="inlineStr">
+      <c r="F19" s="57" t="inlineStr"/>
+      <c r="G19" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Биология              Морозова Е.Н. </t>
         </is>
       </c>
-      <c r="H19" s="33" t="inlineStr">
+      <c r="H19" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Биология              Морозова Е.Н. </t>
         </is>
       </c>
-      <c r="I19" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Документационное  обеспечение управления       Иванова Ж.В. </t>
-        </is>
-      </c>
-      <c r="J19" s="31" t="inlineStr"/>
-      <c r="K19" s="31" t="inlineStr">
+      <c r="I19" s="33" t="inlineStr"/>
+      <c r="J19" s="33" t="inlineStr">
+        <is>
+          <t>Числитель             Жилищное право                          Лебедева М.Л.</t>
+        </is>
+      </c>
+      <c r="K19" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Информационное обеспечение логистических процессов        Олимова Е.Н. </t>
         </is>
       </c>
-      <c r="L19" s="31" t="inlineStr">
+      <c r="L19" s="33" t="inlineStr">
         <is>
           <t>Моделирование логистических систем     Коломиец А.И.</t>
         </is>
       </c>
-      <c r="M19" s="31" t="inlineStr">
+      <c r="M19" s="33" t="inlineStr">
         <is>
           <t>Правовое обеспечение профессиональной деятельности     Кожевников В.Е.</t>
         </is>
       </c>
-      <c r="N19" s="31" t="inlineStr">
+      <c r="N19" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Товароведение продовольственных и непродовольственных товаров   </t>
         </is>
       </c>
-      <c r="O19" s="21" t="inlineStr"/>
-      <c r="P19" s="29" t="n"/>
-      <c r="Q19" s="30" t="n">
+      <c r="O19" s="1" t="inlineStr"/>
+      <c r="P19" s="31" t="n"/>
+      <c r="Q19" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="31" t="inlineStr">
+      <c r="R19" s="33" t="inlineStr">
         <is>
           <t>Основы латинского языка с медицинской терминологией       Дремлюгина Л.А.</t>
         </is>
       </c>
-      <c r="S19" s="31" t="inlineStr">
+      <c r="S19" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve"> История России   Козлов Д.В. </t>
         </is>
       </c>
-      <c r="T19" s="31" t="inlineStr"/>
-      <c r="U19" s="31" t="inlineStr"/>
-      <c r="V19" s="31" t="inlineStr"/>
+      <c r="T19" s="36" t="inlineStr"/>
+      <c r="U19" s="33" t="inlineStr"/>
+      <c r="V19" s="33" t="inlineStr"/>
       <c r="W19" s="33" t="inlineStr">
         <is>
           <t>Оказание медицинской помощи в экстренной форме  Мхитарян Л.С.</t>
         </is>
       </c>
-      <c r="X19" s="31" t="inlineStr">
+      <c r="X19" s="33" t="inlineStr"/>
+      <c r="Y19" s="33" t="inlineStr">
         <is>
           <t>Технология изготовления съемных пластиночных  протезов        Горин А.А.</t>
         </is>
       </c>
-      <c r="Y19" s="31" t="inlineStr"/>
-      <c r="Z19" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Обеспечение безопасной окружающей среды в медицинской организации    Маклаков И.А. </t>
-        </is>
-      </c>
-      <c r="AA19" s="31" t="inlineStr"/>
-      <c r="AB19" s="31" t="inlineStr"/>
-      <c r="AC19" s="32" t="inlineStr"/>
-      <c r="AD19" s="31" t="inlineStr">
+      <c r="Z19" s="33" t="inlineStr"/>
+      <c r="AA19" s="33" t="inlineStr"/>
+      <c r="AB19" s="33" t="inlineStr"/>
+      <c r="AC19" s="34" t="inlineStr"/>
+      <c r="AD19" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Технология визажа Ермолаева И.В.                                               </t>
         </is>
       </c>
-      <c r="AE19" s="31" t="inlineStr">
+      <c r="AE19" s="33" t="inlineStr"/>
+      <c r="AF19" s="33" t="inlineStr"/>
+      <c r="AG19" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Выполнение работ по профессии "Маникюрша"  Алексеенко Е.М.  </t>
         </is>
       </c>
-      <c r="AF19" s="31" t="inlineStr"/>
-      <c r="AG19" s="31" t="inlineStr">
-        <is>
-          <t>Технология косметических услуг                       Джокич Э.А.</t>
-        </is>
-      </c>
-      <c r="AH19" s="1" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
     </row>
     <row r="20" ht="99.95" customHeight="1">
-      <c r="A20" s="24" t="n"/>
-      <c r="B20" s="25" t="n">
+      <c r="A20" s="26" t="n"/>
+      <c r="B20" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="C20" s="26" t="n"/>
-      <c r="D20" s="26" t="n"/>
-      <c r="E20" s="26" t="n"/>
-      <c r="F20" s="26" t="n"/>
-      <c r="G20" s="26" t="n"/>
-      <c r="H20" s="28" t="n"/>
-      <c r="I20" s="26" t="n"/>
-      <c r="J20" s="26" t="n"/>
-      <c r="K20" s="26" t="n"/>
-      <c r="L20" s="26" t="n"/>
-      <c r="M20" s="26" t="n"/>
-      <c r="N20" s="26" t="n"/>
-      <c r="O20" s="21" t="inlineStr"/>
-      <c r="P20" s="29" t="n"/>
-      <c r="Q20" s="30" t="n">
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="28" t="n"/>
+      <c r="E20" s="28" t="n"/>
+      <c r="F20" s="29" t="n"/>
+      <c r="G20" s="28" t="n"/>
+      <c r="H20" s="30" t="n"/>
+      <c r="I20" s="28" t="n"/>
+      <c r="J20" s="33" t="inlineStr"/>
+      <c r="K20" s="28" t="n"/>
+      <c r="L20" s="28" t="n"/>
+      <c r="M20" s="28" t="n"/>
+      <c r="N20" s="28" t="n"/>
+      <c r="O20" s="1" t="inlineStr"/>
+      <c r="P20" s="31" t="n"/>
+      <c r="Q20" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="R20" s="26" t="n"/>
-      <c r="S20" s="26" t="n"/>
-      <c r="T20" s="26" t="n"/>
-      <c r="U20" s="26" t="n"/>
-      <c r="V20" s="26" t="n"/>
+      <c r="R20" s="28" t="n"/>
+      <c r="S20" s="28" t="n"/>
+      <c r="T20" s="28" t="n"/>
+      <c r="U20" s="28" t="n"/>
+      <c r="V20" s="28" t="n"/>
       <c r="W20" s="28" t="n"/>
-      <c r="X20" s="26" t="n"/>
-      <c r="Y20" s="26" t="n"/>
-      <c r="Z20" s="26" t="n"/>
-      <c r="AA20" s="26" t="n"/>
-      <c r="AB20" s="26" t="n"/>
-      <c r="AC20" s="27" t="n"/>
-      <c r="AD20" s="26" t="n"/>
-      <c r="AE20" s="26" t="n"/>
-      <c r="AF20" s="26" t="n"/>
-      <c r="AG20" s="26" t="n"/>
-      <c r="AH20" s="1" t="inlineStr"/>
+      <c r="X20" s="28" t="n"/>
+      <c r="Y20" s="28" t="n"/>
+      <c r="Z20" s="28" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="29" t="n"/>
+      <c r="AD20" s="28" t="n"/>
+      <c r="AE20" s="28" t="n"/>
+      <c r="AF20" s="28" t="n"/>
+      <c r="AG20" s="28" t="n"/>
+      <c r="AH20" s="3" t="inlineStr"/>
     </row>
     <row r="21" ht="99.95" customHeight="1">
-      <c r="A21" s="24" t="n"/>
-      <c r="B21" s="25" t="n">
+      <c r="A21" s="26" t="n"/>
+      <c r="B21" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="C21" s="36" t="inlineStr">
+      <c r="C21" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Иностранный язык            Шарипов И.Н. </t>
         </is>
       </c>
-      <c r="D21" s="36" t="inlineStr"/>
-      <c r="E21" s="36" t="inlineStr">
+      <c r="D21" s="39" t="inlineStr">
+        <is>
+          <t>Математика       Ширнин А.Г.</t>
+        </is>
+      </c>
+      <c r="E21" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Биология              Морозова Е.Н. </t>
         </is>
       </c>
-      <c r="F21" s="38" t="inlineStr"/>
-      <c r="G21" s="31" t="inlineStr">
+      <c r="F21" s="58" t="inlineStr"/>
+      <c r="G21" s="33" t="inlineStr">
         <is>
           <t>Обществознание   Кожевников В.Е.</t>
         </is>
       </c>
-      <c r="H21" s="39" t="inlineStr">
+      <c r="H21" s="42" t="inlineStr">
         <is>
           <t>Обществознание   Кожевников В.Е.</t>
         </is>
       </c>
-      <c r="I21" s="36" t="inlineStr"/>
-      <c r="J21" s="50" t="inlineStr"/>
-      <c r="K21" s="36" t="inlineStr"/>
-      <c r="L21" s="37" t="inlineStr">
+      <c r="I21" s="39" t="inlineStr"/>
+      <c r="J21" s="59" t="inlineStr">
+        <is>
+          <t>Гражданский процесс                           Лебедева М.Л.</t>
+        </is>
+      </c>
+      <c r="K21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> История России   Козлов Д.В. </t>
+        </is>
+      </c>
+      <c r="L21" s="39" t="inlineStr">
         <is>
           <t>Распределительная логистика    Коломиец А.И.</t>
         </is>
       </c>
-      <c r="M21" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Основы предпринимательства                          Иванов В.В.  </t>
-        </is>
-      </c>
-      <c r="N21" s="36" t="inlineStr">
+      <c r="M21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> История России   Козлов Д.В. </t>
+        </is>
+      </c>
+      <c r="N21" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Товароведение продовольственных и непродовольственных товаров   </t>
         </is>
       </c>
-      <c r="O21" s="21" t="inlineStr"/>
-      <c r="P21" s="29" t="n"/>
-      <c r="Q21" s="30" t="n">
+      <c r="O21" s="1" t="inlineStr"/>
+      <c r="P21" s="31" t="n"/>
+      <c r="Q21" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="R21" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> История России   Козлов Д.В. </t>
-        </is>
-      </c>
-      <c r="S21" s="36" t="inlineStr">
+      <c r="R21" s="39" t="inlineStr"/>
+      <c r="S21" s="39" t="inlineStr">
         <is>
           <t>Основы латинского языка с медицинской терминологией       Дремлюгина Л.А.</t>
         </is>
       </c>
-      <c r="T21" s="36" t="inlineStr"/>
-      <c r="U21" s="36" t="inlineStr"/>
-      <c r="V21" s="36" t="inlineStr"/>
+      <c r="T21" s="43" t="inlineStr"/>
+      <c r="U21" s="39" t="inlineStr"/>
+      <c r="V21" s="39" t="inlineStr"/>
       <c r="W21" s="39" t="inlineStr">
         <is>
-          <t>ЗАЧЕТ            Оказание медицинской помощи в экстренной форме  Мхитарян Л.С.</t>
-        </is>
-      </c>
-      <c r="X21" s="36" t="inlineStr">
-        <is>
-          <t>Зуботехническое материаловедение с курсом охраны труда и техники безопасности   Горин А.А.</t>
-        </is>
-      </c>
-      <c r="Y21" s="36" t="inlineStr"/>
-      <c r="Z21" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Санитария и гигиена в деятельности медицинской сестры                Маклаков И.А. </t>
-        </is>
-      </c>
-      <c r="AA21" s="36" t="inlineStr"/>
-      <c r="AB21" s="31" t="inlineStr"/>
-      <c r="AC21" s="31" t="inlineStr"/>
-      <c r="AD21" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Технология визажа Ермолаева И.В.                                               </t>
-        </is>
-      </c>
-      <c r="AE21" s="36" t="inlineStr">
+          <t>ЗАЧЕТ               Оказание медицинской помощи в экстренной форме  Мхитарян Л.С.</t>
+        </is>
+      </c>
+      <c r="X21" s="39" t="inlineStr"/>
+      <c r="Y21" s="39" t="inlineStr">
+        <is>
+          <t>Технология изготовления съемных пластиночных  протезов        Горин А.А.</t>
+        </is>
+      </c>
+      <c r="Z21" s="40" t="inlineStr"/>
+      <c r="AA21" s="39" t="inlineStr"/>
+      <c r="AB21" s="33" t="inlineStr"/>
+      <c r="AC21" s="33" t="inlineStr"/>
+      <c r="AD21" s="39" t="inlineStr"/>
+      <c r="AE21" s="39" t="inlineStr"/>
+      <c r="AF21" s="33" t="inlineStr"/>
+      <c r="AG21" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Выполнение работ по профессии "Маникюрша"  Алексеенко Е.М.  </t>
         </is>
       </c>
-      <c r="AF21" s="31" t="inlineStr"/>
-      <c r="AG21" s="31" t="inlineStr">
-        <is>
-          <t>Технология косметических услуг                       Джокич Э.А.</t>
-        </is>
-      </c>
-      <c r="AH21" s="1" t="inlineStr"/>
+      <c r="AH21" s="3" t="inlineStr"/>
     </row>
     <row r="22" ht="99.95" customHeight="1" thickBot="1">
-      <c r="A22" s="26" t="n"/>
-      <c r="B22" s="25" t="n">
+      <c r="A22" s="28" t="n"/>
+      <c r="B22" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="C22" s="41" t="n"/>
-      <c r="D22" s="41" t="n"/>
-      <c r="E22" s="41" t="n"/>
-      <c r="F22" s="42" t="n"/>
-      <c r="G22" s="26" t="n"/>
-      <c r="H22" s="43" t="n"/>
-      <c r="I22" s="41" t="n"/>
-      <c r="J22" s="41" t="n"/>
-      <c r="K22" s="41" t="n"/>
-      <c r="L22" s="24" t="n"/>
-      <c r="M22" s="41" t="n"/>
-      <c r="N22" s="41" t="n"/>
-      <c r="O22" s="21" t="inlineStr"/>
-      <c r="P22" s="44" t="n"/>
-      <c r="Q22" s="45" t="n">
+      <c r="C22" s="45" t="n"/>
+      <c r="D22" s="45" t="n"/>
+      <c r="E22" s="45" t="n"/>
+      <c r="F22" s="46" t="n"/>
+      <c r="G22" s="28" t="n"/>
+      <c r="H22" s="47" t="n"/>
+      <c r="I22" s="45" t="n"/>
+      <c r="J22" s="45" t="n"/>
+      <c r="K22" s="45" t="n"/>
+      <c r="L22" s="45" t="n"/>
+      <c r="M22" s="45" t="n"/>
+      <c r="N22" s="45" t="n"/>
+      <c r="O22" s="1" t="inlineStr"/>
+      <c r="P22" s="48" t="n"/>
+      <c r="Q22" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="R22" s="41" t="n"/>
-      <c r="S22" s="41" t="n"/>
-      <c r="T22" s="41" t="n"/>
-      <c r="U22" s="41" t="n"/>
-      <c r="V22" s="41" t="n"/>
-      <c r="W22" s="43" t="n"/>
-      <c r="X22" s="41" t="n"/>
-      <c r="Y22" s="41" t="n"/>
-      <c r="Z22" s="24" t="n"/>
-      <c r="AA22" s="41" t="n"/>
-      <c r="AB22" s="26" t="n"/>
-      <c r="AC22" s="26" t="n"/>
-      <c r="AD22" s="41" t="n"/>
-      <c r="AE22" s="41" t="n"/>
-      <c r="AF22" s="26" t="n"/>
-      <c r="AG22" s="26" t="n"/>
-      <c r="AH22" s="1" t="inlineStr"/>
+      <c r="R22" s="45" t="n"/>
+      <c r="S22" s="45" t="n"/>
+      <c r="T22" s="45" t="n"/>
+      <c r="U22" s="45" t="n"/>
+      <c r="V22" s="45" t="n"/>
+      <c r="W22" s="45" t="n"/>
+      <c r="X22" s="45" t="n"/>
+      <c r="Y22" s="45" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="45" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="28" t="n"/>
+      <c r="AD22" s="45" t="n"/>
+      <c r="AE22" s="45" t="n"/>
+      <c r="AF22" s="28" t="n"/>
+      <c r="AG22" s="28" t="n"/>
+      <c r="AH22" s="3" t="inlineStr"/>
     </row>
     <row r="23" ht="99.95" customHeight="1">
-      <c r="A23" s="46" t="inlineStr">
+      <c r="A23" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">среда </t>
         </is>
       </c>
-      <c r="B23" s="25" t="n">
+      <c r="B23" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>Право     Кожевников В.Е.</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Русский язык       Исаева Г.А.</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E23" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve"> Информатика    Олимова Е.Н.          1 подгруппа</t>
         </is>
       </c>
-      <c r="F23" s="48" t="inlineStr"/>
-      <c r="G23" s="48" t="inlineStr"/>
-      <c r="H23" s="18" t="inlineStr"/>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Документационное  обеспечение управления       Иванова Ж.В.  </t>
-        </is>
-      </c>
-      <c r="J23" s="18" t="inlineStr"/>
+      <c r="F23" s="52" t="inlineStr"/>
+      <c r="G23" s="54" t="inlineStr"/>
+      <c r="H23" s="21" t="inlineStr"/>
+      <c r="I23" s="19" t="inlineStr"/>
+      <c r="J23" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Организация работы органов и учреждений социальной защиты населения, органов Пенсионного фонда РФ                   Лютова М.В. </t>
+        </is>
+      </c>
       <c r="K23" s="19" t="inlineStr"/>
-      <c r="L23" s="18" t="inlineStr"/>
-      <c r="M23" s="20" t="inlineStr">
+      <c r="L23" s="19" t="inlineStr">
+        <is>
+          <t>Транспортная логистика Коломиец А.И.</t>
+        </is>
+      </c>
+      <c r="M23" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Основы предпринимательства                          Иванов В.В.  </t>
         </is>
       </c>
-      <c r="N23" s="18" t="inlineStr">
+      <c r="N23" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Товароведение продовольственных и непродовольственных товаров   </t>
         </is>
       </c>
-      <c r="O23" s="21" t="inlineStr"/>
-      <c r="P23" s="22" t="inlineStr">
+      <c r="O23" s="1" t="inlineStr"/>
+      <c r="P23" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">среда </t>
         </is>
       </c>
-      <c r="Q23" s="51" t="n">
+      <c r="Q23" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="R23" s="52" t="inlineStr">
-        <is>
-          <t>ДЕНЬ САМОПОДГОТОВКИ</t>
-        </is>
-      </c>
-      <c r="S23" s="52" t="inlineStr">
-        <is>
-          <t>ДЕНЬ САМОПОДГОТОВКИ</t>
-        </is>
-      </c>
-      <c r="T23" s="48" t="inlineStr"/>
-      <c r="U23" s="18" t="inlineStr"/>
-      <c r="V23" s="18" t="inlineStr"/>
-      <c r="W23" s="18" t="inlineStr"/>
-      <c r="X23" s="18" t="inlineStr">
-        <is>
-          <t>История  России                   Козлов Д.В.</t>
-        </is>
-      </c>
-      <c r="Y23" s="19" t="inlineStr">
-        <is>
-          <t>Технология изготовления съемных пластиночных  протезов                    Горин А.А.</t>
-        </is>
-      </c>
-      <c r="Z23" s="18" t="inlineStr"/>
-      <c r="AA23" s="18" t="inlineStr">
+      <c r="R23" s="19" t="inlineStr">
+        <is>
+          <t>БЖД                                    Ходаковский В.В.</t>
+        </is>
+      </c>
+      <c r="S23" s="19" t="inlineStr">
+        <is>
+          <t>БЖД                                    Ходаковский В.В.</t>
+        </is>
+      </c>
+      <c r="T23" s="52" t="inlineStr">
+        <is>
+          <t>Стоматологическое прсвящение               Мхитарян Л.С.</t>
+        </is>
+      </c>
+      <c r="U23" s="19" t="inlineStr"/>
+      <c r="V23" s="19" t="inlineStr"/>
+      <c r="W23" s="19" t="inlineStr"/>
+      <c r="X23" s="19" t="inlineStr">
+        <is>
+          <t>Анатомия и физиология человека с курсом биомеханики зубочелюстной системы                    Горин А.А.</t>
+        </is>
+      </c>
+      <c r="Y23" s="20" t="inlineStr"/>
+      <c r="Z23" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Обеспечение безопасной окружающей среды в медицинской организации Маклаков И.А. </t>
+        </is>
+      </c>
+      <c r="AA23" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Сестринский уход за пациентами хирургического профиля        Байбакова А.Х. </t>
         </is>
       </c>
-      <c r="AB23" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Технология маникюра Алексеенко Е.М.  </t>
-        </is>
-      </c>
-      <c r="AC23" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Анатомия и физиология человека          Маклаков И.А. </t>
-        </is>
-      </c>
-      <c r="AD23" s="18" t="inlineStr"/>
-      <c r="AE23" s="18" t="inlineStr">
+      <c r="AB23" s="19" t="inlineStr"/>
+      <c r="AC23" s="19" t="inlineStr">
         <is>
           <t>Рисунок и живопись                Щукина А.А.</t>
         </is>
       </c>
-      <c r="AF23" s="18" t="inlineStr">
-        <is>
-          <t>КР                   Технология косметических услуг                       Джокич Э.А.</t>
-        </is>
-      </c>
-      <c r="AG23" s="18" t="inlineStr">
-        <is>
-          <t>КР                   Технология косметических услуг                       Джокич Э.А.</t>
-        </is>
-      </c>
-      <c r="AH23" s="53" t="inlineStr"/>
+      <c r="AD23" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Выполнение работ по профессии "Маникюрша"  Алексеенко Е.М.  </t>
+        </is>
+      </c>
+      <c r="AE23" s="19" t="inlineStr"/>
+      <c r="AF23" s="19" t="inlineStr">
+        <is>
+          <t>Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.</t>
+        </is>
+      </c>
+      <c r="AG23" s="21" t="inlineStr"/>
+      <c r="AH23" s="61" t="inlineStr"/>
     </row>
     <row r="24" ht="99.95" customHeight="1">
-      <c r="A24" s="24" t="n"/>
-      <c r="B24" s="25" t="n">
+      <c r="A24" s="26" t="n"/>
+      <c r="B24" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="26" t="n"/>
-      <c r="D24" s="26" t="n"/>
-      <c r="E24" s="26" t="n"/>
-      <c r="F24" s="26" t="n"/>
-      <c r="G24" s="26" t="n"/>
-      <c r="H24" s="26" t="n"/>
-      <c r="I24" s="26" t="n"/>
-      <c r="J24" s="26" t="n"/>
-      <c r="K24" s="27" t="n"/>
-      <c r="L24" s="26" t="n"/>
+      <c r="C24" s="28" t="n"/>
+      <c r="D24" s="28" t="n"/>
+      <c r="E24" s="28" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+      <c r="H24" s="28" t="n"/>
+      <c r="I24" s="28" t="n"/>
+      <c r="J24" s="28" t="n"/>
+      <c r="K24" s="28" t="n"/>
+      <c r="L24" s="28" t="n"/>
       <c r="M24" s="28" t="n"/>
-      <c r="N24" s="26" t="n"/>
-      <c r="O24" s="21" t="inlineStr"/>
-      <c r="P24" s="29" t="n"/>
-      <c r="Q24" s="30" t="n">
+      <c r="N24" s="28" t="n"/>
+      <c r="O24" s="1" t="inlineStr"/>
+      <c r="P24" s="31" t="n"/>
+      <c r="Q24" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="R24" s="24" t="n"/>
-      <c r="S24" s="24" t="n"/>
-      <c r="T24" s="26" t="n"/>
-      <c r="U24" s="26" t="n"/>
-      <c r="V24" s="26" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
-      <c r="Y24" s="27" t="n"/>
-      <c r="Z24" s="26" t="n"/>
-      <c r="AA24" s="26" t="n"/>
-      <c r="AB24" s="26" t="n"/>
-      <c r="AC24" s="26" t="n"/>
-      <c r="AD24" s="26" t="n"/>
-      <c r="AE24" s="26" t="n"/>
-      <c r="AF24" s="26" t="n"/>
-      <c r="AG24" s="26" t="n"/>
-      <c r="AH24" s="4" t="n"/>
+      <c r="R24" s="28" t="n"/>
+      <c r="S24" s="28" t="n"/>
+      <c r="T24" s="28" t="n"/>
+      <c r="U24" s="28" t="n"/>
+      <c r="V24" s="28" t="n"/>
+      <c r="W24" s="28" t="n"/>
+      <c r="X24" s="28" t="n"/>
+      <c r="Y24" s="29" t="n"/>
+      <c r="Z24" s="28" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="28" t="n"/>
+      <c r="AD24" s="28" t="n"/>
+      <c r="AE24" s="28" t="n"/>
+      <c r="AF24" s="28" t="n"/>
+      <c r="AG24" s="28" t="n"/>
+      <c r="AH24" s="5" t="n"/>
     </row>
     <row r="25" ht="99.95" customHeight="1">
-      <c r="A25" s="24" t="n"/>
-      <c r="B25" s="25" t="n">
+      <c r="A25" s="26" t="n"/>
+      <c r="B25" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="31" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>История                    Козлов Д.В.</t>
         </is>
       </c>
-      <c r="D25" s="31" t="inlineStr">
+      <c r="D25" s="33" t="inlineStr">
         <is>
           <t>Математика       Ширнин А.Г.</t>
         </is>
       </c>
-      <c r="E25" s="31" t="inlineStr">
+      <c r="E25" s="33" t="inlineStr">
         <is>
           <t>Русский язык       Исаева Г.А.</t>
         </is>
       </c>
-      <c r="F25" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Информатика    Олимова Е.Н.     (ОД, ТД)           </t>
-        </is>
-      </c>
-      <c r="G25" s="31" t="inlineStr">
-        <is>
-          <t>Обществознание    Кожевников В.Е.</t>
-        </is>
-      </c>
-      <c r="H25" s="31" t="inlineStr">
-        <is>
-          <t>Обществознание    Кожевников В.Е.</t>
-        </is>
-      </c>
-      <c r="I25" s="31" t="inlineStr">
+      <c r="F25" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Информатика    Олимова Е.Н.     (ОД, ТД)       Обществознание    Кожевников В.Е.   (Ю)      </t>
+        </is>
+      </c>
+      <c r="G25" s="56" t="inlineStr"/>
+      <c r="H25" s="36" t="inlineStr"/>
+      <c r="I25" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Документационное  обеспечение управления       Иванова Ж.В.  </t>
         </is>
       </c>
-      <c r="J25" s="49" t="inlineStr"/>
-      <c r="K25" s="32" t="inlineStr">
+      <c r="J25" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Организация работы органов и учреждений социальной защиты населения, органов Пенсионного фонда РФ                   Лютова М.В. </t>
+        </is>
+      </c>
+      <c r="K25" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Экономика организации    Иванов В.В.  </t>
         </is>
       </c>
-      <c r="L25" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Моделирование логистических систем     Коломиец А.И.                    </t>
+      <c r="L25" s="33" t="inlineStr">
+        <is>
+          <t>Распределительная логистика    Коломиец А.И.</t>
         </is>
       </c>
       <c r="M25" s="33" t="inlineStr">
@@ -3443,1752 +3440,1768 @@
           <t xml:space="preserve">Экономика и основы анализа финансово - хозяйственной деятельности торговой организации  Иванов В.В.  </t>
         </is>
       </c>
-      <c r="N25" s="31" t="inlineStr">
+      <c r="N25" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Товароведение продовольственных и непродовольственных товаров   </t>
         </is>
       </c>
-      <c r="O25" s="21" t="inlineStr"/>
-      <c r="P25" s="29" t="n"/>
-      <c r="Q25" s="30" t="n">
+      <c r="O25" s="1" t="inlineStr"/>
+      <c r="P25" s="31" t="n"/>
+      <c r="Q25" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="24" t="n"/>
-      <c r="S25" s="24" t="n"/>
-      <c r="T25" s="31" t="inlineStr">
+      <c r="R25" s="33" t="inlineStr">
+        <is>
+          <t>Сестринское дело в стоматологии   Мхитарян Л.С.</t>
+        </is>
+      </c>
+      <c r="S25" s="33" t="inlineStr">
+        <is>
+          <t>Сестринское дело в стоматологии   Мхитарян Л.С.</t>
+        </is>
+      </c>
+      <c r="T25" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.       </t>
         </is>
       </c>
-      <c r="U25" s="31" t="inlineStr"/>
-      <c r="V25" s="31" t="inlineStr"/>
-      <c r="W25" s="31" t="inlineStr"/>
-      <c r="X25" s="31" t="inlineStr">
-        <is>
-          <t>ВПО           Писарева Н.А.</t>
-        </is>
-      </c>
-      <c r="Y25" s="32" t="inlineStr">
-        <is>
-          <t>Технология изготовления съемных пластиночных  протезов                    Горин А.А.</t>
-        </is>
-      </c>
-      <c r="Z25" s="31" t="inlineStr"/>
-      <c r="AA25" s="31" t="inlineStr">
+      <c r="U25" s="33" t="inlineStr"/>
+      <c r="V25" s="33" t="inlineStr"/>
+      <c r="W25" s="33" t="inlineStr"/>
+      <c r="X25" s="33" t="inlineStr">
+        <is>
+          <t>Зуботехническое материаловедение с курсом охраны труда и техники безопасности   Горин А.А.</t>
+        </is>
+      </c>
+      <c r="Y25" s="34" t="inlineStr"/>
+      <c r="Z25" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Анатомия и физиология человека            Маклаков И.А. </t>
+        </is>
+      </c>
+      <c r="AA25" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Сестринский уход за пациентами хирургического профиля        Байбакова А.Х. </t>
         </is>
       </c>
-      <c r="AB25" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Анатомия и физиология человека          Маклаков И.А. </t>
-        </is>
-      </c>
-      <c r="AC25" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Технология маникюра Алексеенко Е.М.  </t>
-        </is>
-      </c>
-      <c r="AD25" s="31" t="inlineStr"/>
-      <c r="AE25" s="31" t="inlineStr">
-        <is>
-          <t>Рисунок и живопись                Щукина А.А.</t>
-        </is>
-      </c>
-      <c r="AF25" s="31" t="inlineStr">
-        <is>
-          <t>КР                      Технология косметических услуг                       Джокич Э.А.</t>
-        </is>
-      </c>
-      <c r="AG25" s="31" t="inlineStr">
-        <is>
-          <t>КР                      Технология косметических услуг                       Джокич Э.А.</t>
-        </is>
-      </c>
-      <c r="AH25" s="1" t="inlineStr"/>
+      <c r="AB25" s="35" t="inlineStr"/>
+      <c r="AC25" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рисунок и живопись                Щукина А.А.     </t>
+        </is>
+      </c>
+      <c r="AD25" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Выполнение работ по профессии "Маникюрша"  Алексеенко Е.М.  </t>
+        </is>
+      </c>
+      <c r="AE25" s="33" t="inlineStr"/>
+      <c r="AF25" s="33" t="inlineStr">
+        <is>
+          <t>Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.</t>
+        </is>
+      </c>
+      <c r="AG25" s="33" t="inlineStr"/>
+      <c r="AH25" s="3" t="inlineStr"/>
     </row>
     <row r="26" ht="99.95" customHeight="1">
-      <c r="A26" s="24" t="n"/>
-      <c r="B26" s="25" t="n">
+      <c r="A26" s="26" t="n"/>
+      <c r="B26" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C26" s="26" t="n"/>
-      <c r="D26" s="26" t="n"/>
-      <c r="E26" s="26" t="n"/>
-      <c r="F26" s="26" t="n"/>
-      <c r="G26" s="26" t="n"/>
-      <c r="H26" s="26" t="n"/>
-      <c r="I26" s="26" t="n"/>
-      <c r="J26" s="26" t="n"/>
-      <c r="K26" s="27" t="n"/>
-      <c r="L26" s="26" t="n"/>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="28" t="n"/>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+      <c r="H26" s="28" t="n"/>
+      <c r="I26" s="28" t="n"/>
+      <c r="J26" s="28" t="n"/>
+      <c r="K26" s="28" t="n"/>
+      <c r="L26" s="28" t="n"/>
       <c r="M26" s="28" t="n"/>
-      <c r="N26" s="26" t="n"/>
-      <c r="O26" s="21" t="inlineStr"/>
-      <c r="P26" s="29" t="n"/>
-      <c r="Q26" s="30" t="n">
+      <c r="N26" s="28" t="n"/>
+      <c r="O26" s="1" t="inlineStr"/>
+      <c r="P26" s="31" t="n"/>
+      <c r="Q26" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="R26" s="24" t="n"/>
-      <c r="S26" s="24" t="n"/>
-      <c r="T26" s="26" t="n"/>
-      <c r="U26" s="26" t="n"/>
-      <c r="V26" s="26" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
-      <c r="Y26" s="27" t="n"/>
-      <c r="Z26" s="26" t="n"/>
-      <c r="AA26" s="26" t="n"/>
-      <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="26" t="n"/>
-      <c r="AD26" s="26" t="n"/>
-      <c r="AE26" s="26" t="n"/>
-      <c r="AF26" s="26" t="n"/>
-      <c r="AG26" s="26" t="n"/>
-      <c r="AH26" s="1" t="inlineStr"/>
+      <c r="R26" s="28" t="n"/>
+      <c r="S26" s="28" t="n"/>
+      <c r="T26" s="28" t="n"/>
+      <c r="U26" s="28" t="n"/>
+      <c r="V26" s="28" t="n"/>
+      <c r="W26" s="28" t="n"/>
+      <c r="X26" s="28" t="n"/>
+      <c r="Y26" s="29" t="n"/>
+      <c r="Z26" s="28" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="30" t="n"/>
+      <c r="AC26" s="28" t="n"/>
+      <c r="AD26" s="28" t="n"/>
+      <c r="AE26" s="28" t="n"/>
+      <c r="AF26" s="28" t="n"/>
+      <c r="AG26" s="28" t="n"/>
+      <c r="AH26" s="3" t="inlineStr"/>
     </row>
     <row r="27" ht="99.95" customHeight="1">
-      <c r="A27" s="24" t="n"/>
-      <c r="B27" s="25" t="n">
+      <c r="A27" s="26" t="n"/>
+      <c r="B27" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="C27" s="31" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>Литература       Исаева Г.А.</t>
         </is>
       </c>
-      <c r="D27" s="31" t="inlineStr"/>
-      <c r="E27" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> История       Козлов Д.В. </t>
-        </is>
-      </c>
-      <c r="F27" s="31" t="inlineStr">
+      <c r="D27" s="33" t="inlineStr"/>
+      <c r="E27" s="33" t="inlineStr">
+        <is>
+          <t>Обществознание    Кожевников В.Е.</t>
+        </is>
+      </c>
+      <c r="F27" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Основы безопасности и защиты Родины   Иванов В.В.  </t>
         </is>
       </c>
-      <c r="G27" s="31" t="inlineStr">
+      <c r="G27" s="33" t="inlineStr">
         <is>
           <t>Математика       Ширнин А.Г.</t>
         </is>
       </c>
-      <c r="H27" s="31" t="inlineStr">
+      <c r="H27" s="33" t="inlineStr">
         <is>
           <t>Математика       Ширнин А.Г.</t>
         </is>
       </c>
-      <c r="I27" s="31" t="inlineStr">
-        <is>
-          <t>ВПО           Писарева Н.А.</t>
-        </is>
-      </c>
-      <c r="J27" s="49" t="inlineStr"/>
-      <c r="K27" s="32" t="inlineStr">
+      <c r="I27" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Документационное  обеспечение управления       Иванова Ж.В.  </t>
+        </is>
+      </c>
+      <c r="J27" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Числитель Социальная работа с различными группами населения     Лютова М.В. </t>
+        </is>
+      </c>
+      <c r="K27" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Информационное обеспечение логистических процессов        Олимова Е.Н. </t>
         </is>
       </c>
-      <c r="L27" s="31" t="inlineStr">
-        <is>
-          <t>Распределительная логистика    Коломиец А.И.</t>
-        </is>
-      </c>
+      <c r="L27" s="52" t="inlineStr"/>
       <c r="M27" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Эксплуатация торгово - технологического оборудования и охрана труда </t>
         </is>
       </c>
-      <c r="N27" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Этика и психология делового общения                 Иванова Ж.В.     </t>
-        </is>
-      </c>
-      <c r="O27" s="21" t="inlineStr"/>
-      <c r="P27" s="29" t="n"/>
-      <c r="Q27" s="30" t="n">
+      <c r="N27" s="36" t="inlineStr"/>
+      <c r="O27" s="1" t="inlineStr"/>
+      <c r="P27" s="31" t="n"/>
+      <c r="Q27" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="R27" s="24" t="n"/>
-      <c r="S27" s="24" t="n"/>
-      <c r="T27" s="31" t="inlineStr">
-        <is>
-          <t>Правовое обеспечение профессиональной деятельности     Кожевников В.Е.</t>
-        </is>
-      </c>
-      <c r="U27" s="31" t="inlineStr"/>
-      <c r="V27" s="31" t="inlineStr"/>
-      <c r="W27" s="31" t="inlineStr"/>
-      <c r="X27" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.       </t>
-        </is>
-      </c>
-      <c r="Y27" s="32" t="inlineStr">
+      <c r="R27" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История России   Козлов Д.В. </t>
+        </is>
+      </c>
+      <c r="S27" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История России   Козлов Д.В. </t>
+        </is>
+      </c>
+      <c r="T27" s="33" t="inlineStr">
+        <is>
+          <t>Гигиена полости рта                Мхитарян Л.С.</t>
+        </is>
+      </c>
+      <c r="U27" s="33" t="inlineStr"/>
+      <c r="V27" s="33" t="inlineStr"/>
+      <c r="W27" s="33" t="inlineStr"/>
+      <c r="X27" s="33" t="inlineStr"/>
+      <c r="Y27" s="34" t="inlineStr">
         <is>
           <t>Технология изготовления съемных пластиночных  протезов                    Горин А.А.</t>
         </is>
       </c>
-      <c r="Z27" s="31" t="inlineStr">
+      <c r="Z27" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Анатомия и физиология человека            Маклаков И.А. </t>
         </is>
       </c>
-      <c r="AA27" s="31" t="inlineStr">
+      <c r="AA27" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Сестринский уход и реабилитация пациентов терапевтического профиля разных возрастных групп Байбакова А.Х. </t>
         </is>
       </c>
-      <c r="AB27" s="31" t="inlineStr">
+      <c r="AB27" s="35" t="inlineStr">
         <is>
           <t>Рисунок и живопись                Щукина А.А.</t>
         </is>
       </c>
-      <c r="AC27" s="31" t="inlineStr"/>
-      <c r="AD27" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Выполнение работ по профессии "Маникюрша"  Алексеенко Е.М.  </t>
-        </is>
-      </c>
-      <c r="AE27" s="31" t="inlineStr"/>
-      <c r="AF27" s="31" t="inlineStr"/>
-      <c r="AG27" s="31" t="inlineStr"/>
-      <c r="AH27" s="1" t="inlineStr"/>
+      <c r="AC27" s="33" t="inlineStr"/>
+      <c r="AD27" s="33" t="inlineStr"/>
+      <c r="AE27" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сервисная деятельность  Алексеенко Е.М.  </t>
+        </is>
+      </c>
+      <c r="AF27" s="33" t="inlineStr"/>
+      <c r="AG27" s="33" t="inlineStr">
+        <is>
+          <t>Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
     </row>
     <row r="28" ht="99.95" customHeight="1">
-      <c r="A28" s="24" t="n"/>
-      <c r="B28" s="25" t="n">
+      <c r="A28" s="26" t="n"/>
+      <c r="B28" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="C28" s="26" t="n"/>
-      <c r="D28" s="26" t="n"/>
-      <c r="E28" s="26" t="n"/>
-      <c r="F28" s="26" t="n"/>
-      <c r="G28" s="26" t="n"/>
-      <c r="H28" s="26" t="n"/>
-      <c r="I28" s="26" t="n"/>
-      <c r="J28" s="26" t="n"/>
-      <c r="K28" s="27" t="n"/>
-      <c r="L28" s="26" t="n"/>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="28" t="n"/>
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
+      <c r="H28" s="28" t="n"/>
+      <c r="I28" s="28" t="n"/>
+      <c r="J28" s="33" t="inlineStr"/>
+      <c r="K28" s="28" t="n"/>
+      <c r="L28" s="28" t="n"/>
       <c r="M28" s="28" t="n"/>
-      <c r="N28" s="26" t="n"/>
-      <c r="O28" s="21" t="inlineStr"/>
-      <c r="P28" s="29" t="n"/>
-      <c r="Q28" s="30" t="n">
+      <c r="N28" s="28" t="n"/>
+      <c r="O28" s="1" t="inlineStr"/>
+      <c r="P28" s="31" t="n"/>
+      <c r="Q28" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="24" t="n"/>
-      <c r="S28" s="24" t="n"/>
-      <c r="T28" s="26" t="n"/>
-      <c r="U28" s="26" t="n"/>
-      <c r="V28" s="26" t="n"/>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
-      <c r="Y28" s="27" t="n"/>
-      <c r="Z28" s="26" t="n"/>
-      <c r="AA28" s="26" t="n"/>
-      <c r="AB28" s="26" t="n"/>
-      <c r="AC28" s="26" t="n"/>
-      <c r="AD28" s="26" t="n"/>
-      <c r="AE28" s="26" t="n"/>
-      <c r="AF28" s="26" t="n"/>
-      <c r="AG28" s="26" t="n"/>
-      <c r="AH28" s="1" t="inlineStr"/>
+      <c r="R28" s="28" t="n"/>
+      <c r="S28" s="28" t="n"/>
+      <c r="T28" s="28" t="n"/>
+      <c r="U28" s="28" t="n"/>
+      <c r="V28" s="28" t="n"/>
+      <c r="W28" s="28" t="n"/>
+      <c r="X28" s="28" t="n"/>
+      <c r="Y28" s="29" t="n"/>
+      <c r="Z28" s="28" t="n"/>
+      <c r="AA28" s="28" t="n"/>
+      <c r="AB28" s="30" t="n"/>
+      <c r="AC28" s="28" t="n"/>
+      <c r="AD28" s="28" t="n"/>
+      <c r="AE28" s="28" t="n"/>
+      <c r="AF28" s="28" t="n"/>
+      <c r="AG28" s="28" t="n"/>
+      <c r="AH28" s="3" t="inlineStr"/>
     </row>
     <row r="29" ht="99.95" customHeight="1">
-      <c r="A29" s="24" t="n"/>
-      <c r="B29" s="25" t="n">
+      <c r="A29" s="26" t="n"/>
+      <c r="B29" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="C29" s="31" t="inlineStr">
-        <is>
-          <t>Математика       Ширнин А.Г.</t>
-        </is>
-      </c>
-      <c r="D29" s="31" t="inlineStr"/>
-      <c r="E29" s="36" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Основы безопасности и защиты Родины   Иванов В.В.  </t>
+        </is>
+      </c>
+      <c r="D29" s="33" t="inlineStr"/>
+      <c r="E29" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> Информатика    Олимова Е.Н.          2 подгруппа</t>
         </is>
       </c>
-      <c r="F29" s="31" t="inlineStr">
+      <c r="F29" s="33" t="inlineStr">
         <is>
           <t>Литература       Исаева Г.А.</t>
         </is>
       </c>
-      <c r="G29" s="31" t="inlineStr">
+      <c r="G29" s="33" t="inlineStr">
         <is>
           <t>История                    Козлов Д.В.</t>
         </is>
       </c>
-      <c r="H29" s="36" t="inlineStr">
+      <c r="H29" s="39" t="inlineStr">
         <is>
           <t>История                    Козлов Д.В.</t>
         </is>
       </c>
-      <c r="I29" s="36" t="inlineStr"/>
-      <c r="J29" s="36" t="inlineStr"/>
-      <c r="K29" s="54" t="inlineStr"/>
-      <c r="L29" s="31" t="inlineStr">
-        <is>
-          <t>Транспортная логистика Коломиец А.И.</t>
-        </is>
-      </c>
-      <c r="M29" s="55" t="inlineStr">
-        <is>
-          <t>Основы финансовой грамотности    Кожевников В.Е.</t>
-        </is>
-      </c>
-      <c r="N29" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Финансы, налоги и налогообложение Иванов В.В. </t>
-        </is>
-      </c>
-      <c r="O29" s="21" t="inlineStr"/>
-      <c r="P29" s="29" t="n"/>
-      <c r="Q29" s="30" t="n">
+      <c r="I29" s="39" t="inlineStr"/>
+      <c r="J29" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Социальная работа с различными группами населения     Лютова М.В. </t>
+        </is>
+      </c>
+      <c r="K29" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Документационное  обеспечение управления       Иванова Ж.В.  </t>
+        </is>
+      </c>
+      <c r="L29" s="36" t="inlineStr"/>
+      <c r="M29" s="62" t="inlineStr"/>
+      <c r="N29" s="43" t="inlineStr"/>
+      <c r="O29" s="1" t="inlineStr"/>
+      <c r="P29" s="31" t="n"/>
+      <c r="Q29" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="R29" s="24" t="n"/>
-      <c r="S29" s="24" t="n"/>
-      <c r="T29" s="36" t="inlineStr"/>
-      <c r="U29" s="36" t="inlineStr"/>
-      <c r="V29" s="36" t="inlineStr"/>
-      <c r="W29" s="36" t="inlineStr"/>
-      <c r="X29" s="36" t="inlineStr">
+      <c r="R29" s="43" t="inlineStr"/>
+      <c r="S29" s="39" t="inlineStr"/>
+      <c r="T29" s="39" t="inlineStr">
+        <is>
+          <t>Гигиена полости рта                Мхитарян Л.С.</t>
+        </is>
+      </c>
+      <c r="U29" s="43" t="inlineStr"/>
+      <c r="V29" s="39" t="inlineStr"/>
+      <c r="W29" s="39" t="inlineStr"/>
+      <c r="X29" s="39" t="inlineStr"/>
+      <c r="Y29" s="41" t="inlineStr">
         <is>
           <t>Технология изготовления съемных пластиночных  протезов                    Горин А.А.</t>
         </is>
       </c>
-      <c r="Y29" s="38" t="inlineStr">
+      <c r="Z29" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Генетика с основами медицинской генетики  Маклаков И.А. </t>
+        </is>
+      </c>
+      <c r="AA29" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сестринский уход и реабилитация пациентов терапевтического профиля разных возрастных групп Байбакова А.Х. </t>
+        </is>
+      </c>
+      <c r="AB29" s="42" t="inlineStr">
+        <is>
+          <t>Рисунок и живопись                Щукина А.А.</t>
+        </is>
+      </c>
+      <c r="AC29" s="39" t="inlineStr"/>
+      <c r="AD29" s="39" t="inlineStr"/>
+      <c r="AE29" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сервисная деятельность  Алексеенко Е.М.  </t>
+        </is>
+      </c>
+      <c r="AF29" s="36" t="inlineStr"/>
+      <c r="AG29" s="33" t="inlineStr">
         <is>
           <t>Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.</t>
         </is>
       </c>
-      <c r="Z29" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Генетика с основами медицинской генетики  Маклаков И.А. </t>
-        </is>
-      </c>
-      <c r="AA29" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сестринский уход и реабилитация пациентов терапевтического профиля разных возрастных групп Байбакова А.Х. </t>
-        </is>
-      </c>
-      <c r="AB29" s="36" t="inlineStr">
-        <is>
-          <t>Рисунок и живопись                Щукина А.А.</t>
-        </is>
-      </c>
-      <c r="AC29" s="36" t="inlineStr"/>
-      <c r="AD29" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Выполнение работ по профессии "Маникюрша"  Алексеенко Е.М.  </t>
-        </is>
-      </c>
-      <c r="AE29" s="36" t="inlineStr"/>
-      <c r="AF29" s="31" t="inlineStr"/>
-      <c r="AG29" s="31" t="inlineStr"/>
-      <c r="AH29" s="1" t="inlineStr"/>
+      <c r="AH29" s="3" t="inlineStr"/>
     </row>
     <row r="30" ht="99.75" customHeight="1" thickBot="1">
-      <c r="A30" s="26" t="n"/>
-      <c r="B30" s="25" t="n">
+      <c r="A30" s="28" t="n"/>
+      <c r="B30" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="C30" s="26" t="n"/>
-      <c r="D30" s="26" t="n"/>
-      <c r="E30" s="41" t="n"/>
-      <c r="F30" s="26" t="n"/>
-      <c r="G30" s="26" t="n"/>
-      <c r="H30" s="41" t="n"/>
-      <c r="I30" s="41" t="n"/>
-      <c r="J30" s="41" t="n"/>
-      <c r="K30" s="56" t="n"/>
-      <c r="L30" s="26" t="n"/>
-      <c r="M30" s="57" t="n"/>
-      <c r="N30" s="41" t="n"/>
-      <c r="O30" s="21" t="inlineStr"/>
-      <c r="P30" s="44" t="n"/>
-      <c r="Q30" s="45" t="n">
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="28" t="n"/>
+      <c r="E30" s="45" t="n"/>
+      <c r="F30" s="28" t="n"/>
+      <c r="G30" s="28" t="n"/>
+      <c r="H30" s="45" t="n"/>
+      <c r="I30" s="45" t="n"/>
+      <c r="J30" s="45" t="n"/>
+      <c r="K30" s="26" t="n"/>
+      <c r="L30" s="28" t="n"/>
+      <c r="M30" s="26" t="n"/>
+      <c r="N30" s="45" t="n"/>
+      <c r="O30" s="1" t="inlineStr"/>
+      <c r="P30" s="48" t="n"/>
+      <c r="Q30" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="R30" s="41" t="n"/>
-      <c r="S30" s="41" t="n"/>
-      <c r="T30" s="41" t="n"/>
-      <c r="U30" s="41" t="n"/>
-      <c r="V30" s="41" t="n"/>
-      <c r="W30" s="41" t="n"/>
-      <c r="X30" s="41" t="n"/>
-      <c r="Y30" s="42" t="n"/>
-      <c r="Z30" s="26" t="n"/>
-      <c r="AA30" s="41" t="n"/>
-      <c r="AB30" s="41" t="n"/>
-      <c r="AC30" s="41" t="n"/>
-      <c r="AD30" s="41" t="n"/>
-      <c r="AE30" s="41" t="n"/>
-      <c r="AF30" s="26" t="n"/>
-      <c r="AG30" s="26" t="n"/>
-      <c r="AH30" s="1" t="inlineStr"/>
+      <c r="R30" s="45" t="n"/>
+      <c r="S30" s="45" t="n"/>
+      <c r="T30" s="45" t="n"/>
+      <c r="U30" s="45" t="n"/>
+      <c r="V30" s="45" t="n"/>
+      <c r="W30" s="45" t="n"/>
+      <c r="X30" s="45" t="n"/>
+      <c r="Y30" s="46" t="n"/>
+      <c r="Z30" s="28" t="n"/>
+      <c r="AA30" s="45" t="n"/>
+      <c r="AB30" s="47" t="n"/>
+      <c r="AC30" s="45" t="n"/>
+      <c r="AD30" s="45" t="n"/>
+      <c r="AE30" s="45" t="n"/>
+      <c r="AF30" s="28" t="n"/>
+      <c r="AG30" s="28" t="n"/>
+      <c r="AH30" s="3" t="inlineStr"/>
     </row>
     <row r="31" ht="99.95" customHeight="1">
-      <c r="A31" s="46" t="inlineStr">
+      <c r="A31" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">четверг </t>
         </is>
       </c>
-      <c r="B31" s="25" t="n">
+      <c r="B31" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve"> Информатика    Олимова Е.Н.          1 подгруппа</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Математика       Ширнин А.Г.</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Химия        Морозова Е.Н. </t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
+          <t>Право     Кожевников В.Е.</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="inlineStr"/>
+      <c r="H31" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Основы безопасности и защиты Родины   Иванов В.В.  </t>
         </is>
       </c>
-      <c r="F31" s="18" t="inlineStr">
-        <is>
-          <t>Право     Кожевников В.Е.</t>
-        </is>
-      </c>
-      <c r="G31" s="18" t="inlineStr"/>
-      <c r="H31" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Химия        Морозова Е.Н. </t>
-        </is>
-      </c>
-      <c r="I31" s="18" t="inlineStr"/>
-      <c r="J31" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Основы пенсионного законодательства РФ             Григорьев Д.В. </t>
-        </is>
-      </c>
-      <c r="K31" s="18" t="inlineStr">
+      <c r="I31" s="63" t="inlineStr"/>
+      <c r="J31" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Основы пенсионного законодательства РФ             Григорьев Д.В. </t>
+        </is>
+      </c>
+      <c r="K31" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">История России   Козлов Д.В.         </t>
         </is>
       </c>
-      <c r="L31" s="58" t="inlineStr"/>
-      <c r="M31" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">История России   Козлов Д.В.         </t>
-        </is>
-      </c>
-      <c r="N31" s="20" t="inlineStr">
+      <c r="L31" s="64" t="inlineStr"/>
+      <c r="M31" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> История России   Козлов Д.В.         </t>
+        </is>
+      </c>
+      <c r="N31" s="25" t="inlineStr">
         <is>
           <t>Этика и психология делового общения                 Иванова Ж.В.</t>
         </is>
       </c>
-      <c r="O31" s="21" t="inlineStr"/>
-      <c r="P31" s="22" t="inlineStr">
+      <c r="O31" s="1" t="inlineStr"/>
+      <c r="P31" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">четверг </t>
         </is>
       </c>
-      <c r="Q31" s="51" t="n">
+      <c r="Q31" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="R31" s="18" t="inlineStr">
+      <c r="R31" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Анатомия и физиология человека          Маклаков И.А. </t>
         </is>
       </c>
-      <c r="S31" s="18" t="inlineStr"/>
-      <c r="T31" s="18" t="inlineStr"/>
-      <c r="U31" s="48" t="inlineStr">
+      <c r="S31" s="19" t="inlineStr"/>
+      <c r="T31" s="21" t="inlineStr"/>
+      <c r="U31" s="52" t="inlineStr">
         <is>
           <t>Гигиена полости рта                Мхитарян Л.С.</t>
         </is>
       </c>
-      <c r="V31" s="48" t="inlineStr">
+      <c r="V31" s="52" t="inlineStr">
         <is>
           <t>Гигиена полости рта                Мхитарян Л.С.</t>
         </is>
       </c>
-      <c r="W31" s="18" t="inlineStr">
-        <is>
-          <t>Стоматологические заболевания и их профилактика Станишевская Д.Н.</t>
-        </is>
-      </c>
-      <c r="X31" s="19" t="inlineStr"/>
-      <c r="Y31" s="18" t="inlineStr"/>
-      <c r="Z31" s="48" t="inlineStr">
+      <c r="W31" s="19" t="inlineStr">
+        <is>
+          <t>Стоматологические заболевания и их профилактика Станишевская Д.Н.   УРОК НА ПРОИЗВОДСТВЕ</t>
+        </is>
+      </c>
+      <c r="X31" s="20" t="inlineStr"/>
+      <c r="Y31" s="19" t="inlineStr"/>
+      <c r="Z31" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">Общий уход за пациентами     Перова Н.И.     </t>
         </is>
       </c>
-      <c r="AA31" s="18" t="inlineStr"/>
-      <c r="AB31" s="18" t="inlineStr"/>
-      <c r="AC31" s="20" t="inlineStr"/>
-      <c r="AD31" s="20" t="inlineStr"/>
-      <c r="AE31" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Выполнение работ по профессии "Маникюрша"  Алексеенко Е.М.  </t>
-        </is>
-      </c>
-      <c r="AF31" s="18" t="inlineStr">
+      <c r="AA31" s="19" t="inlineStr"/>
+      <c r="AB31" s="21" t="inlineStr"/>
+      <c r="AC31" s="22" t="inlineStr"/>
+      <c r="AD31" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Технология педикюра Алексеенко Е.М.  </t>
+        </is>
+      </c>
+      <c r="AE31" s="21" t="inlineStr"/>
+      <c r="AF31" s="19" t="inlineStr">
         <is>
           <t>Технология коррекции тела     Березовикова А.В.</t>
         </is>
       </c>
-      <c r="AG31" s="18" t="inlineStr"/>
-      <c r="AH31" s="1" t="inlineStr"/>
+      <c r="AG31" s="19" t="inlineStr"/>
+      <c r="AH31" s="3" t="inlineStr"/>
     </row>
     <row r="32" ht="99.95" customHeight="1">
-      <c r="A32" s="24" t="n"/>
-      <c r="B32" s="25" t="n">
+      <c r="A32" s="26" t="n"/>
+      <c r="B32" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="26" t="n"/>
-      <c r="G32" s="26" t="n"/>
-      <c r="H32" s="26" t="n"/>
-      <c r="I32" s="26" t="n"/>
-      <c r="J32" s="26" t="n"/>
-      <c r="K32" s="26" t="n"/>
-      <c r="L32" s="35" t="n"/>
-      <c r="M32" s="26" t="n"/>
-      <c r="N32" s="28" t="n"/>
-      <c r="O32" s="21" t="inlineStr"/>
-      <c r="P32" s="29" t="n"/>
-      <c r="Q32" s="30" t="n">
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="28" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="28" t="n"/>
+      <c r="H32" s="28" t="n"/>
+      <c r="I32" s="28" t="n"/>
+      <c r="J32" s="28" t="n"/>
+      <c r="K32" s="28" t="n"/>
+      <c r="L32" s="38" t="n"/>
+      <c r="M32" s="28" t="n"/>
+      <c r="N32" s="30" t="n"/>
+      <c r="O32" s="1" t="inlineStr"/>
+      <c r="P32" s="31" t="n"/>
+      <c r="Q32" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="R32" s="26" t="n"/>
-      <c r="S32" s="26" t="n"/>
-      <c r="T32" s="26" t="n"/>
-      <c r="U32" s="26" t="n"/>
-      <c r="V32" s="26" t="n"/>
-      <c r="W32" s="26" t="n"/>
-      <c r="X32" s="27" t="n"/>
-      <c r="Y32" s="26" t="n"/>
-      <c r="Z32" s="26" t="n"/>
-      <c r="AA32" s="26" t="n"/>
-      <c r="AB32" s="26" t="n"/>
-      <c r="AC32" s="28" t="n"/>
-      <c r="AD32" s="28" t="n"/>
-      <c r="AE32" s="26" t="n"/>
-      <c r="AF32" s="26" t="n"/>
-      <c r="AG32" s="26" t="n"/>
-      <c r="AH32" s="1" t="inlineStr"/>
+      <c r="R32" s="28" t="n"/>
+      <c r="S32" s="28" t="n"/>
+      <c r="T32" s="28" t="n"/>
+      <c r="U32" s="28" t="n"/>
+      <c r="V32" s="28" t="n"/>
+      <c r="W32" s="28" t="n"/>
+      <c r="X32" s="29" t="n"/>
+      <c r="Y32" s="28" t="n"/>
+      <c r="Z32" s="28" t="n"/>
+      <c r="AA32" s="28" t="n"/>
+      <c r="AB32" s="28" t="n"/>
+      <c r="AC32" s="30" t="n"/>
+      <c r="AD32" s="30" t="n"/>
+      <c r="AE32" s="28" t="n"/>
+      <c r="AF32" s="28" t="n"/>
+      <c r="AG32" s="28" t="n"/>
+      <c r="AH32" s="3" t="inlineStr"/>
     </row>
     <row r="33" ht="99.75" customHeight="1">
-      <c r="A33" s="24" t="n"/>
-      <c r="B33" s="25" t="n">
+      <c r="A33" s="26" t="n"/>
+      <c r="B33" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="C33" s="31" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Основы безопасности и защиты Родины   Иванов В.В.  </t>
         </is>
       </c>
-      <c r="D33" s="31" t="inlineStr">
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Химия        Морозова Е.Н. </t>
         </is>
       </c>
-      <c r="E33" s="31" t="inlineStr">
-        <is>
-          <t>Математика       Ширнин А.Г.</t>
-        </is>
-      </c>
-      <c r="F33" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Информатика    Олимова Е.Н.       (Ю)</t>
-        </is>
-      </c>
-      <c r="G33" s="31" t="inlineStr"/>
-      <c r="H33" s="31" t="inlineStr">
+      <c r="E33" s="33" t="inlineStr">
         <is>
           <t>История                    Козлов Д.В.</t>
         </is>
       </c>
-      <c r="I33" s="31" t="inlineStr">
+      <c r="F33" s="33" t="inlineStr">
+        <is>
+          <t>Математика      Ширнин А.Г.     (ОД, ТД)        Информатика    Олимова Е.Н.       (Ю)</t>
+        </is>
+      </c>
+      <c r="G33" s="33" t="inlineStr"/>
+      <c r="H33" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Математика      Ширнин А.Г. </t>
+        </is>
+      </c>
+      <c r="I33" s="33" t="inlineStr">
         <is>
           <t>Физическая культура                    Ритор Л.М.</t>
         </is>
       </c>
-      <c r="J33" s="49" t="inlineStr">
+      <c r="J33" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">Основы пенсионного законодательства РФ             Григорьев Д.В. </t>
         </is>
       </c>
-      <c r="K33" s="31" t="inlineStr">
+      <c r="K33" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Документационное  обеспечение управления       Иванова Ж.В.  </t>
         </is>
       </c>
-      <c r="L33" s="34" t="inlineStr">
+      <c r="L33" s="37" t="inlineStr">
         <is>
           <t>Физическая культура                    Ритор Л.М.</t>
         </is>
       </c>
-      <c r="M33" s="31" t="inlineStr">
+      <c r="M33" s="33" t="inlineStr">
         <is>
           <t>Основы финансовой грамотности    Кожевников В.Е.</t>
         </is>
       </c>
-      <c r="N33" s="33" t="inlineStr">
+      <c r="N33" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Логистика      Коломиец А.И. </t>
         </is>
       </c>
-      <c r="O33" s="21" t="inlineStr"/>
-      <c r="P33" s="29" t="n"/>
-      <c r="Q33" s="30" t="n">
+      <c r="O33" s="1" t="inlineStr"/>
+      <c r="P33" s="31" t="n"/>
+      <c r="Q33" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="R33" s="31" t="inlineStr">
+      <c r="R33" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Анатомия и физиология человека          Маклаков И.А. </t>
         </is>
       </c>
-      <c r="S33" s="31" t="inlineStr"/>
-      <c r="T33" s="31" t="inlineStr">
+      <c r="S33" s="33" t="inlineStr"/>
+      <c r="T33" s="33" t="inlineStr">
         <is>
           <t>Физическая культура                    Ритор Л.М.</t>
         </is>
       </c>
-      <c r="U33" s="31" t="inlineStr">
+      <c r="U33" s="33" t="inlineStr">
         <is>
           <t>Гигиена полости рта                Мхитарян Л.С.</t>
         </is>
       </c>
-      <c r="V33" s="31" t="inlineStr">
+      <c r="V33" s="33" t="inlineStr">
         <is>
           <t>Гигиена полости рта                Мхитарян Л.С.</t>
         </is>
       </c>
-      <c r="W33" s="31" t="inlineStr">
+      <c r="W33" s="33" t="inlineStr">
         <is>
           <t>Стоматологические заболевания и их профилактика Станишевская Д.Н.</t>
         </is>
       </c>
-      <c r="X33" s="32" t="inlineStr">
+      <c r="X33" s="34" t="inlineStr">
         <is>
           <t>Физическая культура                    Ритор Л.М.</t>
         </is>
       </c>
-      <c r="Y33" s="31" t="inlineStr">
+      <c r="Y33" s="33" t="inlineStr">
         <is>
           <t>Физическая культура                    Ритор Л.М.</t>
         </is>
       </c>
-      <c r="Z33" s="31" t="inlineStr">
+      <c r="Z33" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Общий уход за пациентами      Перова Н.И.        </t>
         </is>
       </c>
-      <c r="AA33" s="31" t="inlineStr">
+      <c r="AA33" s="33" t="inlineStr">
         <is>
           <t>Физическая культура                    Ритор Л.М.</t>
         </is>
       </c>
-      <c r="AB33" s="31" t="inlineStr">
+      <c r="AB33" s="33" t="inlineStr"/>
+      <c r="AC33" s="35" t="inlineStr"/>
+      <c r="AD33" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Технология маникюра Алексеенко Е.М.  </t>
+        </is>
+      </c>
+      <c r="AE33" s="33" t="inlineStr">
         <is>
           <t>Физическая культура                    Ритор Л.М.</t>
         </is>
       </c>
-      <c r="AC33" s="33" t="inlineStr">
-        <is>
-          <t>Физическая культура                    Ритор Л.М.</t>
-        </is>
-      </c>
-      <c r="AD33" s="33" t="inlineStr"/>
-      <c r="AE33" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Выполнение работ по профессии "Маникюрша"  Алексеенко Е.М.  </t>
-        </is>
-      </c>
-      <c r="AF33" s="31" t="inlineStr">
+      <c r="AF33" s="33" t="inlineStr">
         <is>
           <t>Технология коррекции тела     Березовикова А.В.</t>
         </is>
       </c>
-      <c r="AG33" s="31" t="inlineStr"/>
-      <c r="AH33" s="1" t="inlineStr"/>
+      <c r="AG33" s="33" t="inlineStr"/>
+      <c r="AH33" s="3" t="inlineStr"/>
     </row>
     <row r="34" ht="99.95" customHeight="1">
-      <c r="A34" s="24" t="n"/>
-      <c r="B34" s="25" t="n">
+      <c r="A34" s="26" t="n"/>
+      <c r="B34" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C34" s="26" t="n"/>
-      <c r="D34" s="26" t="n"/>
-      <c r="E34" s="26" t="n"/>
-      <c r="F34" s="26" t="n"/>
-      <c r="G34" s="26" t="n"/>
-      <c r="H34" s="26" t="n"/>
-      <c r="I34" s="26" t="n"/>
-      <c r="J34" s="26" t="n"/>
-      <c r="K34" s="26" t="n"/>
-      <c r="L34" s="35" t="n"/>
-      <c r="M34" s="26" t="n"/>
-      <c r="N34" s="28" t="n"/>
-      <c r="O34" s="21" t="inlineStr"/>
-      <c r="P34" s="29" t="n"/>
-      <c r="Q34" s="30" t="n">
+      <c r="C34" s="28" t="n"/>
+      <c r="D34" s="28" t="n"/>
+      <c r="E34" s="28" t="n"/>
+      <c r="F34" s="28" t="n"/>
+      <c r="G34" s="28" t="n"/>
+      <c r="H34" s="28" t="n"/>
+      <c r="I34" s="28" t="n"/>
+      <c r="J34" s="28" t="n"/>
+      <c r="K34" s="28" t="n"/>
+      <c r="L34" s="38" t="n"/>
+      <c r="M34" s="28" t="n"/>
+      <c r="N34" s="30" t="n"/>
+      <c r="O34" s="1" t="inlineStr"/>
+      <c r="P34" s="31" t="n"/>
+      <c r="Q34" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="R34" s="26" t="n"/>
-      <c r="S34" s="26" t="n"/>
-      <c r="T34" s="26" t="n"/>
-      <c r="U34" s="26" t="n"/>
-      <c r="V34" s="26" t="n"/>
-      <c r="W34" s="26" t="n"/>
-      <c r="X34" s="27" t="n"/>
-      <c r="Y34" s="26" t="n"/>
-      <c r="Z34" s="26" t="n"/>
-      <c r="AA34" s="26" t="n"/>
-      <c r="AB34" s="26" t="n"/>
-      <c r="AC34" s="28" t="n"/>
-      <c r="AD34" s="28" t="n"/>
-      <c r="AE34" s="26" t="n"/>
-      <c r="AF34" s="26" t="n"/>
-      <c r="AG34" s="26" t="n"/>
-      <c r="AH34" s="1" t="inlineStr"/>
+      <c r="R34" s="28" t="n"/>
+      <c r="S34" s="28" t="n"/>
+      <c r="T34" s="28" t="n"/>
+      <c r="U34" s="28" t="n"/>
+      <c r="V34" s="28" t="n"/>
+      <c r="W34" s="28" t="n"/>
+      <c r="X34" s="29" t="n"/>
+      <c r="Y34" s="28" t="n"/>
+      <c r="Z34" s="28" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="30" t="n"/>
+      <c r="AD34" s="30" t="n"/>
+      <c r="AE34" s="28" t="n"/>
+      <c r="AF34" s="28" t="n"/>
+      <c r="AG34" s="28" t="n"/>
+      <c r="AH34" s="3" t="inlineStr"/>
     </row>
     <row r="35" ht="99.95" customHeight="1">
-      <c r="A35" s="24" t="n"/>
-      <c r="B35" s="25" t="n">
+      <c r="A35" s="26" t="n"/>
+      <c r="B35" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="C35" s="31" t="inlineStr">
+      <c r="C35" s="33" t="inlineStr">
+        <is>
+          <t>Математика       Ширнин А.Г.</t>
+        </is>
+      </c>
+      <c r="D35" s="33" t="inlineStr">
+        <is>
+          <t>Право     Кожевников В.Е.</t>
+        </is>
+      </c>
+      <c r="E35" s="56" t="inlineStr"/>
+      <c r="F35" s="33" t="inlineStr">
+        <is>
+          <t>История                    Козлов Д.В.</t>
+        </is>
+      </c>
+      <c r="G35" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Химия        Морозова Е.Н. </t>
         </is>
       </c>
-      <c r="D35" s="31" t="inlineStr">
-        <is>
-          <t>Право     Кожевников В.Е.</t>
-        </is>
-      </c>
-      <c r="E35" s="31" t="inlineStr">
-        <is>
-          <t>История                    Козлов Д.В.</t>
-        </is>
-      </c>
-      <c r="F35" s="31" t="inlineStr"/>
-      <c r="G35" s="31" t="inlineStr">
-        <is>
-          <t>Математика       Ширнин А.Г.</t>
-        </is>
-      </c>
-      <c r="H35" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Основы безопасности и защиты Родины   Иванов В.В.  </t>
-        </is>
-      </c>
-      <c r="I35" s="31" t="inlineStr"/>
-      <c r="J35" s="49" t="inlineStr">
+      <c r="H35" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Химия        Морозова Е.Н. </t>
+        </is>
+      </c>
+      <c r="I35" s="33" t="inlineStr"/>
+      <c r="J35" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">Правовые основы медико-социальной экспертизы       Григорьев Д.В. </t>
         </is>
       </c>
-      <c r="K35" s="31" t="inlineStr"/>
-      <c r="L35" s="34" t="inlineStr">
+      <c r="K35" s="36" t="inlineStr"/>
+      <c r="L35" s="37" t="inlineStr">
         <is>
           <t>Моделирование логистических систем     Коломиец А.И.</t>
         </is>
       </c>
-      <c r="M35" s="31" t="inlineStr"/>
-      <c r="N35" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Информационные технологии в профессиональной деятельности     Олимова Е.Н. </t>
-        </is>
-      </c>
-      <c r="O35" s="21" t="inlineStr"/>
-      <c r="P35" s="29" t="n"/>
-      <c r="Q35" s="30" t="n">
+      <c r="M35" s="36" t="inlineStr"/>
+      <c r="N35" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Числитель Информационные технологии в профессиональной деятельности     Олимова Е.Н. </t>
+        </is>
+      </c>
+      <c r="O35" s="1" t="inlineStr"/>
+      <c r="P35" s="31" t="n"/>
+      <c r="Q35" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="R35" s="31" t="inlineStr"/>
-      <c r="S35" s="31" t="inlineStr">
+      <c r="R35" s="33" t="inlineStr"/>
+      <c r="S35" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Анатомия и физиология человека          Маклаков И.А. </t>
         </is>
       </c>
-      <c r="T35" s="31" t="inlineStr"/>
-      <c r="U35" s="31" t="inlineStr">
+      <c r="T35" s="33" t="inlineStr"/>
+      <c r="U35" s="33" t="inlineStr">
         <is>
           <t>Гигиена полости рта                Мхитарян Л.С.</t>
         </is>
       </c>
-      <c r="V35" s="31" t="inlineStr">
+      <c r="V35" s="33" t="inlineStr">
         <is>
           <t>Гигиена полости рта                Мхитарян Л.С.</t>
         </is>
       </c>
-      <c r="W35" s="31" t="inlineStr">
-        <is>
-          <t>Современные методики и материалы в профилактике стоматологических заболеваний  Станишевская Д.Н.</t>
-        </is>
-      </c>
-      <c r="X35" s="32" t="inlineStr"/>
-      <c r="Y35" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Технология изготовления несъемных и бюгельных протезов          Стецюк Д.В. </t>
-        </is>
-      </c>
-      <c r="Z35" s="31" t="inlineStr">
+      <c r="W35" s="33" t="inlineStr">
+        <is>
+          <t>Стоматологические заболевания и их профилактика Станишевская Д.Н.</t>
+        </is>
+      </c>
+      <c r="X35" s="34" t="inlineStr"/>
+      <c r="Y35" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Технология изготовления несъемных и бюгельных протезов       Стецюк Д.В. </t>
+        </is>
+      </c>
+      <c r="Z35" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Общий уход за пациентами       Перова Н.И.         </t>
         </is>
       </c>
-      <c r="AA35" s="31" t="inlineStr"/>
-      <c r="AB35" s="31" t="inlineStr">
-        <is>
-          <t>Санитария и гигиена в сфере услуг                Джокич Э.А.</t>
-        </is>
-      </c>
-      <c r="AC35" s="33" t="inlineStr">
+      <c r="AA35" s="33" t="inlineStr"/>
+      <c r="AB35" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">БЖД              Иванов В.В.  </t>
+        </is>
+      </c>
+      <c r="AC35" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Технология педикюра Алексеенко Е.М.  </t>
         </is>
       </c>
-      <c r="AD35" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Технология маникюра  Алексеенко Е.М.  </t>
-        </is>
-      </c>
-      <c r="AE35" s="31" t="inlineStr">
+      <c r="AD35" s="33" t="inlineStr"/>
+      <c r="AE35" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Экологические основы природопользования                                      Иванова Ж.В.   </t>
         </is>
       </c>
-      <c r="AF35" s="31" t="inlineStr"/>
-      <c r="AG35" s="31" t="inlineStr">
-        <is>
-          <t>Технология коррекции тела  Березовикова А.В.</t>
-        </is>
-      </c>
-      <c r="AH35" s="1" t="inlineStr"/>
+      <c r="AF35" s="33" t="inlineStr"/>
+      <c r="AG35" s="33" t="inlineStr">
+        <is>
+          <t>Технология коррекции тела     Березовикова А.В.</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
     </row>
     <row r="36" ht="99.95" customHeight="1">
-      <c r="A36" s="24" t="n"/>
-      <c r="B36" s="25" t="n">
+      <c r="A36" s="26" t="n"/>
+      <c r="B36" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="C36" s="26" t="n"/>
-      <c r="D36" s="26" t="n"/>
-      <c r="E36" s="26" t="n"/>
-      <c r="F36" s="26" t="n"/>
-      <c r="G36" s="26" t="n"/>
-      <c r="H36" s="26" t="n"/>
-      <c r="I36" s="26" t="n"/>
-      <c r="J36" s="26" t="n"/>
-      <c r="K36" s="26" t="n"/>
-      <c r="L36" s="35" t="n"/>
-      <c r="M36" s="26" t="n"/>
-      <c r="N36" s="26" t="n"/>
-      <c r="O36" s="21" t="inlineStr"/>
-      <c r="P36" s="29" t="n"/>
-      <c r="Q36" s="30" t="n">
+      <c r="C36" s="28" t="n"/>
+      <c r="D36" s="28" t="n"/>
+      <c r="E36" s="28" t="n"/>
+      <c r="F36" s="28" t="n"/>
+      <c r="G36" s="28" t="n"/>
+      <c r="H36" s="28" t="n"/>
+      <c r="I36" s="28" t="n"/>
+      <c r="J36" s="28" t="n"/>
+      <c r="K36" s="28" t="n"/>
+      <c r="L36" s="38" t="n"/>
+      <c r="M36" s="28" t="n"/>
+      <c r="N36" s="35" t="inlineStr"/>
+      <c r="O36" s="1" t="inlineStr"/>
+      <c r="P36" s="31" t="n"/>
+      <c r="Q36" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="R36" s="26" t="n"/>
-      <c r="S36" s="26" t="n"/>
-      <c r="T36" s="26" t="n"/>
-      <c r="U36" s="26" t="n"/>
-      <c r="V36" s="26" t="n"/>
-      <c r="W36" s="26" t="n"/>
-      <c r="X36" s="27" t="n"/>
-      <c r="Y36" s="26" t="n"/>
-      <c r="Z36" s="26" t="n"/>
-      <c r="AA36" s="26" t="n"/>
-      <c r="AB36" s="26" t="n"/>
-      <c r="AC36" s="28" t="n"/>
-      <c r="AD36" s="26" t="n"/>
-      <c r="AE36" s="26" t="n"/>
-      <c r="AF36" s="26" t="n"/>
-      <c r="AG36" s="26" t="n"/>
-      <c r="AH36" s="1" t="inlineStr"/>
+      <c r="R36" s="28" t="n"/>
+      <c r="S36" s="28" t="n"/>
+      <c r="T36" s="28" t="n"/>
+      <c r="U36" s="28" t="n"/>
+      <c r="V36" s="28" t="n"/>
+      <c r="W36" s="28" t="n"/>
+      <c r="X36" s="29" t="n"/>
+      <c r="Y36" s="28" t="n"/>
+      <c r="Z36" s="28" t="n"/>
+      <c r="AA36" s="28" t="n"/>
+      <c r="AB36" s="28" t="n"/>
+      <c r="AC36" s="30" t="n"/>
+      <c r="AD36" s="28" t="n"/>
+      <c r="AE36" s="28" t="n"/>
+      <c r="AF36" s="28" t="n"/>
+      <c r="AG36" s="28" t="n"/>
+      <c r="AH36" s="3" t="inlineStr"/>
     </row>
     <row r="37" ht="99.95" customHeight="1">
-      <c r="A37" s="24" t="n"/>
-      <c r="B37" s="25" t="n">
+      <c r="A37" s="26" t="n"/>
+      <c r="B37" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="C37" s="36" t="inlineStr">
+      <c r="C37" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> Информатика    Олимова Е.Н.          2 подгруппа</t>
         </is>
       </c>
-      <c r="D37" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Основы безопасности и защиты Родины   Иванов В.В.  </t>
-        </is>
-      </c>
-      <c r="E37" s="36" t="inlineStr">
-        <is>
-          <t>Право     Кожевников В.Е.</t>
-        </is>
-      </c>
-      <c r="F37" s="36" t="inlineStr"/>
-      <c r="G37" s="36" t="inlineStr">
+      <c r="D37" s="39" t="inlineStr">
+        <is>
+          <t>Обществознание    Кожевников В.Е.</t>
+        </is>
+      </c>
+      <c r="E37" s="43" t="inlineStr"/>
+      <c r="F37" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Химия        Морозова Е.Н. </t>
         </is>
       </c>
-      <c r="H37" s="31" t="inlineStr">
+      <c r="G37" s="39" t="inlineStr">
         <is>
           <t>Математика       Ширнин А.Г.</t>
         </is>
       </c>
-      <c r="I37" s="36" t="inlineStr"/>
-      <c r="J37" s="36" t="inlineStr">
+      <c r="H37" s="39" t="inlineStr"/>
+      <c r="I37" s="39" t="inlineStr"/>
+      <c r="J37" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Правовые основы медико-социальной экспертизы       Григорьев Д.В. </t>
         </is>
       </c>
-      <c r="K37" s="31" t="inlineStr"/>
-      <c r="L37" s="59" t="inlineStr">
+      <c r="K37" s="33" t="inlineStr"/>
+      <c r="L37" s="65" t="inlineStr">
         <is>
           <t>Распределительная логистика    Коломиец А.И.</t>
         </is>
       </c>
-      <c r="M37" s="31" t="inlineStr"/>
-      <c r="N37" s="36" t="inlineStr"/>
-      <c r="O37" s="21" t="inlineStr"/>
-      <c r="P37" s="29" t="n"/>
-      <c r="Q37" s="30" t="n">
+      <c r="M37" s="33" t="inlineStr"/>
+      <c r="N37" s="39" t="inlineStr"/>
+      <c r="O37" s="1" t="inlineStr"/>
+      <c r="P37" s="31" t="n"/>
+      <c r="Q37" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="R37" s="36" t="inlineStr"/>
-      <c r="S37" s="36" t="inlineStr">
+      <c r="R37" s="33" t="inlineStr"/>
+      <c r="S37" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Анатомия и физиология человека          Маклаков И.А. </t>
         </is>
       </c>
-      <c r="T37" s="36" t="inlineStr"/>
-      <c r="U37" s="36" t="inlineStr">
+      <c r="T37" s="39" t="inlineStr"/>
+      <c r="U37" s="39" t="inlineStr">
         <is>
           <t>Гигиена полости рта                Мхитарян Л.С.</t>
         </is>
       </c>
-      <c r="V37" s="36" t="inlineStr">
+      <c r="V37" s="39" t="inlineStr">
         <is>
           <t>Гигиена полости рта                Мхитарян Л.С.</t>
         </is>
       </c>
-      <c r="W37" s="36" t="inlineStr">
-        <is>
-          <t>Современные методики и материалы в профилактике стоматологических заболеваний  Станишевская Д.Н.</t>
-        </is>
-      </c>
-      <c r="X37" s="38" t="inlineStr"/>
-      <c r="Y37" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Технология изготовления несъемных и бюгельных протезов          Стецюк Д.В. </t>
-        </is>
-      </c>
-      <c r="Z37" s="36" t="inlineStr">
+      <c r="W37" s="39" t="inlineStr">
+        <is>
+          <t>Стоматологические заболевания и их профилактика Станишевская Д.Н.</t>
+        </is>
+      </c>
+      <c r="X37" s="41" t="inlineStr"/>
+      <c r="Y37" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Технология изготовления несъемных и бюгельных протезов        Стецюк Д.В.  </t>
+        </is>
+      </c>
+      <c r="Z37" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Общий уход за пациентами          Перова Н.И.     </t>
         </is>
       </c>
-      <c r="AA37" s="36" t="inlineStr"/>
-      <c r="AB37" s="37" t="inlineStr">
+      <c r="AA37" s="39" t="inlineStr"/>
+      <c r="AB37" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">Технология педикюра Алексеенко Е.М.  </t>
         </is>
       </c>
-      <c r="AC37" s="36" t="inlineStr">
-        <is>
-          <t>Санитария и гигиена в сфере услуг                Джокич Э.А.</t>
-        </is>
-      </c>
-      <c r="AD37" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Технология маникюра  Алексеенко Е.М.  </t>
-        </is>
-      </c>
-      <c r="AE37" s="36" t="inlineStr"/>
-      <c r="AF37" s="36" t="inlineStr"/>
-      <c r="AG37" s="36" t="inlineStr">
-        <is>
-          <t>Технология коррекции тела Березовикова А.В.</t>
-        </is>
-      </c>
-      <c r="AH37" s="1" t="inlineStr"/>
+      <c r="AC37" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">БЖД              Иванов В.В.  </t>
+        </is>
+      </c>
+      <c r="AD37" s="39" t="inlineStr"/>
+      <c r="AE37" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Экологические основы природопользования                                      Иванова Ж.В.   </t>
+        </is>
+      </c>
+      <c r="AF37" s="39" t="inlineStr"/>
+      <c r="AG37" s="40" t="inlineStr">
+        <is>
+          <t>Технология коррекции тела     Березовикова А.В.</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
     </row>
     <row r="38" ht="99.95" customHeight="1" thickBot="1">
-      <c r="A38" s="26" t="n"/>
-      <c r="B38" s="25" t="n">
+      <c r="A38" s="28" t="n"/>
+      <c r="B38" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="C38" s="41" t="n"/>
-      <c r="D38" s="41" t="n"/>
-      <c r="E38" s="41" t="n"/>
-      <c r="F38" s="41" t="n"/>
-      <c r="G38" s="41" t="n"/>
-      <c r="H38" s="26" t="n"/>
-      <c r="I38" s="41" t="n"/>
-      <c r="J38" s="41" t="n"/>
-      <c r="K38" s="26" t="n"/>
-      <c r="L38" s="60" t="n"/>
-      <c r="M38" s="26" t="n"/>
-      <c r="N38" s="41" t="n"/>
-      <c r="O38" s="21" t="inlineStr"/>
-      <c r="P38" s="44" t="n"/>
-      <c r="Q38" s="45" t="n">
+      <c r="C38" s="45" t="n"/>
+      <c r="D38" s="45" t="n"/>
+      <c r="E38" s="45" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="45" t="n"/>
+      <c r="H38" s="45" t="n"/>
+      <c r="I38" s="45" t="n"/>
+      <c r="J38" s="45" t="n"/>
+      <c r="K38" s="28" t="n"/>
+      <c r="L38" s="66" t="n"/>
+      <c r="M38" s="28" t="n"/>
+      <c r="N38" s="45" t="n"/>
+      <c r="O38" s="1" t="inlineStr"/>
+      <c r="P38" s="48" t="n"/>
+      <c r="Q38" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="R38" s="41" t="n"/>
-      <c r="S38" s="41" t="n"/>
-      <c r="T38" s="41" t="n"/>
-      <c r="U38" s="41" t="n"/>
-      <c r="V38" s="41" t="n"/>
-      <c r="W38" s="41" t="n"/>
-      <c r="X38" s="42" t="n"/>
-      <c r="Y38" s="41" t="n"/>
-      <c r="Z38" s="41" t="n"/>
-      <c r="AA38" s="41" t="n"/>
-      <c r="AB38" s="24" t="n"/>
-      <c r="AC38" s="41" t="n"/>
-      <c r="AD38" s="41" t="n"/>
-      <c r="AE38" s="41" t="n"/>
-      <c r="AF38" s="41" t="n"/>
-      <c r="AG38" s="41" t="n"/>
-      <c r="AH38" s="1" t="inlineStr"/>
+      <c r="R38" s="28" t="n"/>
+      <c r="S38" s="45" t="n"/>
+      <c r="T38" s="45" t="n"/>
+      <c r="U38" s="45" t="n"/>
+      <c r="V38" s="45" t="n"/>
+      <c r="W38" s="45" t="n"/>
+      <c r="X38" s="46" t="n"/>
+      <c r="Y38" s="45" t="n"/>
+      <c r="Z38" s="45" t="n"/>
+      <c r="AA38" s="45" t="n"/>
+      <c r="AB38" s="26" t="n"/>
+      <c r="AC38" s="45" t="n"/>
+      <c r="AD38" s="45" t="n"/>
+      <c r="AE38" s="45" t="n"/>
+      <c r="AF38" s="45" t="n"/>
+      <c r="AG38" s="26" t="n"/>
+      <c r="AH38" s="3" t="inlineStr"/>
     </row>
     <row r="39" ht="99.95" customHeight="1">
-      <c r="A39" s="46" t="inlineStr">
+      <c r="A39" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">пятница </t>
         </is>
       </c>
-      <c r="B39" s="25" t="n">
+      <c r="B39" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="18" t="inlineStr"/>
-      <c r="D39" s="18" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr"/>
+      <c r="D39" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Химия        Морозова Е.Н. </t>
         </is>
       </c>
-      <c r="E39" s="18" t="inlineStr">
+      <c r="E39" s="19" t="inlineStr">
         <is>
           <t>Право     Кожевников В.Е.</t>
         </is>
       </c>
-      <c r="F39" s="18" t="inlineStr">
+      <c r="F39" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Основы безопасности и защиты Родины   Иванов В.В.  </t>
         </is>
       </c>
-      <c r="G39" s="18" t="inlineStr">
-        <is>
-          <t>Иностранный язык            Шарипов И.Н.</t>
-        </is>
-      </c>
-      <c r="H39" s="18" t="inlineStr">
+      <c r="G39" s="19" t="inlineStr">
         <is>
           <t>Литература       Исаева Г.А.</t>
         </is>
       </c>
-      <c r="I39" s="18" t="inlineStr"/>
-      <c r="J39" s="18" t="inlineStr">
-        <is>
-          <t>Право социального обеспечения                             Лебедева М.Л.</t>
-        </is>
-      </c>
-      <c r="K39" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">БЖД         Ходаковский В.В. </t>
-        </is>
-      </c>
-      <c r="L39" s="18" t="inlineStr"/>
-      <c r="M39" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">БЖД         Ходаковский В.В. </t>
-        </is>
-      </c>
-      <c r="N39" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Маркетинг  Систейкина Е.Е.</t>
-        </is>
-      </c>
-      <c r="O39" s="21" t="inlineStr"/>
-      <c r="P39" s="22" t="inlineStr">
+      <c r="H39" s="19" t="inlineStr">
+        <is>
+          <t>Литература       Исаева Г.А.</t>
+        </is>
+      </c>
+      <c r="I39" s="19" t="inlineStr">
+        <is>
+          <t>Жилищное право                          Лебедева М.Л.</t>
+        </is>
+      </c>
+      <c r="J39" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Иностранный язык в профессиональной деятельности        Шарипов И.Н. </t>
+        </is>
+      </c>
+      <c r="K39" s="52" t="inlineStr">
+        <is>
+          <t>БЖД                                    Ходаковский В.В.</t>
+        </is>
+      </c>
+      <c r="L39" s="19" t="inlineStr"/>
+      <c r="M39" s="52" t="inlineStr">
+        <is>
+          <t>БЖД                                    Ходаковский В.В.</t>
+        </is>
+      </c>
+      <c r="N39" s="19" t="inlineStr">
+        <is>
+          <t>Маркетинг  Систейкина Е.Е.</t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="inlineStr"/>
+      <c r="P39" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">пятница </t>
         </is>
       </c>
-      <c r="Q39" s="51" t="n">
+      <c r="Q39" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="R39" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">История России   Козлов Д.В. </t>
-        </is>
-      </c>
-      <c r="S39" s="18" t="inlineStr">
+      <c r="R39" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Числитель              История России   Козлов Д.В. </t>
+        </is>
+      </c>
+      <c r="S39" s="19" t="inlineStr">
         <is>
           <t>Клиническое материаловедение  Станишевская Д.Н.</t>
         </is>
       </c>
-      <c r="T39" s="18" t="inlineStr"/>
-      <c r="U39" s="18" t="inlineStr"/>
-      <c r="V39" s="18" t="inlineStr"/>
-      <c r="W39" s="18" t="inlineStr"/>
-      <c r="X39" s="18" t="inlineStr">
+      <c r="T39" s="19" t="inlineStr"/>
+      <c r="U39" s="19" t="inlineStr"/>
+      <c r="V39" s="19" t="inlineStr"/>
+      <c r="W39" s="19" t="inlineStr"/>
+      <c r="X39" s="19" t="inlineStr">
         <is>
           <t>Анатомия и физиология человека с курсом биомеханики зубочелюстной системы                    Горин А.А.</t>
         </is>
       </c>
-      <c r="Y39" s="18" t="inlineStr"/>
-      <c r="Z39" s="18" t="inlineStr"/>
-      <c r="AA39" s="18" t="inlineStr"/>
-      <c r="AB39" s="18" t="inlineStr">
+      <c r="Y39" s="19" t="inlineStr"/>
+      <c r="Z39" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Анатомия и физиология человека            Маклаков И.А. </t>
+        </is>
+      </c>
+      <c r="AA39" s="21" t="inlineStr"/>
+      <c r="AB39" s="19" t="inlineStr">
+        <is>
+          <t>Санитария и гигиена в сфере услуг                Джокич Э.А.</t>
+        </is>
+      </c>
+      <c r="AC39" s="19" t="inlineStr">
         <is>
           <t>Основы латинского языка с медицинской терминологией       Дремлюгина Л.А.</t>
         </is>
       </c>
-      <c r="AC39" s="18" t="inlineStr">
-        <is>
-          <t>Санитария и гигиена в сфере услуг                Джокич Э.А.</t>
-        </is>
-      </c>
-      <c r="AD39" s="19" t="inlineStr"/>
-      <c r="AE39" s="18" t="inlineStr">
+      <c r="AD39" s="67" t="inlineStr"/>
+      <c r="AE39" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Выполнение работ по профессии "Педикюрша"  Алексеенко Е.М.  </t>
         </is>
       </c>
-      <c r="AF39" s="19" t="inlineStr">
+      <c r="AF39" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Технология визажа Ермолаева И.В.                                               </t>
         </is>
       </c>
-      <c r="AG39" s="18" t="inlineStr"/>
-      <c r="AH39" s="1" t="inlineStr"/>
+      <c r="AG39" s="21" t="inlineStr"/>
+      <c r="AH39" s="3" t="inlineStr"/>
     </row>
     <row r="40" ht="99.95" customHeight="1">
-      <c r="A40" s="24" t="n"/>
-      <c r="B40" s="25" t="n">
+      <c r="A40" s="26" t="n"/>
+      <c r="B40" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="26" t="n"/>
-      <c r="D40" s="26" t="n"/>
-      <c r="E40" s="26" t="n"/>
-      <c r="F40" s="26" t="n"/>
-      <c r="G40" s="26" t="n"/>
-      <c r="H40" s="26" t="n"/>
-      <c r="I40" s="26" t="n"/>
-      <c r="J40" s="26" t="n"/>
-      <c r="K40" s="26" t="n"/>
-      <c r="L40" s="26" t="n"/>
-      <c r="M40" s="26" t="n"/>
-      <c r="N40" s="26" t="n"/>
-      <c r="O40" s="21" t="inlineStr"/>
-      <c r="P40" s="29" t="n"/>
-      <c r="Q40" s="30" t="n">
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="28" t="n"/>
+      <c r="H40" s="28" t="n"/>
+      <c r="I40" s="28" t="n"/>
+      <c r="J40" s="28" t="n"/>
+      <c r="K40" s="28" t="n"/>
+      <c r="L40" s="28" t="n"/>
+      <c r="M40" s="28" t="n"/>
+      <c r="N40" s="28" t="n"/>
+      <c r="O40" s="1" t="inlineStr"/>
+      <c r="P40" s="31" t="n"/>
+      <c r="Q40" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="R40" s="26" t="n"/>
-      <c r="S40" s="26" t="n"/>
-      <c r="T40" s="26" t="n"/>
-      <c r="U40" s="26" t="n"/>
-      <c r="V40" s="26" t="n"/>
-      <c r="W40" s="26" t="n"/>
-      <c r="X40" s="26" t="n"/>
-      <c r="Y40" s="26" t="n"/>
-      <c r="Z40" s="26" t="n"/>
-      <c r="AA40" s="26" t="n"/>
-      <c r="AB40" s="26" t="n"/>
-      <c r="AC40" s="26" t="n"/>
-      <c r="AD40" s="27" t="n"/>
-      <c r="AE40" s="26" t="n"/>
-      <c r="AF40" s="27" t="n"/>
-      <c r="AG40" s="26" t="n"/>
-      <c r="AH40" s="1" t="inlineStr"/>
+      <c r="R40" s="33" t="inlineStr"/>
+      <c r="S40" s="28" t="n"/>
+      <c r="T40" s="28" t="n"/>
+      <c r="U40" s="28" t="n"/>
+      <c r="V40" s="28" t="n"/>
+      <c r="W40" s="28" t="n"/>
+      <c r="X40" s="28" t="n"/>
+      <c r="Y40" s="28" t="n"/>
+      <c r="Z40" s="28" t="n"/>
+      <c r="AA40" s="28" t="n"/>
+      <c r="AB40" s="28" t="n"/>
+      <c r="AC40" s="28" t="n"/>
+      <c r="AD40" s="29" t="n"/>
+      <c r="AE40" s="28" t="n"/>
+      <c r="AF40" s="29" t="n"/>
+      <c r="AG40" s="28" t="n"/>
+      <c r="AH40" s="3" t="inlineStr"/>
     </row>
     <row r="41" ht="99.95" customHeight="1">
-      <c r="A41" s="24" t="n"/>
-      <c r="B41" s="25" t="n">
+      <c r="A41" s="26" t="n"/>
+      <c r="B41" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="C41" s="31" t="inlineStr"/>
-      <c r="D41" s="31" t="inlineStr">
+      <c r="C41" s="36" t="inlineStr"/>
+      <c r="D41" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Биология              Морозова Е.Н. </t>
         </is>
       </c>
-      <c r="E41" s="31" t="inlineStr">
+      <c r="E41" s="33" t="inlineStr">
         <is>
           <t>Математика       Ширнин А.Г.</t>
         </is>
       </c>
-      <c r="F41" s="31" t="inlineStr">
+      <c r="F41" s="33" t="inlineStr">
         <is>
           <t>Литература       Исаева Г.А.</t>
         </is>
       </c>
-      <c r="G41" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Право     Кожевников В.Е.</t>
-        </is>
-      </c>
-      <c r="H41" s="32" t="inlineStr">
-        <is>
-          <t>Иностранный язык            Шарипов И.Н.</t>
-        </is>
-      </c>
-      <c r="I41" s="31" t="inlineStr"/>
-      <c r="J41" s="31" t="inlineStr">
-        <is>
-          <t>Жилищное право                          Лебедева М.Л.</t>
-        </is>
-      </c>
-      <c r="K41" s="31" t="inlineStr">
+      <c r="G41" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Иностранный язык            Шарипов И.Н. </t>
+        </is>
+      </c>
+      <c r="H41" s="34" t="inlineStr">
+        <is>
+          <t>Право     Кожевников В.Е.</t>
+        </is>
+      </c>
+      <c r="I41" s="33" t="inlineStr">
+        <is>
+          <t>Гражданское  право                   Лебедева М.Л.</t>
+        </is>
+      </c>
+      <c r="J41" s="33" t="inlineStr">
+        <is>
+          <t>Статистика Систейкина Е.Е.</t>
+        </is>
+      </c>
+      <c r="K41" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Экономика организации    Иванов В.В.  </t>
         </is>
       </c>
-      <c r="L41" s="31" t="inlineStr"/>
-      <c r="M41" s="31" t="inlineStr">
+      <c r="L41" s="33" t="inlineStr"/>
+      <c r="M41" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Экономика и основы анализа финансово - хозяйственной деятельности торговой организации  Иванов В.В.  </t>
         </is>
       </c>
-      <c r="N41" s="31" t="inlineStr">
-        <is>
-          <t>Маркетинг  Систейкина Е.Е.</t>
-        </is>
-      </c>
-      <c r="O41" s="21" t="inlineStr"/>
-      <c r="P41" s="29" t="n"/>
-      <c r="Q41" s="30" t="n">
+      <c r="N41" s="33" t="inlineStr">
+        <is>
+          <t>Статистика Систейкина Е.Е.</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr"/>
+      <c r="P41" s="31" t="n"/>
+      <c r="Q41" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="R41" s="31" t="inlineStr">
-        <is>
-          <t>Основы латинского языка с медицинской терминологией       Дремлюгина Л.А.</t>
-        </is>
-      </c>
-      <c r="S41" s="31" t="inlineStr">
+      <c r="R41" s="33" t="inlineStr">
+        <is>
+          <t>Числитель             Основы латинского языка с медицинской терминологией       Дремлюгина Л.А.</t>
+        </is>
+      </c>
+      <c r="S41" s="33" t="inlineStr">
         <is>
           <t>Клиническое материаловедение  Станишевская Д.Н.</t>
         </is>
       </c>
-      <c r="T41" s="31" t="inlineStr"/>
-      <c r="U41" s="31" t="inlineStr"/>
-      <c r="V41" s="31" t="inlineStr"/>
-      <c r="W41" s="31" t="inlineStr"/>
-      <c r="X41" s="31" t="inlineStr">
+      <c r="T41" s="33" t="inlineStr"/>
+      <c r="U41" s="33" t="inlineStr"/>
+      <c r="V41" s="33" t="inlineStr"/>
+      <c r="W41" s="33" t="inlineStr"/>
+      <c r="X41" s="33" t="inlineStr">
         <is>
           <t>Зуботехническое материаловедение с курсом охраны труда и техники безопасности   Горин А.А.</t>
         </is>
       </c>
-      <c r="Y41" s="31" t="inlineStr"/>
-      <c r="Z41" s="31" t="inlineStr"/>
-      <c r="AA41" s="31" t="inlineStr"/>
-      <c r="AB41" s="31" t="inlineStr">
+      <c r="Y41" s="33" t="inlineStr"/>
+      <c r="Z41" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Генетика с основами медицинской генетики  Маклаков И.А. </t>
+        </is>
+      </c>
+      <c r="AA41" s="36" t="inlineStr"/>
+      <c r="AB41" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> История России   Козлов Д.В. </t>
+        </is>
+      </c>
+      <c r="AC41" s="33" t="inlineStr">
         <is>
           <t>Санитария и гигиена в сфере услуг                Джокич Э.А.</t>
         </is>
       </c>
-      <c r="AC41" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> История России   Козлов Д.В. </t>
-        </is>
-      </c>
-      <c r="AD41" s="32" t="inlineStr"/>
-      <c r="AE41" s="31" t="inlineStr">
+      <c r="AD41" s="57" t="inlineStr"/>
+      <c r="AE41" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Выполнение работ по профессии "Педикюрша"  Алексеенко Е.М.  </t>
         </is>
       </c>
-      <c r="AF41" s="32" t="inlineStr">
+      <c r="AF41" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">Технология визажа Ермолаева И.В.                                               </t>
         </is>
       </c>
-      <c r="AG41" s="31" t="inlineStr"/>
-      <c r="AH41" s="1" t="inlineStr"/>
+      <c r="AG41" s="36" t="inlineStr"/>
+      <c r="AH41" s="3" t="inlineStr"/>
     </row>
     <row r="42" ht="99.95" customHeight="1">
-      <c r="A42" s="24" t="n"/>
-      <c r="B42" s="25" t="n">
+      <c r="A42" s="26" t="n"/>
+      <c r="B42" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C42" s="26" t="n"/>
-      <c r="D42" s="26" t="n"/>
-      <c r="E42" s="26" t="n"/>
-      <c r="F42" s="26" t="n"/>
-      <c r="G42" s="28" t="n"/>
-      <c r="H42" s="27" t="n"/>
-      <c r="I42" s="26" t="n"/>
-      <c r="J42" s="26" t="n"/>
-      <c r="K42" s="26" t="n"/>
-      <c r="L42" s="26" t="n"/>
-      <c r="M42" s="26" t="n"/>
-      <c r="N42" s="26" t="n"/>
-      <c r="O42" s="21" t="inlineStr"/>
-      <c r="P42" s="29" t="n"/>
-      <c r="Q42" s="30" t="n">
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="28" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="30" t="n"/>
+      <c r="H42" s="29" t="n"/>
+      <c r="I42" s="28" t="n"/>
+      <c r="J42" s="28" t="n"/>
+      <c r="K42" s="28" t="n"/>
+      <c r="L42" s="28" t="n"/>
+      <c r="M42" s="28" t="n"/>
+      <c r="N42" s="28" t="n"/>
+      <c r="O42" s="1" t="inlineStr"/>
+      <c r="P42" s="31" t="n"/>
+      <c r="Q42" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="R42" s="26" t="n"/>
-      <c r="S42" s="26" t="n"/>
-      <c r="T42" s="26" t="n"/>
-      <c r="U42" s="26" t="n"/>
-      <c r="V42" s="26" t="n"/>
-      <c r="W42" s="26" t="n"/>
-      <c r="X42" s="26" t="n"/>
-      <c r="Y42" s="26" t="n"/>
-      <c r="Z42" s="26" t="n"/>
-      <c r="AA42" s="26" t="n"/>
-      <c r="AB42" s="26" t="n"/>
-      <c r="AC42" s="26" t="n"/>
-      <c r="AD42" s="27" t="n"/>
-      <c r="AE42" s="26" t="n"/>
-      <c r="AF42" s="27" t="n"/>
-      <c r="AG42" s="26" t="n"/>
-      <c r="AH42" s="1" t="inlineStr"/>
+      <c r="R42" s="33" t="inlineStr"/>
+      <c r="S42" s="28" t="n"/>
+      <c r="T42" s="28" t="n"/>
+      <c r="U42" s="28" t="n"/>
+      <c r="V42" s="28" t="n"/>
+      <c r="W42" s="28" t="n"/>
+      <c r="X42" s="28" t="n"/>
+      <c r="Y42" s="28" t="n"/>
+      <c r="Z42" s="28" t="n"/>
+      <c r="AA42" s="28" t="n"/>
+      <c r="AB42" s="28" t="n"/>
+      <c r="AC42" s="28" t="n"/>
+      <c r="AD42" s="29" t="n"/>
+      <c r="AE42" s="28" t="n"/>
+      <c r="AF42" s="29" t="n"/>
+      <c r="AG42" s="28" t="n"/>
+      <c r="AH42" s="3" t="inlineStr"/>
     </row>
     <row r="43" ht="99.95" customHeight="1">
-      <c r="A43" s="24" t="n"/>
-      <c r="B43" s="25" t="n">
+      <c r="A43" s="26" t="n"/>
+      <c r="B43" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="C43" s="31" t="inlineStr">
+      <c r="C43" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Химия        Морозова Е.Н. </t>
         </is>
       </c>
-      <c r="D43" s="31" t="inlineStr"/>
-      <c r="E43" s="31" t="inlineStr">
+      <c r="D43" s="36" t="inlineStr"/>
+      <c r="E43" s="33" t="inlineStr">
         <is>
           <t>Литература       Исаева Г.А.</t>
         </is>
       </c>
-      <c r="F43" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Иностранный язык            Шарипов И.Н. </t>
-        </is>
-      </c>
-      <c r="G43" s="33" t="inlineStr">
+      <c r="F43" s="33" t="inlineStr"/>
+      <c r="G43" s="35" t="inlineStr">
         <is>
           <t>Математика       Ширнин А.Г.</t>
         </is>
       </c>
-      <c r="H43" s="33" t="inlineStr">
+      <c r="H43" s="35" t="inlineStr">
         <is>
           <t>Математика       Ширнин А.Г.</t>
         </is>
       </c>
-      <c r="I43" s="31" t="inlineStr">
-        <is>
-          <t>Гражданское  право                   Лебедева М.Л.</t>
-        </is>
-      </c>
-      <c r="J43" s="31" t="inlineStr">
-        <is>
-          <t>Статистика Систейкина Е.Е.</t>
-        </is>
-      </c>
-      <c r="K43" s="31" t="inlineStr">
+      <c r="I43" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Иностранный язык в профессиональной деятельности        Шарипов И.Н. </t>
+        </is>
+      </c>
+      <c r="J43" s="33" t="inlineStr">
+        <is>
+          <t>Право социального обеспечения                             Лебедева М.Л.</t>
+        </is>
+      </c>
+      <c r="K43" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Налоги и налогообложение Иванов В.В. </t>
         </is>
       </c>
-      <c r="L43" s="31" t="inlineStr"/>
-      <c r="M43" s="31" t="inlineStr">
+      <c r="L43" s="33" t="inlineStr"/>
+      <c r="M43" s="33" t="inlineStr">
         <is>
           <t>Основы финансовой грамотности    Кожевников В.Е.</t>
         </is>
       </c>
-      <c r="N43" s="31" t="inlineStr">
-        <is>
-          <t>Статистика Систейкина Е.Е.</t>
-        </is>
-      </c>
-      <c r="O43" s="21" t="inlineStr"/>
-      <c r="P43" s="29" t="n"/>
-      <c r="Q43" s="30" t="n">
+      <c r="N43" s="33" t="inlineStr">
+        <is>
+          <t>Маркетинг  Систейкина Е.Е.</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="inlineStr"/>
+      <c r="P43" s="31" t="n"/>
+      <c r="Q43" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="R43" s="31" t="inlineStr">
+      <c r="R43" s="33" t="inlineStr">
         <is>
           <t>Клиническое материаловедение  Станишевская Д.Н.</t>
         </is>
       </c>
-      <c r="S43" s="31" t="inlineStr">
-        <is>
-          <t>Основы латинского языка с медицинской терминологией       Дремлюгина Л.А.</t>
-        </is>
-      </c>
-      <c r="T43" s="31" t="inlineStr"/>
-      <c r="U43" s="31" t="inlineStr"/>
-      <c r="V43" s="31" t="inlineStr"/>
-      <c r="W43" s="31" t="inlineStr"/>
-      <c r="X43" s="32" t="inlineStr">
+      <c r="S43" s="33" t="inlineStr">
+        <is>
+          <t>Числитель             Основы латинского языка с медицинской терминологией       Дремлюгина Л.А.</t>
+        </is>
+      </c>
+      <c r="T43" s="33" t="inlineStr"/>
+      <c r="U43" s="33" t="inlineStr"/>
+      <c r="V43" s="33" t="inlineStr">
+        <is>
+          <t>Клиническое материаловедение  Станишевская Д.Н.</t>
+        </is>
+      </c>
+      <c r="W43" s="36" t="inlineStr"/>
+      <c r="X43" s="34" t="inlineStr">
         <is>
           <t>Технология изготовления съемных пластиночных  протезов        Горин А.А.</t>
         </is>
       </c>
-      <c r="Y43" s="31" t="inlineStr"/>
-      <c r="Z43" s="31" t="inlineStr">
+      <c r="Y43" s="33" t="inlineStr"/>
+      <c r="Z43" s="33" t="inlineStr"/>
+      <c r="AA43" s="36" t="inlineStr"/>
+      <c r="AB43" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Анатомия и физиология человека          Маклаков И.А. </t>
+        </is>
+      </c>
+      <c r="AC43" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve"> История России   Козлов Д.В. </t>
         </is>
       </c>
-      <c r="AA43" s="31" t="inlineStr"/>
-      <c r="AB43" s="31" t="inlineStr"/>
-      <c r="AC43" s="31" t="inlineStr"/>
-      <c r="AD43" s="32" t="inlineStr">
+      <c r="AD43" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">Выполнение работ по профессии "Педикюрша"  Алексеенко Е.М.  </t>
         </is>
       </c>
-      <c r="AE43" s="31" t="inlineStr">
+      <c r="AE43" s="33" t="inlineStr">
         <is>
           <t>Эстетические процедуры коррекции, эпиляции                   Джокич Э.А.</t>
         </is>
       </c>
-      <c r="AF43" s="32" t="inlineStr"/>
-      <c r="AG43" s="31" t="inlineStr">
+      <c r="AF43" s="57" t="inlineStr"/>
+      <c r="AG43" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Технология визажа Ермолаева И.В.                                               </t>
         </is>
       </c>
-      <c r="AH43" s="1" t="inlineStr"/>
+      <c r="AH43" s="3" t="inlineStr"/>
     </row>
     <row r="44" ht="99.95" customHeight="1">
-      <c r="A44" s="24" t="n"/>
-      <c r="B44" s="25" t="n">
+      <c r="A44" s="26" t="n"/>
+      <c r="B44" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="C44" s="26" t="n"/>
-      <c r="D44" s="26" t="n"/>
-      <c r="E44" s="26" t="n"/>
-      <c r="F44" s="26" t="n"/>
-      <c r="G44" s="28" t="n"/>
-      <c r="H44" s="28" t="n"/>
-      <c r="I44" s="26" t="n"/>
-      <c r="J44" s="26" t="n"/>
-      <c r="K44" s="26" t="n"/>
-      <c r="L44" s="26" t="n"/>
-      <c r="M44" s="26" t="n"/>
-      <c r="N44" s="26" t="n"/>
-      <c r="O44" s="21" t="inlineStr"/>
-      <c r="P44" s="29" t="n"/>
-      <c r="Q44" s="30" t="n">
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="28" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="30" t="n"/>
+      <c r="H44" s="30" t="n"/>
+      <c r="I44" s="28" t="n"/>
+      <c r="J44" s="28" t="n"/>
+      <c r="K44" s="28" t="n"/>
+      <c r="L44" s="28" t="n"/>
+      <c r="M44" s="28" t="n"/>
+      <c r="N44" s="28" t="n"/>
+      <c r="O44" s="1" t="inlineStr"/>
+      <c r="P44" s="31" t="n"/>
+      <c r="Q44" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="R44" s="26" t="n"/>
-      <c r="S44" s="26" t="n"/>
-      <c r="T44" s="26" t="n"/>
-      <c r="U44" s="26" t="n"/>
-      <c r="V44" s="26" t="n"/>
-      <c r="W44" s="26" t="n"/>
-      <c r="X44" s="27" t="n"/>
-      <c r="Y44" s="26" t="n"/>
-      <c r="Z44" s="26" t="n"/>
-      <c r="AA44" s="26" t="n"/>
-      <c r="AB44" s="26" t="n"/>
-      <c r="AC44" s="26" t="n"/>
-      <c r="AD44" s="27" t="n"/>
-      <c r="AE44" s="26" t="n"/>
-      <c r="AF44" s="27" t="n"/>
-      <c r="AG44" s="26" t="n"/>
-      <c r="AH44" s="1" t="inlineStr"/>
+      <c r="R44" s="28" t="n"/>
+      <c r="S44" s="33" t="inlineStr"/>
+      <c r="T44" s="28" t="n"/>
+      <c r="U44" s="28" t="n"/>
+      <c r="V44" s="28" t="n"/>
+      <c r="W44" s="28" t="n"/>
+      <c r="X44" s="29" t="n"/>
+      <c r="Y44" s="28" t="n"/>
+      <c r="Z44" s="28" t="n"/>
+      <c r="AA44" s="28" t="n"/>
+      <c r="AB44" s="28" t="n"/>
+      <c r="AC44" s="28" t="n"/>
+      <c r="AD44" s="29" t="n"/>
+      <c r="AE44" s="28" t="n"/>
+      <c r="AF44" s="29" t="n"/>
+      <c r="AG44" s="28" t="n"/>
+      <c r="AH44" s="3" t="inlineStr"/>
     </row>
     <row r="45" ht="99.95" customHeight="1">
-      <c r="A45" s="24" t="n"/>
-      <c r="B45" s="25" t="n">
+      <c r="A45" s="26" t="n"/>
+      <c r="B45" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="C45" s="36" t="inlineStr">
+      <c r="C45" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Биология              Морозова Е.Н. </t>
+        </is>
+      </c>
+      <c r="D45" s="43" t="inlineStr"/>
+      <c r="E45" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Основы безопасности и защиты Родины   Иванов В.В.  </t>
         </is>
       </c>
-      <c r="D45" s="36" t="inlineStr"/>
-      <c r="E45" s="36" t="inlineStr"/>
-      <c r="F45" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Биология              Морозова Е.Н. </t>
-        </is>
-      </c>
-      <c r="G45" s="36" t="inlineStr">
-        <is>
-          <t>Литература       Исаева Г.А.</t>
-        </is>
-      </c>
-      <c r="H45" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Право     Кожевников В.Е.</t>
-        </is>
-      </c>
-      <c r="I45" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Иностранный язык в профессиональной деятельности        Шарипов И.Н. </t>
-        </is>
-      </c>
-      <c r="J45" s="36" t="inlineStr">
+      <c r="F45" s="39" t="inlineStr"/>
+      <c r="G45" s="39" t="inlineStr"/>
+      <c r="H45" s="39" t="inlineStr">
+        <is>
+          <t>Иностранный язык            Шарипов И.Н.</t>
+        </is>
+      </c>
+      <c r="I45" s="39" t="inlineStr"/>
+      <c r="J45" s="39" t="inlineStr">
         <is>
           <t>Гражданский процесс                           Лебедева М.Л.</t>
         </is>
       </c>
-      <c r="K45" s="36" t="inlineStr">
+      <c r="K45" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Статистика       Систейкина Е.Е. </t>
         </is>
       </c>
-      <c r="L45" s="36" t="inlineStr"/>
-      <c r="M45" s="36" t="inlineStr"/>
-      <c r="N45" s="36" t="inlineStr"/>
-      <c r="O45" s="21" t="inlineStr"/>
-      <c r="P45" s="29" t="n"/>
-      <c r="Q45" s="30" t="n">
+      <c r="L45" s="39" t="inlineStr"/>
+      <c r="M45" s="39" t="inlineStr">
+        <is>
+          <t>Правовое обеспечение профессиональной деятельности     Кожевников В.Е.</t>
+        </is>
+      </c>
+      <c r="N45" s="39" t="inlineStr"/>
+      <c r="O45" s="1" t="inlineStr"/>
+      <c r="P45" s="31" t="n"/>
+      <c r="Q45" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="R45" s="36" t="inlineStr">
+      <c r="R45" s="39" t="inlineStr">
         <is>
           <t>Клиническое материаловедение  Станишевская Д.Н.</t>
         </is>
       </c>
-      <c r="S45" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">История России   Козлов Д.В. </t>
-        </is>
-      </c>
-      <c r="T45" s="36" t="inlineStr"/>
-      <c r="U45" s="36" t="inlineStr"/>
-      <c r="V45" s="36" t="inlineStr"/>
-      <c r="W45" s="36" t="inlineStr"/>
-      <c r="X45" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Технология изготовления съемных пластиночных  протезов        Горин А.А.</t>
-        </is>
-      </c>
-      <c r="Y45" s="36" t="inlineStr"/>
-      <c r="Z45" s="36" t="inlineStr">
-        <is>
-          <t>Иностранный язык в профессиональной деятельности      Дремлюгина Л.А.</t>
-        </is>
-      </c>
-      <c r="AA45" s="36" t="inlineStr"/>
-      <c r="AB45" s="36" t="inlineStr"/>
-      <c r="AC45" s="36" t="inlineStr"/>
-      <c r="AD45" s="38" t="inlineStr">
+      <c r="S45" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Числитель     История России   Козлов Д.В.         </t>
+        </is>
+      </c>
+      <c r="T45" s="39" t="inlineStr"/>
+      <c r="U45" s="39" t="inlineStr"/>
+      <c r="V45" s="39" t="inlineStr">
+        <is>
+          <t>Клиническое материаловедение  Станишевская Д.Н.</t>
+        </is>
+      </c>
+      <c r="W45" s="43" t="inlineStr"/>
+      <c r="X45" s="39" t="inlineStr">
+        <is>
+          <t>Технология изготовления съемных пластиночных  протезов        Горин А.А.</t>
+        </is>
+      </c>
+      <c r="Y45" s="39" t="inlineStr"/>
+      <c r="Z45" s="39" t="inlineStr"/>
+      <c r="AA45" s="43" t="inlineStr"/>
+      <c r="AB45" s="39" t="inlineStr">
+        <is>
+          <t>Основы латинского языка с медицинской терминологией       Дремлюгина Л.А.</t>
+        </is>
+      </c>
+      <c r="AC45" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Анатомия и физиология человека          Маклаков И.А. </t>
+        </is>
+      </c>
+      <c r="AD45" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Выполнение работ по профессии "Педикюрша"  Алексеенко Е.М.  </t>
         </is>
       </c>
-      <c r="AE45" s="36" t="inlineStr">
+      <c r="AE45" s="39" t="inlineStr">
         <is>
           <t>Эстетические процедуры коррекции, эпиляции                   Джокич Э.А.</t>
         </is>
       </c>
-      <c r="AF45" s="36" t="inlineStr"/>
-      <c r="AG45" s="31" t="inlineStr">
+      <c r="AF45" s="43" t="inlineStr"/>
+      <c r="AG45" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Технология визажа Ермолаева И.В.                                               </t>
         </is>
       </c>
-      <c r="AH45" s="1" t="inlineStr"/>
+      <c r="AH45" s="3" t="inlineStr"/>
     </row>
     <row r="46" ht="99.95" customHeight="1" thickBot="1">
-      <c r="A46" s="26" t="n"/>
-      <c r="B46" s="40" t="n">
+      <c r="A46" s="28" t="n"/>
+      <c r="B46" s="44" t="n">
         <v>8</v>
       </c>
-      <c r="C46" s="41" t="n"/>
-      <c r="D46" s="41" t="n"/>
-      <c r="E46" s="41" t="n"/>
-      <c r="F46" s="41" t="n"/>
-      <c r="G46" s="41" t="n"/>
-      <c r="H46" s="41" t="n"/>
-      <c r="I46" s="41" t="n"/>
-      <c r="J46" s="41" t="n"/>
-      <c r="K46" s="41" t="n"/>
-      <c r="L46" s="41" t="n"/>
-      <c r="M46" s="41" t="n"/>
-      <c r="N46" s="41" t="n"/>
-      <c r="O46" s="21" t="inlineStr"/>
-      <c r="P46" s="44" t="n"/>
-      <c r="Q46" s="45" t="n">
+      <c r="C46" s="45" t="n"/>
+      <c r="D46" s="45" t="n"/>
+      <c r="E46" s="45" t="n"/>
+      <c r="F46" s="45" t="n"/>
+      <c r="G46" s="45" t="n"/>
+      <c r="H46" s="45" t="n"/>
+      <c r="I46" s="45" t="n"/>
+      <c r="J46" s="45" t="n"/>
+      <c r="K46" s="45" t="n"/>
+      <c r="L46" s="45" t="n"/>
+      <c r="M46" s="45" t="n"/>
+      <c r="N46" s="45" t="n"/>
+      <c r="O46" s="1" t="inlineStr"/>
+      <c r="P46" s="48" t="n"/>
+      <c r="Q46" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="R46" s="41" t="n"/>
-      <c r="S46" s="41" t="n"/>
-      <c r="T46" s="41" t="n"/>
-      <c r="U46" s="41" t="n"/>
-      <c r="V46" s="41" t="n"/>
-      <c r="W46" s="41" t="n"/>
-      <c r="X46" s="41" t="n"/>
-      <c r="Y46" s="41" t="n"/>
-      <c r="Z46" s="41" t="n"/>
-      <c r="AA46" s="41" t="n"/>
-      <c r="AB46" s="41" t="n"/>
-      <c r="AC46" s="41" t="n"/>
-      <c r="AD46" s="42" t="n"/>
-      <c r="AE46" s="41" t="n"/>
-      <c r="AF46" s="41" t="n"/>
-      <c r="AG46" s="26" t="n"/>
-      <c r="AH46" s="1" t="inlineStr"/>
+      <c r="R46" s="45" t="n"/>
+      <c r="S46" s="39" t="inlineStr"/>
+      <c r="T46" s="45" t="n"/>
+      <c r="U46" s="45" t="n"/>
+      <c r="V46" s="45" t="n"/>
+      <c r="W46" s="45" t="n"/>
+      <c r="X46" s="45" t="n"/>
+      <c r="Y46" s="45" t="n"/>
+      <c r="Z46" s="45" t="n"/>
+      <c r="AA46" s="45" t="n"/>
+      <c r="AB46" s="45" t="n"/>
+      <c r="AC46" s="45" t="n"/>
+      <c r="AD46" s="46" t="n"/>
+      <c r="AE46" s="45" t="n"/>
+      <c r="AF46" s="45" t="n"/>
+      <c r="AG46" s="28" t="n"/>
+      <c r="AH46" s="3" t="inlineStr"/>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="1" t="inlineStr"/>
-      <c r="B47" s="61" t="inlineStr"/>
-      <c r="C47" s="1" t="inlineStr"/>
-      <c r="D47" s="1" t="inlineStr"/>
-      <c r="E47" s="1" t="inlineStr"/>
-      <c r="F47" s="1" t="inlineStr"/>
-      <c r="G47" s="1" t="inlineStr"/>
-      <c r="H47" s="1" t="inlineStr"/>
-      <c r="I47" s="1" t="inlineStr"/>
-      <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="62" t="inlineStr"/>
-      <c r="L47" s="21" t="inlineStr"/>
-      <c r="M47" s="21" t="inlineStr"/>
-      <c r="N47" s="21" t="inlineStr"/>
-      <c r="O47" s="1" t="inlineStr"/>
-      <c r="P47" s="1" t="inlineStr"/>
-      <c r="Q47" s="1" t="inlineStr"/>
-      <c r="R47" s="1" t="inlineStr"/>
-      <c r="S47" s="1" t="inlineStr"/>
-      <c r="T47" s="1" t="inlineStr"/>
-      <c r="U47" s="1" t="inlineStr"/>
-      <c r="V47" s="1" t="inlineStr"/>
-      <c r="W47" s="1" t="inlineStr"/>
-      <c r="X47" s="1" t="inlineStr"/>
-      <c r="Y47" s="1" t="inlineStr"/>
-      <c r="Z47" s="1" t="inlineStr"/>
-      <c r="AA47" s="1" t="inlineStr"/>
-      <c r="AB47" s="1" t="inlineStr"/>
-      <c r="AC47" s="1" t="inlineStr"/>
-      <c r="AD47" s="1" t="inlineStr"/>
-      <c r="AE47" s="1" t="inlineStr"/>
-      <c r="AF47" s="1" t="inlineStr"/>
-      <c r="AG47" s="1" t="inlineStr"/>
-      <c r="AH47" s="1" t="inlineStr"/>
+      <c r="A47" s="3" t="inlineStr"/>
+      <c r="B47" s="68" t="inlineStr"/>
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="69" t="inlineStr"/>
+      <c r="L47" s="1" t="inlineStr"/>
+      <c r="M47" s="1" t="inlineStr"/>
+      <c r="N47" s="1" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr"/>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr"/>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr"/>
+      <c r="V47" s="3" t="inlineStr"/>
+      <c r="W47" s="3" t="inlineStr"/>
+      <c r="X47" s="3" t="inlineStr"/>
+      <c r="Y47" s="3" t="inlineStr"/>
+      <c r="Z47" s="3" t="inlineStr"/>
+      <c r="AA47" s="3" t="inlineStr"/>
+      <c r="AB47" s="3" t="inlineStr"/>
+      <c r="AC47" s="3" t="inlineStr"/>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr"/>
+      <c r="AF47" s="3" t="inlineStr"/>
+      <c r="AG47" s="3" t="inlineStr"/>
+      <c r="AH47" s="3" t="inlineStr"/>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="1" t="inlineStr"/>
-      <c r="B48" s="1" t="inlineStr"/>
-      <c r="C48" s="1" t="inlineStr"/>
-      <c r="D48" s="1" t="inlineStr"/>
-      <c r="E48" s="1" t="inlineStr"/>
-      <c r="F48" s="1" t="inlineStr"/>
-      <c r="G48" s="1" t="inlineStr"/>
-      <c r="H48" s="1" t="inlineStr"/>
-      <c r="I48" s="1" t="inlineStr"/>
-      <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="4" t="n"/>
-      <c r="L48" s="21" t="inlineStr"/>
-      <c r="M48" s="21" t="inlineStr"/>
-      <c r="N48" s="21" t="inlineStr"/>
-      <c r="O48" s="1" t="inlineStr"/>
-      <c r="P48" s="1" t="inlineStr"/>
-      <c r="Q48" s="1" t="inlineStr"/>
-      <c r="R48" s="1" t="inlineStr"/>
-      <c r="S48" s="1" t="inlineStr"/>
-      <c r="T48" s="1" t="inlineStr"/>
-      <c r="U48" s="1" t="inlineStr"/>
-      <c r="V48" s="1" t="inlineStr"/>
-      <c r="W48" s="1" t="inlineStr"/>
-      <c r="X48" s="1" t="inlineStr"/>
-      <c r="Y48" s="1" t="inlineStr"/>
-      <c r="Z48" s="1" t="inlineStr"/>
-      <c r="AA48" s="1" t="inlineStr"/>
-      <c r="AB48" s="1" t="inlineStr"/>
-      <c r="AC48" s="1" t="inlineStr"/>
-      <c r="AD48" s="1" t="inlineStr"/>
-      <c r="AE48" s="1" t="inlineStr"/>
-      <c r="AF48" s="1" t="inlineStr"/>
-      <c r="AG48" s="1" t="inlineStr"/>
-      <c r="AH48" s="1" t="inlineStr"/>
+      <c r="A48" s="3" t="inlineStr"/>
+      <c r="B48" s="3" t="inlineStr"/>
+      <c r="C48" s="3" t="inlineStr"/>
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="1" t="inlineStr"/>
+      <c r="M48" s="1" t="inlineStr"/>
+      <c r="N48" s="1" t="inlineStr"/>
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr"/>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr"/>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr"/>
+      <c r="V48" s="3" t="inlineStr"/>
+      <c r="W48" s="3" t="inlineStr"/>
+      <c r="X48" s="3" t="inlineStr"/>
+      <c r="Y48" s="3" t="inlineStr"/>
+      <c r="Z48" s="3" t="inlineStr"/>
+      <c r="AA48" s="3" t="inlineStr"/>
+      <c r="AB48" s="3" t="inlineStr"/>
+      <c r="AC48" s="3" t="inlineStr"/>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr"/>
+      <c r="AF48" s="3" t="inlineStr"/>
+      <c r="AG48" s="3" t="inlineStr"/>
+      <c r="AH48" s="3" t="inlineStr"/>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="1" t="inlineStr"/>
-      <c r="B49" s="1" t="inlineStr"/>
-      <c r="C49" s="1" t="inlineStr"/>
-      <c r="D49" s="1" t="inlineStr"/>
-      <c r="E49" s="1" t="inlineStr"/>
-      <c r="F49" s="1" t="inlineStr"/>
-      <c r="G49" s="1" t="inlineStr"/>
-      <c r="H49" s="1" t="inlineStr"/>
-      <c r="I49" s="1" t="inlineStr"/>
-      <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="4" t="n"/>
-      <c r="L49" s="1" t="inlineStr"/>
-      <c r="M49" s="1" t="inlineStr"/>
-      <c r="N49" s="1" t="inlineStr"/>
-      <c r="O49" s="1" t="inlineStr"/>
-      <c r="P49" s="1" t="inlineStr"/>
-      <c r="Q49" s="1" t="inlineStr"/>
-      <c r="R49" s="1" t="inlineStr"/>
-      <c r="S49" s="1" t="inlineStr"/>
-      <c r="T49" s="1" t="inlineStr"/>
-      <c r="U49" s="1" t="inlineStr"/>
-      <c r="V49" s="1" t="inlineStr"/>
-      <c r="W49" s="1" t="inlineStr"/>
-      <c r="X49" s="1" t="inlineStr"/>
-      <c r="Y49" s="1" t="inlineStr"/>
-      <c r="Z49" s="1" t="inlineStr"/>
-      <c r="AA49" s="1" t="inlineStr"/>
-      <c r="AB49" s="1" t="inlineStr"/>
-      <c r="AC49" s="1" t="inlineStr"/>
-      <c r="AD49" s="1" t="inlineStr"/>
-      <c r="AE49" s="1" t="inlineStr"/>
-      <c r="AF49" s="1" t="inlineStr"/>
-      <c r="AG49" s="1" t="inlineStr"/>
-      <c r="AH49" s="1" t="inlineStr"/>
+      <c r="A49" s="3" t="inlineStr"/>
+      <c r="B49" s="3" t="inlineStr"/>
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="3" t="inlineStr"/>
+      <c r="M49" s="3" t="inlineStr"/>
+      <c r="N49" s="3" t="inlineStr"/>
+      <c r="O49" s="3" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr"/>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr"/>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr"/>
+      <c r="V49" s="3" t="inlineStr"/>
+      <c r="W49" s="3" t="inlineStr"/>
+      <c r="X49" s="3" t="inlineStr"/>
+      <c r="Y49" s="3" t="inlineStr"/>
+      <c r="Z49" s="3" t="inlineStr"/>
+      <c r="AA49" s="3" t="inlineStr"/>
+      <c r="AB49" s="3" t="inlineStr"/>
+      <c r="AC49" s="3" t="inlineStr"/>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr"/>
+      <c r="AF49" s="3" t="inlineStr"/>
+      <c r="AG49" s="3" t="inlineStr"/>
+      <c r="AH49" s="3" t="inlineStr"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="1" t="inlineStr"/>
-      <c r="B50" s="1" t="inlineStr"/>
-      <c r="C50" s="1" t="inlineStr"/>
-      <c r="D50" s="1" t="inlineStr"/>
-      <c r="E50" s="1" t="inlineStr"/>
-      <c r="F50" s="1" t="inlineStr"/>
-      <c r="G50" s="1" t="inlineStr"/>
-      <c r="H50" s="1" t="inlineStr"/>
-      <c r="I50" s="1" t="inlineStr"/>
-      <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="4" t="n"/>
-      <c r="L50" s="1" t="inlineStr"/>
-      <c r="M50" s="1" t="inlineStr"/>
-      <c r="N50" s="1" t="inlineStr"/>
-      <c r="O50" s="1" t="inlineStr"/>
-      <c r="P50" s="1" t="inlineStr"/>
-      <c r="Q50" s="1" t="inlineStr"/>
-      <c r="R50" s="1" t="inlineStr"/>
-      <c r="S50" s="1" t="inlineStr"/>
-      <c r="T50" s="1" t="inlineStr"/>
-      <c r="U50" s="1" t="inlineStr"/>
-      <c r="V50" s="1" t="inlineStr"/>
-      <c r="W50" s="1" t="inlineStr"/>
-      <c r="X50" s="1" t="inlineStr"/>
-      <c r="Y50" s="1" t="inlineStr"/>
-      <c r="Z50" s="1" t="inlineStr"/>
-      <c r="AA50" s="1" t="inlineStr"/>
-      <c r="AB50" s="1" t="inlineStr"/>
-      <c r="AC50" s="1" t="inlineStr"/>
-      <c r="AD50" s="1" t="inlineStr"/>
-      <c r="AE50" s="1" t="inlineStr"/>
-      <c r="AF50" s="1" t="inlineStr"/>
-      <c r="AG50" s="1" t="inlineStr"/>
-      <c r="AH50" s="1" t="inlineStr"/>
+      <c r="A50" s="3" t="inlineStr"/>
+      <c r="B50" s="3" t="inlineStr"/>
+      <c r="C50" s="3" t="inlineStr"/>
+      <c r="D50" s="3" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr"/>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="3" t="inlineStr"/>
+      <c r="M50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr"/>
+      <c r="O50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr"/>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr"/>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr"/>
+      <c r="V50" s="3" t="inlineStr"/>
+      <c r="W50" s="3" t="inlineStr"/>
+      <c r="X50" s="3" t="inlineStr"/>
+      <c r="Y50" s="3" t="inlineStr"/>
+      <c r="Z50" s="3" t="inlineStr"/>
+      <c r="AA50" s="3" t="inlineStr"/>
+      <c r="AB50" s="3" t="inlineStr"/>
+      <c r="AC50" s="3" t="inlineStr"/>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr"/>
+      <c r="AF50" s="3" t="inlineStr"/>
+      <c r="AG50" s="3" t="inlineStr"/>
+      <c r="AH50" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="571">
+  <mergeCells count="570">
     <mergeCell ref="U31:U32"/>
     <mergeCell ref="R13:R14"/>
     <mergeCell ref="A39:A46"/>
@@ -5199,12 +5212,12 @@
     <mergeCell ref="K27:K28"/>
     <mergeCell ref="Z37:Z38"/>
     <mergeCell ref="AD45:AD46"/>
-    <mergeCell ref="V45:V46"/>
+    <mergeCell ref="AF45:AF46"/>
     <mergeCell ref="W11:W12"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="X45:X46"/>
     <mergeCell ref="H13:H14"/>
-    <mergeCell ref="AF45:AF46"/>
+    <mergeCell ref="V45:V46"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="AG43:AG44"/>
     <mergeCell ref="AF11:AF12"/>
@@ -5227,24 +5240,23 @@
     <mergeCell ref="H41:H42"/>
     <mergeCell ref="C45:C46"/>
     <mergeCell ref="I7:I8"/>
+    <mergeCell ref="AA15:AA16"/>
     <mergeCell ref="D11:D12"/>
-    <mergeCell ref="AA15:AA16"/>
-    <mergeCell ref="I2:V2"/>
     <mergeCell ref="AC15:AC16"/>
     <mergeCell ref="X19:X20"/>
     <mergeCell ref="L43:L44"/>
+    <mergeCell ref="N43:N44"/>
     <mergeCell ref="S39:S40"/>
-    <mergeCell ref="N43:N44"/>
     <mergeCell ref="AC3:AG3"/>
     <mergeCell ref="V27:V28"/>
     <mergeCell ref="AF9:AF10"/>
     <mergeCell ref="K47:K50"/>
+    <mergeCell ref="AC29:AC30"/>
     <mergeCell ref="S37:S38"/>
-    <mergeCell ref="AC29:AC30"/>
     <mergeCell ref="X33:X34"/>
+    <mergeCell ref="Z33:Z34"/>
     <mergeCell ref="AC23:AC24"/>
     <mergeCell ref="U37:U38"/>
-    <mergeCell ref="Z33:Z34"/>
     <mergeCell ref="AE23:AE24"/>
     <mergeCell ref="M37:M38"/>
     <mergeCell ref="M27:M28"/>
@@ -5255,21 +5267,23 @@
     <mergeCell ref="D37:D38"/>
     <mergeCell ref="J21:J22"/>
     <mergeCell ref="AD7:AD8"/>
+    <mergeCell ref="L21:L22"/>
     <mergeCell ref="G25:G26"/>
-    <mergeCell ref="L21:L22"/>
     <mergeCell ref="M41:M42"/>
     <mergeCell ref="T31:T32"/>
+    <mergeCell ref="U19:U20"/>
     <mergeCell ref="Z15:Z16"/>
-    <mergeCell ref="U19:U20"/>
+    <mergeCell ref="AB15:AB16"/>
+    <mergeCell ref="R23:R24"/>
     <mergeCell ref="W19:W20"/>
-    <mergeCell ref="AB15:AB16"/>
     <mergeCell ref="M43:M44"/>
     <mergeCell ref="AF19:AF20"/>
     <mergeCell ref="A23:A30"/>
+    <mergeCell ref="H29:H30"/>
     <mergeCell ref="A31:A38"/>
-    <mergeCell ref="H29:H30"/>
     <mergeCell ref="R7:R8"/>
     <mergeCell ref="M11:M12"/>
+    <mergeCell ref="S27:S28"/>
     <mergeCell ref="AB25:AB26"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="U45:U46"/>
@@ -5293,7 +5307,6 @@
     <mergeCell ref="V43:V44"/>
     <mergeCell ref="X43:X44"/>
     <mergeCell ref="J29:J30"/>
-    <mergeCell ref="R39:R40"/>
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="E43:E44"/>
     <mergeCell ref="U27:U28"/>
@@ -5305,9 +5318,9 @@
     <mergeCell ref="AE17:AE18"/>
     <mergeCell ref="AD23:AD24"/>
     <mergeCell ref="Z21:Z22"/>
+    <mergeCell ref="N37:N38"/>
     <mergeCell ref="AB21:AB22"/>
     <mergeCell ref="L37:L38"/>
-    <mergeCell ref="N37:N38"/>
     <mergeCell ref="AG11:AG12"/>
     <mergeCell ref="W35:W36"/>
     <mergeCell ref="Y35:Y36"/>
@@ -5326,11 +5339,11 @@
     <mergeCell ref="T39:T40"/>
     <mergeCell ref="G31:G32"/>
     <mergeCell ref="D35:D36"/>
-    <mergeCell ref="J19:J20"/>
     <mergeCell ref="L19:L20"/>
     <mergeCell ref="E39:E40"/>
     <mergeCell ref="N25:N26"/>
     <mergeCell ref="AF33:AF34"/>
+    <mergeCell ref="S23:S24"/>
     <mergeCell ref="AG17:AG18"/>
     <mergeCell ref="T21:T22"/>
     <mergeCell ref="U41:U42"/>
@@ -5342,8 +5355,8 @@
     <mergeCell ref="L45:L46"/>
     <mergeCell ref="AE19:AE20"/>
     <mergeCell ref="AB23:AB24"/>
+    <mergeCell ref="F31:F32"/>
     <mergeCell ref="AG19:AG20"/>
-    <mergeCell ref="F31:F32"/>
     <mergeCell ref="U43:U44"/>
     <mergeCell ref="T11:T12"/>
     <mergeCell ref="Z39:Z40"/>
@@ -5354,14 +5367,13 @@
     <mergeCell ref="AD37:AD38"/>
     <mergeCell ref="T27:T28"/>
     <mergeCell ref="I31:I32"/>
+    <mergeCell ref="K37:K38"/>
     <mergeCell ref="AD17:AD18"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="K37:K38"/>
     <mergeCell ref="I45:I46"/>
     <mergeCell ref="W25:W26"/>
     <mergeCell ref="AD19:AD20"/>
     <mergeCell ref="G39:G40"/>
-    <mergeCell ref="J27:J28"/>
     <mergeCell ref="T9:T10"/>
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="AE13:AE14"/>
@@ -5391,18 +5403,18 @@
     <mergeCell ref="T37:T38"/>
     <mergeCell ref="V37:V38"/>
     <mergeCell ref="AC41:AC42"/>
+    <mergeCell ref="Z45:Z46"/>
     <mergeCell ref="AE41:AE42"/>
-    <mergeCell ref="Z45:Z46"/>
+    <mergeCell ref="AB45:AB46"/>
     <mergeCell ref="AE35:AE36"/>
     <mergeCell ref="AG41:AG42"/>
-    <mergeCell ref="AB45:AB46"/>
     <mergeCell ref="T45:T46"/>
+    <mergeCell ref="AG35:AG36"/>
     <mergeCell ref="U11:U12"/>
-    <mergeCell ref="AG35:AG36"/>
     <mergeCell ref="S11:S12"/>
     <mergeCell ref="AC43:AC44"/>
+    <mergeCell ref="Y29:Y30"/>
     <mergeCell ref="K45:K46"/>
-    <mergeCell ref="Y29:Y30"/>
     <mergeCell ref="N33:N34"/>
     <mergeCell ref="Y39:Y40"/>
     <mergeCell ref="F21:F22"/>
@@ -5420,8 +5432,8 @@
     <mergeCell ref="F39:F40"/>
     <mergeCell ref="T19:T20"/>
     <mergeCell ref="J43:J44"/>
+    <mergeCell ref="AA21:AA22"/>
     <mergeCell ref="V25:V26"/>
-    <mergeCell ref="AA21:AA22"/>
     <mergeCell ref="X25:X26"/>
     <mergeCell ref="AD9:AD10"/>
     <mergeCell ref="AG29:AG30"/>
@@ -5434,8 +5446,8 @@
     <mergeCell ref="K33:K34"/>
     <mergeCell ref="C33:C34"/>
     <mergeCell ref="V13:V14"/>
+    <mergeCell ref="X13:X14"/>
     <mergeCell ref="E33:E34"/>
-    <mergeCell ref="X13:X14"/>
     <mergeCell ref="S17:S18"/>
     <mergeCell ref="X7:X8"/>
     <mergeCell ref="U17:U18"/>
@@ -5445,14 +5457,14 @@
     <mergeCell ref="K41:K42"/>
     <mergeCell ref="AD15:AD16"/>
     <mergeCell ref="K35:K36"/>
+    <mergeCell ref="AF15:AF16"/>
+    <mergeCell ref="V15:V16"/>
+    <mergeCell ref="AE43:AE44"/>
+    <mergeCell ref="X15:X16"/>
     <mergeCell ref="C35:C36"/>
-    <mergeCell ref="AF15:AF16"/>
-    <mergeCell ref="AE43:AE44"/>
-    <mergeCell ref="V15:V16"/>
     <mergeCell ref="S19:S20"/>
+    <mergeCell ref="M35:M36"/>
     <mergeCell ref="E35:E36"/>
-    <mergeCell ref="M35:M36"/>
-    <mergeCell ref="X15:X16"/>
     <mergeCell ref="U25:U26"/>
     <mergeCell ref="F27:F28"/>
     <mergeCell ref="H27:H28"/>
@@ -5460,7 +5472,6 @@
     <mergeCell ref="AD41:AD42"/>
     <mergeCell ref="Y45:Y46"/>
     <mergeCell ref="AF41:AF42"/>
-    <mergeCell ref="S45:S46"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="Z11:Z12"/>
     <mergeCell ref="AA11:AA12"/>
@@ -5469,6 +5480,7 @@
     <mergeCell ref="K25:K26"/>
     <mergeCell ref="AF43:AF44"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="R29:R30"/>
     <mergeCell ref="P15:P22"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="AA27:AA28"/>
@@ -5491,17 +5503,16 @@
     <mergeCell ref="I43:I44"/>
     <mergeCell ref="K43:K44"/>
     <mergeCell ref="D15:D16"/>
-    <mergeCell ref="S23:S30"/>
     <mergeCell ref="C43:C44"/>
     <mergeCell ref="AC4:AG4"/>
     <mergeCell ref="AC9:AC10"/>
     <mergeCell ref="AE9:AE10"/>
+    <mergeCell ref="X29:X30"/>
     <mergeCell ref="S33:S34"/>
-    <mergeCell ref="X29:X30"/>
     <mergeCell ref="U33:U34"/>
     <mergeCell ref="F37:F38"/>
+    <mergeCell ref="Z23:Z24"/>
     <mergeCell ref="H37:H38"/>
-    <mergeCell ref="Z23:Z24"/>
     <mergeCell ref="AF7:AF8"/>
     <mergeCell ref="X21:X22"/>
     <mergeCell ref="AC11:AC12"/>
@@ -5511,6 +5522,7 @@
     <mergeCell ref="X31:X32"/>
     <mergeCell ref="Z31:Z32"/>
     <mergeCell ref="U35:U36"/>
+    <mergeCell ref="I2:T2"/>
     <mergeCell ref="W13:W14"/>
     <mergeCell ref="E21:E22"/>
     <mergeCell ref="G21:G22"/>
@@ -5549,7 +5561,6 @@
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="N7:N8"/>
     <mergeCell ref="I11:I12"/>
-    <mergeCell ref="S43:S44"/>
     <mergeCell ref="X39:X40"/>
     <mergeCell ref="AE25:AE26"/>
     <mergeCell ref="A15:A22"/>
@@ -5557,21 +5568,21 @@
     <mergeCell ref="AA33:AA34"/>
     <mergeCell ref="X37:X38"/>
     <mergeCell ref="AH23:AH24"/>
-    <mergeCell ref="R23:R30"/>
+    <mergeCell ref="R27:R28"/>
     <mergeCell ref="P31:P38"/>
     <mergeCell ref="Z17:Z18"/>
     <mergeCell ref="G37:G38"/>
     <mergeCell ref="I37:I38"/>
+    <mergeCell ref="AB17:AB18"/>
+    <mergeCell ref="AA45:AA46"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AB11:AB12"/>
     <mergeCell ref="W21:W22"/>
-    <mergeCell ref="AB17:AB18"/>
-    <mergeCell ref="AB11:AB12"/>
-    <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="AA45:AA46"/>
     <mergeCell ref="AD11:AD12"/>
     <mergeCell ref="L25:L26"/>
     <mergeCell ref="M45:M46"/>
+    <mergeCell ref="R35:R36"/>
     <mergeCell ref="W31:W32"/>
-    <mergeCell ref="R35:R36"/>
     <mergeCell ref="Z19:Z20"/>
     <mergeCell ref="AB19:AB20"/>
     <mergeCell ref="W23:W24"/>
@@ -5610,11 +5621,10 @@
     <mergeCell ref="AC35:AC36"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="P39:P46"/>
-    <mergeCell ref="R41:R42"/>
     <mergeCell ref="K13:K14"/>
     <mergeCell ref="E45:E46"/>
+    <mergeCell ref="K7:K8"/>
     <mergeCell ref="J41:J42"/>
-    <mergeCell ref="K7:K8"/>
     <mergeCell ref="G45:G46"/>
     <mergeCell ref="AE15:AE16"/>
     <mergeCell ref="W29:W30"/>
@@ -5628,14 +5638,15 @@
     <mergeCell ref="T43:T44"/>
     <mergeCell ref="Z27:Z28"/>
     <mergeCell ref="M19:M20"/>
+    <mergeCell ref="AB33:AB34"/>
     <mergeCell ref="W37:W38"/>
-    <mergeCell ref="AB33:AB34"/>
     <mergeCell ref="AD33:AD34"/>
     <mergeCell ref="AG23:AG24"/>
     <mergeCell ref="AB35:AB36"/>
     <mergeCell ref="N21:N22"/>
     <mergeCell ref="D45:D46"/>
     <mergeCell ref="F45:F46"/>
+    <mergeCell ref="R25:R26"/>
     <mergeCell ref="Y19:Y20"/>
     <mergeCell ref="T25:T26"/>
     <mergeCell ref="T41:T42"/>
@@ -5653,6 +5664,7 @@
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="T15:T16"/>
     <mergeCell ref="V21:V22"/>
+    <mergeCell ref="S25:S26"/>
     <mergeCell ref="AF37:AF38"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="K15:K16"/>
@@ -5661,12 +5673,12 @@
     <mergeCell ref="AG21:AG22"/>
     <mergeCell ref="Y21:Y22"/>
     <mergeCell ref="Z41:Z42"/>
+    <mergeCell ref="AE31:AE32"/>
+    <mergeCell ref="S7:S8"/>
     <mergeCell ref="AB41:AB42"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="AE31:AE32"/>
     <mergeCell ref="AG31:AG32"/>
+    <mergeCell ref="W45:W46"/>
     <mergeCell ref="U7:U8"/>
-    <mergeCell ref="W45:W46"/>
     <mergeCell ref="AD35:AD36"/>
     <mergeCell ref="W7:W8"/>
     <mergeCell ref="F35:F36"/>
@@ -5686,7 +5698,6 @@
     <mergeCell ref="AD21:AD22"/>
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="J39:J40"/>
-    <mergeCell ref="S31:S32"/>
     <mergeCell ref="Y9:Y10"/>
     <mergeCell ref="AA9:AA10"/>
     <mergeCell ref="T29:T30"/>
@@ -5694,8 +5705,8 @@
     <mergeCell ref="X23:X24"/>
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="AB31:AB32"/>
+    <mergeCell ref="N17:N18"/>
     <mergeCell ref="S13:S14"/>
-    <mergeCell ref="N17:N18"/>
     <mergeCell ref="U13:U14"/>
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="C21:C22"/>
@@ -5705,8 +5716,8 @@
     <mergeCell ref="N19:N20"/>
     <mergeCell ref="S15:S16"/>
     <mergeCell ref="C23:C24"/>
+    <mergeCell ref="I39:I40"/>
     <mergeCell ref="D43:D44"/>
-    <mergeCell ref="I39:I40"/>
     <mergeCell ref="F43:F44"/>
     <mergeCell ref="U21:U22"/>
     <mergeCell ref="AE37:AE38"/>
@@ -5722,10 +5733,10 @@
     <mergeCell ref="V29:V30"/>
     <mergeCell ref="Y43:Y44"/>
     <mergeCell ref="AD39:AD40"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="AF39:AF40"/>
     <mergeCell ref="K21:K22"/>
-    <mergeCell ref="AF39:AF40"/>
     <mergeCell ref="AA43:AA44"/>
-    <mergeCell ref="F25:F26"/>
     <mergeCell ref="AG27:AG28"/>
     <mergeCell ref="AD31:AD32"/>
     <mergeCell ref="V19:V20"/>
@@ -5736,30 +5747,31 @@
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="V31:V32"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="K39:K40"/>
     <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="E11:E12"/>
     <mergeCell ref="A7:A14"/>
     <mergeCell ref="Y25:Y26"/>
     <mergeCell ref="AF21:AF22"/>
     <mergeCell ref="AA25:AA26"/>
     <mergeCell ref="AC25:AC26"/>
+    <mergeCell ref="AF23:AF24"/>
     <mergeCell ref="L27:L28"/>
-    <mergeCell ref="AF23:AF24"/>
     <mergeCell ref="P23:P30"/>
     <mergeCell ref="N27:N28"/>
     <mergeCell ref="Z9:Z10"/>
+    <mergeCell ref="S29:S30"/>
     <mergeCell ref="C37:C38"/>
     <mergeCell ref="AC2:AG2"/>
     <mergeCell ref="V17:V18"/>
     <mergeCell ref="E37:E38"/>
     <mergeCell ref="AC13:AC14"/>
-    <mergeCell ref="S21:S22"/>
+    <mergeCell ref="X17:X18"/>
     <mergeCell ref="X11:X12"/>
     <mergeCell ref="AA13:AA14"/>
-    <mergeCell ref="X17:X18"/>
+    <mergeCell ref="S21:S22"/>
     <mergeCell ref="AE7:AE8"/>
-    <mergeCell ref="N35:N36"/>
+    <mergeCell ref="S31:S32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
